--- a/jira_export_2026-09-10.xlsx
+++ b/jira_export_2026-09-10.xlsx
@@ -815,7 +815,7 @@
     <row r="16" ht="26" customHeight="1">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>166 h</t>
+          <t>169 h</t>
         </is>
       </c>
       <c r="B16" s="7" t="n"/>
@@ -829,7 +829,7 @@
       <c r="F16" s="7" t="n"/>
       <c r="G16" s="8" t="inlineStr">
         <is>
-          <t>43.6%</t>
+          <t>44.4%</t>
         </is>
       </c>
       <c r="H16" s="7" t="n"/>
@@ -900,7 +900,7 @@
       <c r="F25" s="7" t="n"/>
       <c r="G25" s="6" t="inlineStr">
         <is>
-          <t>274</t>
+          <t>275</t>
         </is>
       </c>
       <c r="H25" s="7" t="n"/>
@@ -1169,7 +1169,7 @@
         <v>0</v>
       </c>
       <c r="K6" s="14" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="L6" s="14" t="inlineStr">
         <is>
@@ -1593,7 +1593,7 @@
         <v>1</v>
       </c>
       <c r="K12" s="14" t="n">
-        <v>4</v>
+        <v>5.5</v>
       </c>
       <c r="L12" s="14" t="inlineStr"/>
       <c r="M12" s="14" t="inlineStr"/>
@@ -2305,7 +2305,7 @@
         <v>3</v>
       </c>
       <c r="K22" s="14" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="L22" s="14" t="inlineStr">
         <is>
@@ -3089,7 +3089,7 @@
         <v>3</v>
       </c>
       <c r="K33" s="11" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="L33" s="11" t="inlineStr">
         <is>
@@ -9048,7 +9048,7 @@
         <v>17574.178</v>
       </c>
       <c r="P118" s="18" t="n">
-        <v>183.91</v>
+        <v>178.31</v>
       </c>
     </row>
   </sheetData>
@@ -9924,16 +9924,16 @@
         </is>
       </c>
       <c r="B5" s="14" t="n">
-        <v>52.67</v>
+        <v>53.17</v>
       </c>
       <c r="C5" s="14" t="n">
         <v>16.42</v>
       </c>
       <c r="D5" s="14" t="n">
-        <v>5.75</v>
+        <v>7.25</v>
       </c>
       <c r="E5" s="14" t="n">
-        <v>74.83</v>
+        <v>76.83</v>
       </c>
       <c r="F5" s="14" t="n">
         <v>11.17</v>
@@ -9943,7 +9943,7 @@
       </c>
       <c r="H5" s="21" t="inlineStr">
         <is>
-          <t>11.5%</t>
+          <t>11.8%</t>
         </is>
       </c>
     </row>
@@ -9954,7 +9954,7 @@
         </is>
       </c>
       <c r="B6" s="11" t="n">
-        <v>17.25</v>
+        <v>18.25</v>
       </c>
       <c r="C6" s="11" t="n">
         <v>0</v>
@@ -9963,7 +9963,7 @@
         <v>2.5</v>
       </c>
       <c r="E6" s="11" t="n">
-        <v>19.75</v>
+        <v>20.75</v>
       </c>
       <c r="F6" s="11" t="n">
         <v>5.5</v>
@@ -9973,7 +9973,7 @@
       </c>
       <c r="H6" s="21" t="inlineStr">
         <is>
-          <t>7.2%</t>
+          <t>7.5%</t>
         </is>
       </c>
     </row>
@@ -9985,7 +9985,7 @@
         </is>
       </c>
       <c r="B8" s="23" t="n">
-        <v>53.5</v>
+        <v>53.75</v>
       </c>
     </row>
   </sheetData>
@@ -10149,7 +10149,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I18"/>
+  <dimension ref="A1:I19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -10173,7 +10173,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Épics créées ce mois — 11 commande(s)</t>
+          <t>Épics créées ce mois — 12 commande(s)</t>
         </is>
       </c>
     </row>
@@ -10490,22 +10490,22 @@
     <row r="11">
       <c r="A11" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-35576</t>
+          <t>PDMDEP-35622</t>
         </is>
       </c>
       <c r="B11" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-35572</t>
+          <t>PDMDEP-35618</t>
         </is>
       </c>
       <c r="C11" s="14" t="inlineStr">
         <is>
-          <t>08/09/2026</t>
+          <t>10/09/2026</t>
         </is>
       </c>
       <c r="D11" s="14" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DE L'ARIEGE (CD 09)</t>
+          <t>Commune de la Roche-sur-Yon</t>
         </is>
       </c>
       <c r="E11" s="14" t="inlineStr">
@@ -10525,7 +10525,7 @@
       </c>
       <c r="H11" s="14" t="inlineStr">
         <is>
-          <t>00180891</t>
+          <t>00181123</t>
         </is>
       </c>
       <c r="I11" s="25" t="n">
@@ -10535,12 +10535,12 @@
     <row r="12">
       <c r="A12" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-35567</t>
+          <t>PDMDEP-35576</t>
         </is>
       </c>
       <c r="B12" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-35561</t>
+          <t>PDMDEP-35572</t>
         </is>
       </c>
       <c r="C12" s="11" t="inlineStr">
@@ -10550,7 +10550,7 @@
       </c>
       <c r="D12" s="11" t="inlineStr">
         <is>
-          <t>DEPARTEMENT DU MORBIHAN (CD 56)</t>
+          <t>CONSEIL DEPARTEMENTAL DE L'ARIEGE (CD 09)</t>
         </is>
       </c>
       <c r="E12" s="11" t="inlineStr">
@@ -10570,7 +10570,7 @@
       </c>
       <c r="H12" s="11" t="inlineStr">
         <is>
-          <t>00180878</t>
+          <t>00180891</t>
         </is>
       </c>
       <c r="I12" s="26" t="n">
@@ -10580,22 +10580,22 @@
     <row r="13">
       <c r="A13" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-35511</t>
+          <t>PDMDEP-35567</t>
         </is>
       </c>
       <c r="B13" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-35504</t>
+          <t>PDMDEP-35561</t>
         </is>
       </c>
       <c r="C13" s="14" t="inlineStr">
         <is>
-          <t>07/09/2026</t>
+          <t>08/09/2026</t>
         </is>
       </c>
       <c r="D13" s="14" t="inlineStr">
         <is>
-          <t>[TEST]</t>
+          <t>DEPARTEMENT DU MORBIHAN (CD 56)</t>
         </is>
       </c>
       <c r="E13" s="14" t="inlineStr">
@@ -10605,7 +10605,7 @@
       </c>
       <c r="F13" s="14" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="G13" s="14" t="inlineStr">
@@ -10615,7 +10615,7 @@
       </c>
       <c r="H13" s="14" t="inlineStr">
         <is>
-          <t>0015489263</t>
+          <t>00180878</t>
         </is>
       </c>
       <c r="I13" s="25" t="n">
@@ -10625,22 +10625,22 @@
     <row r="14">
       <c r="A14" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-35464</t>
+          <t>PDMDEP-35511</t>
         </is>
       </c>
       <c r="B14" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-35460</t>
+          <t>PDMDEP-35504</t>
         </is>
       </c>
       <c r="C14" s="11" t="inlineStr">
         <is>
-          <t>04/09/2026</t>
+          <t>07/09/2026</t>
         </is>
       </c>
       <c r="D14" s="11" t="inlineStr">
         <is>
-          <t>DEPARTEMENT DE LA CHARENTE (CD 16)</t>
+          <t>[TEST]</t>
         </is>
       </c>
       <c r="E14" s="11" t="inlineStr">
@@ -10650,7 +10650,7 @@
       </c>
       <c r="F14" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="G14" s="11" t="inlineStr">
@@ -10660,83 +10660,107 @@
       </c>
       <c r="H14" s="11" t="inlineStr">
         <is>
-          <t>00180631</t>
+          <t>0015489263</t>
         </is>
       </c>
       <c r="I14" s="26" t="n">
-        <v>455</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="14" t="inlineStr">
         <is>
+          <t>PDMDEP-35464</t>
+        </is>
+      </c>
+      <c r="B15" s="14" t="inlineStr">
+        <is>
+          <t>PDMDEP-35460</t>
+        </is>
+      </c>
+      <c r="C15" s="14" t="inlineStr">
+        <is>
+          <t>04/09/2026</t>
+        </is>
+      </c>
+      <c r="D15" s="14" t="inlineStr">
+        <is>
+          <t>DEPARTEMENT DE LA CHARENTE (CD 16)</t>
+        </is>
+      </c>
+      <c r="E15" s="14" t="inlineStr">
+        <is>
+          <t>LITTERALIS</t>
+        </is>
+      </c>
+      <c r="F15" s="14" t="inlineStr">
+        <is>
+          <t>Vente additionnelle</t>
+        </is>
+      </c>
+      <c r="G15" s="14" t="inlineStr">
+        <is>
+          <t>Services</t>
+        </is>
+      </c>
+      <c r="H15" s="14" t="inlineStr">
+        <is>
+          <t>00180631</t>
+        </is>
+      </c>
+      <c r="I15" s="25" t="n">
+        <v>455</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="11" t="inlineStr">
+        <is>
           <t>PDMDEP-35439</t>
         </is>
       </c>
-      <c r="B15" s="14" t="inlineStr">
+      <c r="B16" s="11" t="inlineStr">
         <is>
           <t>PDMDEP-35435</t>
         </is>
       </c>
-      <c r="C15" s="14" t="inlineStr">
+      <c r="C16" s="11" t="inlineStr">
         <is>
           <t>03/09/2026</t>
         </is>
       </c>
-      <c r="D15" s="14" t="inlineStr">
+      <c r="D16" s="11" t="inlineStr">
         <is>
           <t>DEPARTEMENT DES HAUTS-DE-SEINE</t>
         </is>
       </c>
-      <c r="E15" s="14" t="inlineStr">
+      <c r="E16" s="11" t="inlineStr">
         <is>
           <t>LITTERALIS</t>
         </is>
       </c>
-      <c r="F15" s="14" t="inlineStr">
+      <c r="F16" s="11" t="inlineStr">
         <is>
           <t>Vente additionnelle</t>
         </is>
       </c>
-      <c r="G15" s="14" t="inlineStr">
+      <c r="G16" s="11" t="inlineStr">
         <is>
           <t>Services</t>
         </is>
       </c>
-      <c r="H15" s="14" t="inlineStr">
+      <c r="H16" s="11" t="inlineStr">
         <is>
           <t>00180506</t>
         </is>
       </c>
-      <c r="I15" s="25" t="n">
+      <c r="I16" s="26" t="n">
         <v>3974</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="17" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="B16" s="17" t="n"/>
-      <c r="C16" s="17" t="n"/>
-      <c r="D16" s="17" t="n"/>
-      <c r="E16" s="17" t="n"/>
-      <c r="F16" s="17" t="n"/>
-      <c r="G16" s="17" t="n"/>
-      <c r="H16" s="17" t="inlineStr">
-        <is>
-          <t>11 commande(s)</t>
-        </is>
-      </c>
-      <c r="I16" s="24" t="n">
-        <v>42279</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="17" t="inlineStr">
         <is>
-          <t>dont Littéralis</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="B17" s="17" t="n"/>
@@ -10747,17 +10771,17 @@
       <c r="G17" s="17" t="n"/>
       <c r="H17" s="17" t="inlineStr">
         <is>
-          <t>5 commande(s)</t>
+          <t>12 commande(s)</t>
         </is>
       </c>
       <c r="I17" s="24" t="n">
-        <v>4429</v>
+        <v>42279</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="17" t="inlineStr">
         <is>
-          <t>dont GEODP</t>
+          <t>dont Littéralis</t>
         </is>
       </c>
       <c r="B18" s="17" t="n"/>
@@ -10772,6 +10796,27 @@
         </is>
       </c>
       <c r="I18" s="24" t="n">
+        <v>4429</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="17" t="inlineStr">
+        <is>
+          <t>dont GEODP</t>
+        </is>
+      </c>
+      <c r="B19" s="17" t="n"/>
+      <c r="C19" s="17" t="n"/>
+      <c r="D19" s="17" t="n"/>
+      <c r="E19" s="17" t="n"/>
+      <c r="F19" s="17" t="n"/>
+      <c r="G19" s="17" t="n"/>
+      <c r="H19" s="17" t="inlineStr">
+        <is>
+          <t>6 commande(s)</t>
+        </is>
+      </c>
+      <c r="I19" s="24" t="n">
         <v>37850</v>
       </c>
     </row>

--- a/jira_export_2026-09-10.xlsx
+++ b/jira_export_2026-09-10.xlsx
@@ -720,7 +720,7 @@
     <row r="7" ht="26" customHeight="1">
       <c r="A7" s="6" t="inlineStr">
         <is>
-          <t>17,574 €</t>
+          <t>17,673 €</t>
         </is>
       </c>
       <c r="B7" s="7" t="n"/>
@@ -734,7 +734,7 @@
       <c r="F7" s="7" t="n"/>
       <c r="G7" s="8" t="inlineStr">
         <is>
-          <t>16.6%</t>
+          <t>16.7%</t>
         </is>
       </c>
       <c r="H7" s="7" t="n"/>
@@ -767,7 +767,7 @@
       <c r="C11" s="7" t="n"/>
       <c r="D11" s="6" t="inlineStr">
         <is>
-          <t>12,128 €</t>
+          <t>12,226 €</t>
         </is>
       </c>
       <c r="E11" s="7" t="n"/>
@@ -815,7 +815,7 @@
     <row r="16" ht="26" customHeight="1">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>169 h</t>
+          <t>172 h</t>
         </is>
       </c>
       <c r="B16" s="7" t="n"/>
@@ -829,7 +829,7 @@
       <c r="F16" s="7" t="n"/>
       <c r="G16" s="8" t="inlineStr">
         <is>
-          <t>44.4%</t>
+          <t>45.3%</t>
         </is>
       </c>
       <c r="H16" s="7" t="n"/>
@@ -900,7 +900,7 @@
       <c r="F25" s="7" t="n"/>
       <c r="G25" s="6" t="inlineStr">
         <is>
-          <t>275</t>
+          <t>276</t>
         </is>
       </c>
       <c r="H25" s="7" t="n"/>
@@ -933,7 +933,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P118"/>
+  <dimension ref="A1:P119"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="43" customWidth="1" min="1" max="1"/>
@@ -1482,42 +1482,38 @@
     <row r="11">
       <c r="A11" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-35037</t>
+          <t>PDMDEP-35105</t>
         </is>
       </c>
       <c r="B11" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">[VILLE DE VILLEFRANCHE SUR SAONE ] - mise a jour carto comprise dans leur abonnement annuel </t>
-        </is>
-      </c>
-      <c r="C11" s="11" t="inlineStr">
-        <is>
-          <t>Fabien REUTENAUER</t>
-        </is>
-      </c>
+          <t>[MAIRIE DE CARNAC] - Migration de GEODP-Placier simple</t>
+        </is>
+      </c>
+      <c r="C11" s="11" t="inlineStr"/>
       <c r="D11" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">VILLE DE VILLEFRANCHE SUR SAONE </t>
+          <t>MAIRIE DE CARNAC</t>
         </is>
       </c>
       <c r="E11" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">mise a jour carto comprise dans leur abonnement annuel </t>
+          <t>Migration de GEODP-Placier simple</t>
         </is>
       </c>
       <c r="F11" s="11" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G11" s="11" t="inlineStr">
         <is>
-          <t>Prestation offerte</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H11" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I11" s="11" t="inlineStr">
@@ -1529,15 +1525,23 @@
         <v>1</v>
       </c>
       <c r="K11" s="11" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="L11" s="11" t="inlineStr"/>
-      <c r="M11" s="11" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="L11" s="11" t="inlineStr">
+        <is>
+          <t>PDMDEP-35114</t>
+        </is>
+      </c>
+      <c r="M11" s="11" t="inlineStr">
+        <is>
+          <t>00178806</t>
+        </is>
+      </c>
       <c r="N11" s="12" t="n">
         <v>0</v>
       </c>
       <c r="O11" s="12" t="n">
-        <v>0</v>
+        <v>98.5</v>
       </c>
       <c r="P11" s="12" t="n">
         <v>0</v>
@@ -1546,12 +1550,12 @@
     <row r="12">
       <c r="A12" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-35029</t>
+          <t>PDMDEP-35037</t>
         </is>
       </c>
       <c r="B12" s="14" t="inlineStr">
         <is>
-          <t>[VILLE DE LEVALLOIS PERRET] - Hébergement Litt Exp test et prod</t>
+          <t xml:space="preserve">[VILLE DE VILLEFRANCHE SUR SAONE ] - mise a jour carto comprise dans leur abonnement annuel </t>
         </is>
       </c>
       <c r="C12" s="14" t="inlineStr">
@@ -1561,12 +1565,12 @@
       </c>
       <c r="D12" s="14" t="inlineStr">
         <is>
-          <t>VILLE DE LEVALLOIS PERRET</t>
+          <t xml:space="preserve">VILLE DE VILLEFRANCHE SUR SAONE </t>
         </is>
       </c>
       <c r="E12" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hébergement Litt Exp </t>
+          <t xml:space="preserve">mise a jour carto comprise dans leur abonnement annuel </t>
         </is>
       </c>
       <c r="F12" s="14" t="inlineStr">
@@ -1576,7 +1580,7 @@
       </c>
       <c r="G12" s="14" t="inlineStr">
         <is>
-          <t>Commande sans prestation</t>
+          <t>Prestation offerte</t>
         </is>
       </c>
       <c r="H12" s="14" t="inlineStr">
@@ -1593,7 +1597,7 @@
         <v>1</v>
       </c>
       <c r="K12" s="14" t="n">
-        <v>5.5</v>
+        <v>1.75</v>
       </c>
       <c r="L12" s="14" t="inlineStr"/>
       <c r="M12" s="14" t="inlineStr"/>
@@ -1610,27 +1614,27 @@
     <row r="13">
       <c r="A13" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-34975</t>
+          <t>PDMDEP-35029</t>
         </is>
       </c>
       <c r="B13" s="11" t="inlineStr">
         <is>
-          <t>[VILLE DE SURESNES] - Migration Littéralis vers nouveau serveur+ montée de version Test et Prod</t>
+          <t>[VILLE DE LEVALLOIS PERRET] - Hébergement Litt Exp test et prod</t>
         </is>
       </c>
       <c r="C13" s="11" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D13" s="11" t="inlineStr">
         <is>
-          <t>VILLE DE SURESNES</t>
+          <t>VILLE DE LEVALLOIS PERRET</t>
         </is>
       </c>
       <c r="E13" s="11" t="inlineStr">
         <is>
-          <t>Migration Littéralis vers nouveau serveur+ montée de version Test et Prod</t>
+          <t xml:space="preserve">Hébergement Litt Exp </t>
         </is>
       </c>
       <c r="F13" s="11" t="inlineStr">
@@ -1640,7 +1644,7 @@
       </c>
       <c r="G13" s="11" t="inlineStr">
         <is>
-          <t>Projet</t>
+          <t>Commande sans prestation</t>
         </is>
       </c>
       <c r="H13" s="11" t="inlineStr">
@@ -1650,29 +1654,21 @@
       </c>
       <c r="I13" s="11" t="inlineStr">
         <is>
-          <t>06/08/2026</t>
+          <t>18/08/2026</t>
         </is>
       </c>
       <c r="J13" s="11" t="n">
         <v>1</v>
       </c>
       <c r="K13" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L13" s="11" t="inlineStr">
-        <is>
-          <t>PDMDEP-34979</t>
-        </is>
-      </c>
-      <c r="M13" s="11" t="inlineStr">
-        <is>
-          <t>00178226</t>
-        </is>
-      </c>
+        <v>5.5</v>
+      </c>
+      <c r="L13" s="11" t="inlineStr"/>
+      <c r="M13" s="11" t="inlineStr"/>
       <c r="N13" s="12" t="n">
-        <v>1100</v>
-      </c>
-      <c r="O13" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O13" s="12" t="n">
         <v>0</v>
       </c>
       <c r="P13" s="12" t="n">
@@ -1682,32 +1678,32 @@
     <row r="14">
       <c r="A14" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-34819</t>
+          <t>PDMDEP-34975</t>
         </is>
       </c>
       <c r="B14" s="14" t="inlineStr">
         <is>
-          <t>[Ville de Bourges] - Migration GEODP Placier et ODP</t>
+          <t>[VILLE DE SURESNES] - Migration Littéralis vers nouveau serveur+ montée de version Test et Prod</t>
         </is>
       </c>
       <c r="C14" s="14" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D14" s="14" t="inlineStr">
         <is>
-          <t>Ville de Bourges</t>
+          <t>VILLE DE SURESNES</t>
         </is>
       </c>
       <c r="E14" s="14" t="inlineStr">
         <is>
-          <t>Migration GEODP Placier et ODP</t>
+          <t>Migration Littéralis vers nouveau serveur+ montée de version Test et Prod</t>
         </is>
       </c>
       <c r="F14" s="14" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G14" s="14" t="inlineStr">
@@ -1717,35 +1713,35 @@
       </c>
       <c r="H14" s="14" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I14" s="14" t="inlineStr">
         <is>
-          <t>29/07/2026</t>
+          <t>06/08/2026</t>
         </is>
       </c>
       <c r="J14" s="14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K14" s="14" t="n">
         <v>0</v>
       </c>
       <c r="L14" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-34825</t>
+          <t>PDMDEP-34979</t>
         </is>
       </c>
       <c r="M14" s="14" t="inlineStr">
         <is>
-          <t>00177218</t>
+          <t>00178226</t>
         </is>
       </c>
       <c r="N14" s="15" t="n">
-        <v>2419</v>
+        <v>1100</v>
       </c>
       <c r="O14" s="16" t="n">
-        <v>120.95</v>
+        <v>0</v>
       </c>
       <c r="P14" s="15" t="n">
         <v>0</v>
@@ -1754,27 +1750,27 @@
     <row r="15">
       <c r="A15" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-34782</t>
+          <t>PDMDEP-34819</t>
         </is>
       </c>
       <c r="B15" s="11" t="inlineStr">
         <is>
-          <t>[MAIRIE DE SAINT-ISMIER] - Acquisition GEODP Placier</t>
+          <t>[Ville de Bourges] - Migration GEODP Placier et ODP</t>
         </is>
       </c>
       <c r="C15" s="11" t="inlineStr">
         <is>
-          <t>Estelle LEDUC</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D15" s="11" t="inlineStr">
         <is>
-          <t>MAIRIE DE SAINT-ISMIER</t>
+          <t>Ville de Bourges</t>
         </is>
       </c>
       <c r="E15" s="11" t="inlineStr">
         <is>
-          <t>GEODP PLACIER</t>
+          <t>Migration GEODP Placier et ODP</t>
         </is>
       </c>
       <c r="F15" s="11" t="inlineStr">
@@ -1789,7 +1785,7 @@
       </c>
       <c r="H15" s="11" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I15" s="11" t="inlineStr">
@@ -1801,52 +1797,52 @@
         <v>2</v>
       </c>
       <c r="K15" s="11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L15" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-34791</t>
+          <t>PDMDEP-34825</t>
         </is>
       </c>
       <c r="M15" s="11" t="inlineStr">
         <is>
-          <t>00177122</t>
+          <t>00177218</t>
         </is>
       </c>
       <c r="N15" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O15" s="12" t="n">
-        <v>643.95</v>
+        <v>2419</v>
+      </c>
+      <c r="O15" s="16" t="n">
+        <v>120.95</v>
       </c>
       <c r="P15" s="12" t="n">
-        <v>321.98</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-34761</t>
+          <t>PDMDEP-34782</t>
         </is>
       </c>
       <c r="B16" s="14" t="inlineStr">
         <is>
-          <t>[COMMUNE DU PUY EN VELAY] - Migration GeODP Placier + migration ODP</t>
+          <t>[MAIRIE DE SAINT-ISMIER] - Acquisition GEODP Placier</t>
         </is>
       </c>
       <c r="C16" s="14" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Estelle LEDUC</t>
         </is>
       </c>
       <c r="D16" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DU PUY EN VELAY</t>
+          <t>MAIRIE DE SAINT-ISMIER</t>
         </is>
       </c>
       <c r="E16" s="14" t="inlineStr">
         <is>
-          <t>Migration GeODP Placier + migration ODP</t>
+          <t>GEODP PLACIER</t>
         </is>
       </c>
       <c r="F16" s="14" t="inlineStr">
@@ -1861,69 +1857,69 @@
       </c>
       <c r="H16" s="14" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I16" s="14" t="inlineStr">
         <is>
-          <t>28/07/2026</t>
+          <t>29/07/2026</t>
         </is>
       </c>
       <c r="J16" s="14" t="n">
         <v>2</v>
       </c>
       <c r="K16" s="14" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L16" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-34768</t>
+          <t>PDMDEP-34791</t>
         </is>
       </c>
       <c r="M16" s="14" t="inlineStr">
         <is>
-          <t>00177029</t>
+          <t>00177122</t>
         </is>
       </c>
       <c r="N16" s="15" t="n">
         <v>0</v>
       </c>
       <c r="O16" s="15" t="n">
-        <v>726.05</v>
+        <v>643.95</v>
       </c>
       <c r="P16" s="15" t="n">
-        <v>0</v>
+        <v>321.98</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-34718</t>
+          <t>PDMDEP-34761</t>
         </is>
       </c>
       <c r="B17" s="11" t="inlineStr">
         <is>
-          <t>[VILLE DE VILLEURBANNE] - Crédits d'heure (14h)</t>
+          <t>[COMMUNE DU PUY EN VELAY] - Migration GeODP Placier + migration ODP</t>
         </is>
       </c>
       <c r="C17" s="11" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D17" s="11" t="inlineStr">
         <is>
-          <t>VILLE DE VILLEURBANNE</t>
+          <t>COMMUNE DU PUY EN VELAY</t>
         </is>
       </c>
       <c r="E17" s="11" t="inlineStr">
         <is>
-          <t>Crédits d'heure (14h)</t>
+          <t>Migration GeODP Placier + migration ODP</t>
         </is>
       </c>
       <c r="F17" s="11" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G17" s="11" t="inlineStr">
@@ -1933,49 +1929,49 @@
       </c>
       <c r="H17" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I17" s="11" t="inlineStr">
         <is>
-          <t>24/07/2026</t>
+          <t>28/07/2026</t>
         </is>
       </c>
       <c r="J17" s="11" t="n">
         <v>2</v>
       </c>
       <c r="K17" s="11" t="n">
-        <v>2.92</v>
+        <v>0</v>
       </c>
       <c r="L17" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-34722</t>
+          <t>PDMDEP-34768</t>
         </is>
       </c>
       <c r="M17" s="11" t="inlineStr">
         <is>
-          <t>00176875</t>
+          <t>00177029</t>
         </is>
       </c>
       <c r="N17" s="12" t="n">
-        <v>1260</v>
-      </c>
-      <c r="O17" s="16" t="n">
-        <v>728</v>
+        <v>0</v>
+      </c>
+      <c r="O17" s="12" t="n">
+        <v>726.05</v>
       </c>
       <c r="P17" s="12" t="n">
-        <v>249.6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-34650</t>
+          <t>PDMDEP-34718</t>
         </is>
       </c>
       <c r="B18" s="14" t="inlineStr">
         <is>
-          <t>[CD 01] -  Transfert de compétence Montée de version</t>
+          <t>[VILLE DE VILLEURBANNE] - Crédits d'heure (14h)</t>
         </is>
       </c>
       <c r="C18" s="14" t="inlineStr">
@@ -1985,12 +1981,12 @@
       </c>
       <c r="D18" s="14" t="inlineStr">
         <is>
-          <t>DEPARTEMENT DE L AIN (CD 01)</t>
+          <t>VILLE DE VILLEURBANNE</t>
         </is>
       </c>
       <c r="E18" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Transfert de compétence Montée de version</t>
+          <t>Crédits d'heure (14h)</t>
         </is>
       </c>
       <c r="F18" s="14" t="inlineStr">
@@ -2010,44 +2006,44 @@
       </c>
       <c r="I18" s="14" t="inlineStr">
         <is>
-          <t>21/07/2026</t>
+          <t>24/07/2026</t>
         </is>
       </c>
       <c r="J18" s="14" t="n">
         <v>2</v>
       </c>
       <c r="K18" s="14" t="n">
-        <v>1.25</v>
+        <v>2.92</v>
       </c>
       <c r="L18" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-34654</t>
+          <t>PDMDEP-34722</t>
         </is>
       </c>
       <c r="M18" s="14" t="inlineStr">
         <is>
-          <t>00176582</t>
+          <t>00176875</t>
         </is>
       </c>
       <c r="N18" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O18" s="15" t="n">
-        <v>0</v>
+        <v>1260</v>
+      </c>
+      <c r="O18" s="16" t="n">
+        <v>728</v>
       </c>
       <c r="P18" s="15" t="n">
-        <v>0</v>
+        <v>249.6</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-34495</t>
+          <t>PDMDEP-34650</t>
         </is>
       </c>
       <c r="B19" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">[COMMUNE DE CLICHY] - PRESTATION DE MODELISATION + integration RODP </t>
+          <t>[CD 01] -  Transfert de compétence Montée de version</t>
         </is>
       </c>
       <c r="C19" s="11" t="inlineStr">
@@ -2057,12 +2053,12 @@
       </c>
       <c r="D19" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE CLICHY</t>
+          <t>DEPARTEMENT DE L AIN (CD 01)</t>
         </is>
       </c>
       <c r="E19" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">PRESTATION DE MODELISATION + integration RODP </t>
+          <t xml:space="preserve"> Transfert de compétence Montée de version</t>
         </is>
       </c>
       <c r="F19" s="11" t="inlineStr">
@@ -2082,64 +2078,64 @@
       </c>
       <c r="I19" s="11" t="inlineStr">
         <is>
-          <t>07/07/2026</t>
+          <t>21/07/2026</t>
         </is>
       </c>
       <c r="J19" s="11" t="n">
         <v>2</v>
       </c>
       <c r="K19" s="11" t="n">
-        <v>3.5</v>
+        <v>1.25</v>
       </c>
       <c r="L19" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-34499</t>
+          <t>PDMDEP-34654</t>
         </is>
       </c>
       <c r="M19" s="11" t="inlineStr">
         <is>
-          <t>00172678</t>
+          <t>00176582</t>
         </is>
       </c>
       <c r="N19" s="12" t="n">
         <v>0</v>
       </c>
       <c r="O19" s="12" t="n">
-        <v>43</v>
+        <v>0</v>
       </c>
       <c r="P19" s="12" t="n">
-        <v>12.29</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-34475</t>
+          <t>PDMDEP-34495</t>
         </is>
       </c>
       <c r="B20" s="14" t="inlineStr">
         <is>
-          <t>[Mairie de Pontcharra] - Migration simple placier</t>
+          <t xml:space="preserve">[COMMUNE DE CLICHY] - PRESTATION DE MODELISATION + integration RODP </t>
         </is>
       </c>
       <c r="C20" s="14" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D20" s="14" t="inlineStr">
         <is>
-          <t>Mairie de Pontcharra</t>
+          <t>COMMUNE DE CLICHY</t>
         </is>
       </c>
       <c r="E20" s="14" t="inlineStr">
         <is>
-          <t>Migration simple placier</t>
+          <t xml:space="preserve">PRESTATION DE MODELISATION + integration RODP </t>
         </is>
       </c>
       <c r="F20" s="14" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G20" s="14" t="inlineStr">
@@ -2149,49 +2145,49 @@
       </c>
       <c r="H20" s="14" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I20" s="14" t="inlineStr">
         <is>
-          <t>06/07/2026</t>
+          <t>07/07/2026</t>
         </is>
       </c>
       <c r="J20" s="14" t="n">
         <v>2</v>
       </c>
       <c r="K20" s="14" t="n">
-        <v>1.5</v>
+        <v>3.5</v>
       </c>
       <c r="L20" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-34481</t>
+          <t>PDMDEP-34499</t>
         </is>
       </c>
       <c r="M20" s="14" t="inlineStr">
         <is>
-          <t>00172611</t>
+          <t>00172678</t>
         </is>
       </c>
       <c r="N20" s="15" t="n">
         <v>0</v>
       </c>
       <c r="O20" s="15" t="n">
-        <v>105</v>
+        <v>43</v>
       </c>
       <c r="P20" s="15" t="n">
-        <v>70</v>
+        <v>12.29</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-34411</t>
+          <t>PDMDEP-34475</t>
         </is>
       </c>
       <c r="B21" s="11" t="inlineStr">
         <is>
-          <t>[MAIRIE DE MAIZIERES LES METZ] - Migration GEODP 1 vers GEODP 2 (Placier)</t>
+          <t>[Mairie de Pontcharra] - Migration simple placier</t>
         </is>
       </c>
       <c r="C21" s="11" t="inlineStr">
@@ -2201,12 +2197,12 @@
       </c>
       <c r="D21" s="11" t="inlineStr">
         <is>
-          <t>MAIRIE DE MAIZIERES LES METZ</t>
+          <t>Mairie de Pontcharra</t>
         </is>
       </c>
       <c r="E21" s="11" t="inlineStr">
         <is>
-          <t>Migration GEODP 1 vers GEODP 2 (Placier)</t>
+          <t>Migration simple placier</t>
         </is>
       </c>
       <c r="F21" s="11" t="inlineStr">
@@ -2226,44 +2222,44 @@
       </c>
       <c r="I21" s="11" t="inlineStr">
         <is>
-          <t>02/07/2026</t>
+          <t>06/07/2026</t>
         </is>
       </c>
       <c r="J21" s="11" t="n">
         <v>2</v>
       </c>
       <c r="K21" s="11" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="L21" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-34420</t>
+          <t>PDMDEP-34481</t>
         </is>
       </c>
       <c r="M21" s="11" t="inlineStr">
         <is>
-          <t>00172317</t>
+          <t>00172611</t>
         </is>
       </c>
       <c r="N21" s="12" t="n">
         <v>0</v>
       </c>
       <c r="O21" s="12" t="n">
-        <v>0</v>
+        <v>105</v>
       </c>
       <c r="P21" s="12" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-34319</t>
+          <t>PDMDEP-34411</t>
         </is>
       </c>
       <c r="B22" s="14" t="inlineStr">
         <is>
-          <t>[Commune de Mouscron (BE)] - Migration GEODP Placier</t>
+          <t>[MAIRIE DE MAIZIERES LES METZ] - Migration GEODP 1 vers GEODP 2 (Placier)</t>
         </is>
       </c>
       <c r="C22" s="14" t="inlineStr">
@@ -2273,12 +2269,12 @@
       </c>
       <c r="D22" s="14" t="inlineStr">
         <is>
-          <t>Commune de Mouscron (BE)</t>
+          <t>MAIRIE DE MAIZIERES LES METZ</t>
         </is>
       </c>
       <c r="E22" s="14" t="inlineStr">
         <is>
-          <t>Migration GEODP Placier</t>
+          <t>Migration GEODP 1 vers GEODP 2 (Placier)</t>
         </is>
       </c>
       <c r="F22" s="14" t="inlineStr">
@@ -2298,29 +2294,29 @@
       </c>
       <c r="I22" s="14" t="inlineStr">
         <is>
-          <t>30/06/2026</t>
+          <t>02/07/2026</t>
         </is>
       </c>
       <c r="J22" s="14" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K22" s="14" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="L22" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-34326</t>
+          <t>PDMDEP-34420</t>
         </is>
       </c>
       <c r="M22" s="14" t="inlineStr">
         <is>
-          <t>00171691</t>
+          <t>00172317</t>
         </is>
       </c>
       <c r="N22" s="15" t="n">
-        <v>769.5</v>
-      </c>
-      <c r="O22" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O22" s="15" t="n">
         <v>0</v>
       </c>
       <c r="P22" s="15" t="n">
@@ -2330,27 +2326,27 @@
     <row r="23">
       <c r="A23" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-34287</t>
+          <t>PDMDEP-34319</t>
         </is>
       </c>
       <c r="B23" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">[COMMUNE DE LUNEL] - Migration GeODP </t>
+          <t>[Commune de Mouscron (BE)] - Migration GEODP Placier</t>
         </is>
       </c>
       <c r="C23" s="11" t="inlineStr">
         <is>
-          <t>Estelle LEDUC</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D23" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE LUNEL</t>
+          <t>Commune de Mouscron (BE)</t>
         </is>
       </c>
       <c r="E23" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Migration GeODP </t>
+          <t>Migration GEODP Placier</t>
         </is>
       </c>
       <c r="F23" s="11" t="inlineStr">
@@ -2360,7 +2356,7 @@
       </c>
       <c r="G23" s="11" t="inlineStr">
         <is>
-          <t>Prestation offerte</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H23" s="11" t="inlineStr">
@@ -2370,21 +2366,29 @@
       </c>
       <c r="I23" s="11" t="inlineStr">
         <is>
-          <t>29/06/2026</t>
+          <t>30/06/2026</t>
         </is>
       </c>
       <c r="J23" s="11" t="n">
         <v>3</v>
       </c>
       <c r="K23" s="11" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="L23" s="11" t="inlineStr"/>
-      <c r="M23" s="11" t="inlineStr"/>
+        <v>0.5</v>
+      </c>
+      <c r="L23" s="11" t="inlineStr">
+        <is>
+          <t>PDMDEP-34326</t>
+        </is>
+      </c>
+      <c r="M23" s="11" t="inlineStr">
+        <is>
+          <t>00171691</t>
+        </is>
+      </c>
       <c r="N23" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O23" s="12" t="n">
+        <v>769.5</v>
+      </c>
+      <c r="O23" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P23" s="12" t="n">
@@ -2394,27 +2398,27 @@
     <row r="24">
       <c r="A24" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-34249</t>
+          <t>PDMDEP-34287</t>
         </is>
       </c>
       <c r="B24" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">[COMMUNE DE VIENNE] - Migration Placier et ODP </t>
+          <t xml:space="preserve">[COMMUNE DE LUNEL] - Migration GeODP </t>
         </is>
       </c>
       <c r="C24" s="14" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Estelle LEDUC</t>
         </is>
       </c>
       <c r="D24" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE VIENNE</t>
+          <t>COMMUNE DE LUNEL</t>
         </is>
       </c>
       <c r="E24" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Migration Placier et ODP </t>
+          <t xml:space="preserve">Migration GeODP </t>
         </is>
       </c>
       <c r="F24" s="14" t="inlineStr">
@@ -2424,7 +2428,7 @@
       </c>
       <c r="G24" s="14" t="inlineStr">
         <is>
-          <t>Projet</t>
+          <t>Prestation offerte</t>
         </is>
       </c>
       <c r="H24" s="14" t="inlineStr">
@@ -2441,22 +2445,14 @@
         <v>3</v>
       </c>
       <c r="K24" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="L24" s="14" t="inlineStr">
-        <is>
-          <t>PDMDEP-34258</t>
-        </is>
-      </c>
-      <c r="M24" s="14" t="inlineStr">
-        <is>
-          <t>00171361</t>
-        </is>
-      </c>
+        <v>2.5</v>
+      </c>
+      <c r="L24" s="14" t="inlineStr"/>
+      <c r="M24" s="14" t="inlineStr"/>
       <c r="N24" s="15" t="n">
-        <v>2127.2</v>
-      </c>
-      <c r="O24" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O24" s="15" t="n">
         <v>0</v>
       </c>
       <c r="P24" s="15" t="n">
@@ -2466,32 +2462,32 @@
     <row r="25">
       <c r="A25" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-34229</t>
+          <t>PDMDEP-34249</t>
         </is>
       </c>
       <c r="B25" s="11" t="inlineStr">
         <is>
-          <t>[DIJON METROPOLE] - GRC + Connecteur</t>
+          <t xml:space="preserve">[COMMUNE DE VIENNE] - Migration Placier et ODP </t>
         </is>
       </c>
       <c r="C25" s="11" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D25" s="11" t="inlineStr">
         <is>
-          <t>DIJON METROPOLE</t>
+          <t>COMMUNE DE VIENNE</t>
         </is>
       </c>
       <c r="E25" s="11" t="inlineStr">
         <is>
-          <t>GRC + Connecteur</t>
+          <t xml:space="preserve">Migration Placier et ODP </t>
         </is>
       </c>
       <c r="F25" s="11" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G25" s="11" t="inlineStr">
@@ -2501,69 +2497,69 @@
       </c>
       <c r="H25" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I25" s="11" t="inlineStr">
         <is>
-          <t>26/06/2026</t>
+          <t>29/06/2026</t>
         </is>
       </c>
       <c r="J25" s="11" t="n">
         <v>3</v>
       </c>
       <c r="K25" s="11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L25" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-34235</t>
+          <t>PDMDEP-34258</t>
         </is>
       </c>
       <c r="M25" s="11" t="inlineStr">
         <is>
-          <t>00171333</t>
+          <t>00171361</t>
         </is>
       </c>
       <c r="N25" s="12" t="n">
-        <v>4536</v>
+        <v>2127.2</v>
       </c>
       <c r="O25" s="16" t="n">
-        <v>72</v>
+        <v>0</v>
       </c>
       <c r="P25" s="12" t="n">
-        <v>72</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-34208</t>
+          <t>PDMDEP-34229</t>
         </is>
       </c>
       <c r="B26" s="14" t="inlineStr">
         <is>
-          <t>[COMMUNE DE CHATEAUGIRON] - Migration GEODP Placier 2</t>
+          <t>[DIJON METROPOLE] - GRC + Connecteur</t>
         </is>
       </c>
       <c r="C26" s="14" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D26" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE CHATEAUGIRON</t>
+          <t>DIJON METROPOLE</t>
         </is>
       </c>
       <c r="E26" s="14" t="inlineStr">
         <is>
-          <t>Migration GEODP Placier 2</t>
+          <t>GRC + Connecteur</t>
         </is>
       </c>
       <c r="F26" s="14" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G26" s="14" t="inlineStr">
@@ -2573,49 +2569,49 @@
       </c>
       <c r="H26" s="14" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I26" s="14" t="inlineStr">
         <is>
-          <t>25/06/2026</t>
+          <t>26/06/2026</t>
         </is>
       </c>
       <c r="J26" s="14" t="n">
         <v>3</v>
       </c>
       <c r="K26" s="14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L26" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-34216</t>
+          <t>PDMDEP-34235</t>
         </is>
       </c>
       <c r="M26" s="14" t="inlineStr">
         <is>
-          <t>00171155</t>
+          <t>00171333</t>
         </is>
       </c>
       <c r="N26" s="15" t="n">
-        <v>525</v>
+        <v>4536</v>
       </c>
       <c r="O26" s="16" t="n">
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="P26" s="15" t="n">
-        <v>0</v>
+        <v>72</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-34192</t>
+          <t>PDMDEP-34208</t>
         </is>
       </c>
       <c r="B27" s="11" t="inlineStr">
         <is>
-          <t>[Commune de Macon ] - GEODP Placier</t>
+          <t>[COMMUNE DE CHATEAUGIRON] - Migration GEODP Placier 2</t>
         </is>
       </c>
       <c r="C27" s="11" t="inlineStr">
@@ -2625,12 +2621,12 @@
       </c>
       <c r="D27" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Commune de Macon </t>
+          <t>COMMUNE DE CHATEAUGIRON</t>
         </is>
       </c>
       <c r="E27" s="11" t="inlineStr">
         <is>
-          <t>GEODP Placier</t>
+          <t>Migration GEODP Placier 2</t>
         </is>
       </c>
       <c r="F27" s="11" t="inlineStr">
@@ -2645,7 +2641,7 @@
       </c>
       <c r="H27" s="11" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I27" s="11" t="inlineStr">
@@ -2657,52 +2653,52 @@
         <v>3</v>
       </c>
       <c r="K27" s="11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L27" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-34201</t>
+          <t>PDMDEP-34216</t>
         </is>
       </c>
       <c r="M27" s="11" t="inlineStr">
         <is>
-          <t>00171162</t>
+          <t>00171155</t>
         </is>
       </c>
       <c r="N27" s="12" t="n">
-        <v>1662</v>
+        <v>525</v>
       </c>
       <c r="O27" s="16" t="n">
-        <v>277</v>
+        <v>0</v>
       </c>
       <c r="P27" s="12" t="n">
-        <v>277</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-34169</t>
+          <t>PDMDEP-34192</t>
         </is>
       </c>
       <c r="B28" s="14" t="inlineStr">
         <is>
-          <t>[COMMUNAUTE URBAINE ANGERS LOIRE METROPOLE] - Migration GEODP 1 vers GEODP 2</t>
+          <t>[Commune de Macon ] - GEODP Placier</t>
         </is>
       </c>
       <c r="C28" s="14" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D28" s="14" t="inlineStr">
         <is>
-          <t>COMMUNAUTE URBAINE ANGERS LOIRE METROPOLE</t>
+          <t xml:space="preserve">Commune de Macon </t>
         </is>
       </c>
       <c r="E28" s="14" t="inlineStr">
         <is>
-          <t>Migration GEODP 1 vers GEODP 2</t>
+          <t>GEODP Placier</t>
         </is>
       </c>
       <c r="F28" s="14" t="inlineStr">
@@ -2717,69 +2713,69 @@
       </c>
       <c r="H28" s="14" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I28" s="14" t="inlineStr">
         <is>
-          <t>24/06/2026</t>
+          <t>25/06/2026</t>
         </is>
       </c>
       <c r="J28" s="14" t="n">
         <v>3</v>
       </c>
       <c r="K28" s="14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L28" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-34227</t>
+          <t>PDMDEP-34201</t>
         </is>
       </c>
       <c r="M28" s="14" t="inlineStr">
         <is>
-          <t>2026-0210095</t>
+          <t>00171162</t>
         </is>
       </c>
       <c r="N28" s="15" t="n">
-        <v>9623.1</v>
+        <v>1662</v>
       </c>
       <c r="O28" s="16" t="n">
-        <v>3849.24</v>
+        <v>277</v>
       </c>
       <c r="P28" s="15" t="n">
-        <v>0</v>
+        <v>277</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-34126</t>
+          <t>PDMDEP-34169</t>
         </is>
       </c>
       <c r="B29" s="11" t="inlineStr">
         <is>
-          <t>[SETE] - AME LiEx</t>
+          <t>[COMMUNAUTE URBAINE ANGERS LOIRE METROPOLE] - Migration GEODP 1 vers GEODP 2</t>
         </is>
       </c>
       <c r="C29" s="11" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D29" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE SETE</t>
+          <t>COMMUNAUTE URBAINE ANGERS LOIRE METROPOLE</t>
         </is>
       </c>
       <c r="E29" s="11" t="inlineStr">
         <is>
-          <t>AME LiEx</t>
+          <t>Migration GEODP 1 vers GEODP 2</t>
         </is>
       </c>
       <c r="F29" s="11" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G29" s="11" t="inlineStr">
@@ -2789,35 +2785,35 @@
       </c>
       <c r="H29" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I29" s="11" t="inlineStr">
         <is>
-          <t>23/06/2026</t>
+          <t>24/06/2026</t>
         </is>
       </c>
       <c r="J29" s="11" t="n">
         <v>3</v>
       </c>
       <c r="K29" s="11" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="L29" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-34130</t>
+          <t>PDMDEP-34227</t>
         </is>
       </c>
       <c r="M29" s="11" t="inlineStr">
         <is>
-          <t>00170928</t>
+          <t>2026-0210095</t>
         </is>
       </c>
       <c r="N29" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O29" s="12" t="n">
-        <v>0</v>
+        <v>9623.1</v>
+      </c>
+      <c r="O29" s="16" t="n">
+        <v>3849.24</v>
       </c>
       <c r="P29" s="12" t="n">
         <v>0</v>
@@ -2826,32 +2822,32 @@
     <row r="30">
       <c r="A30" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-34108</t>
+          <t>PDMDEP-34126</t>
         </is>
       </c>
       <c r="B30" s="14" t="inlineStr">
         <is>
-          <t>[COMMUNE DU PUY EN VELAY] - Migration GeODP Placier + migration ODP</t>
+          <t>[SETE] - AME LiEx</t>
         </is>
       </c>
       <c r="C30" s="14" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D30" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DU PUY EN VELAY</t>
+          <t>COMMUNE DE SETE</t>
         </is>
       </c>
       <c r="E30" s="14" t="inlineStr">
         <is>
-          <t>Migration GeODP Placier + migration ODP</t>
+          <t>AME LiEx</t>
         </is>
       </c>
       <c r="F30" s="14" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G30" s="14" t="inlineStr">
@@ -2861,7 +2857,7 @@
       </c>
       <c r="H30" s="14" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I30" s="14" t="inlineStr">
@@ -2873,22 +2869,22 @@
         <v>3</v>
       </c>
       <c r="K30" s="14" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="L30" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-34117</t>
+          <t>PDMDEP-34130</t>
         </is>
       </c>
       <c r="M30" s="14" t="inlineStr">
         <is>
-          <t>00170907</t>
+          <t>00170928</t>
         </is>
       </c>
       <c r="N30" s="15" t="n">
-        <v>707</v>
-      </c>
-      <c r="O30" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O30" s="15" t="n">
         <v>0</v>
       </c>
       <c r="P30" s="15" t="n">
@@ -2898,27 +2894,27 @@
     <row r="31">
       <c r="A31" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-34081</t>
+          <t>PDMDEP-34108</t>
         </is>
       </c>
       <c r="B31" s="11" t="inlineStr">
         <is>
-          <t>[COMMUNE DE ERQUY] - Migration GEODP Placier + Pax</t>
+          <t>[COMMUNE DU PUY EN VELAY] - Migration GeODP Placier + migration ODP</t>
         </is>
       </c>
       <c r="C31" s="11" t="inlineStr">
         <is>
-          <t>Estelle LEDUC</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D31" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE ERQUY</t>
+          <t>COMMUNE DU PUY EN VELAY</t>
         </is>
       </c>
       <c r="E31" s="11" t="inlineStr">
         <is>
-          <t>Migration GEODP 2 + Pax</t>
+          <t>Migration GeODP Placier + migration ODP</t>
         </is>
       </c>
       <c r="F31" s="11" t="inlineStr">
@@ -2938,7 +2934,7 @@
       </c>
       <c r="I31" s="11" t="inlineStr">
         <is>
-          <t>22/06/2026</t>
+          <t>23/06/2026</t>
         </is>
       </c>
       <c r="J31" s="11" t="n">
@@ -2949,19 +2945,19 @@
       </c>
       <c r="L31" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-34090</t>
+          <t>PDMDEP-34117</t>
         </is>
       </c>
       <c r="M31" s="11" t="inlineStr">
         <is>
-          <t>00170724</t>
+          <t>00170907</t>
         </is>
       </c>
       <c r="N31" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O31" s="12" t="n">
-        <v>177.5</v>
+        <v>707</v>
+      </c>
+      <c r="O31" s="16" t="n">
+        <v>0</v>
       </c>
       <c r="P31" s="12" t="n">
         <v>0</v>
@@ -2970,27 +2966,27 @@
     <row r="32">
       <c r="A32" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-34064</t>
+          <t>PDMDEP-34081</t>
         </is>
       </c>
       <c r="B32" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">[VILLE DE VANNES] - ORMC pour GEODP PLACIER </t>
+          <t>[COMMUNE DE ERQUY] - Migration GEODP Placier + Pax</t>
         </is>
       </c>
       <c r="C32" s="14" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Estelle LEDUC</t>
         </is>
       </c>
       <c r="D32" s="14" t="inlineStr">
         <is>
-          <t>VILLE DE VANNES</t>
+          <t>COMMUNE DE ERQUY</t>
         </is>
       </c>
       <c r="E32" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">ORMC pour GEODP PLACIER </t>
+          <t>Migration GEODP 2 + Pax</t>
         </is>
       </c>
       <c r="F32" s="14" t="inlineStr">
@@ -3005,12 +3001,12 @@
       </c>
       <c r="H32" s="14" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I32" s="14" t="inlineStr">
         <is>
-          <t>19/06/2026</t>
+          <t>22/06/2026</t>
         </is>
       </c>
       <c r="J32" s="14" t="n">
@@ -3021,19 +3017,19 @@
       </c>
       <c r="L32" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-34070</t>
+          <t>PDMDEP-34090</t>
         </is>
       </c>
       <c r="M32" s="14" t="inlineStr">
         <is>
-          <t>00170468</t>
+          <t>00170724</t>
         </is>
       </c>
       <c r="N32" s="15" t="n">
-        <v>300</v>
-      </c>
-      <c r="O32" s="16" t="n">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="O32" s="15" t="n">
+        <v>177.5</v>
       </c>
       <c r="P32" s="15" t="n">
         <v>0</v>
@@ -3042,27 +3038,27 @@
     <row r="33">
       <c r="A33" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-33985</t>
+          <t>PDMDEP-34064</t>
         </is>
       </c>
       <c r="B33" s="11" t="inlineStr">
         <is>
-          <t>[COMMUNE DE QUIMPERLE] - Migration GEODP 1 vers GEODP 2 (Placier)</t>
+          <t xml:space="preserve">[VILLE DE VANNES] - ORMC pour GEODP PLACIER </t>
         </is>
       </c>
       <c r="C33" s="11" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D33" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE QUIMPERLE</t>
+          <t>VILLE DE VANNES</t>
         </is>
       </c>
       <c r="E33" s="11" t="inlineStr">
         <is>
-          <t>Migration GEODP 1 vers GEODP 2 (Placier)</t>
+          <t xml:space="preserve">ORMC pour GEODP PLACIER </t>
         </is>
       </c>
       <c r="F33" s="11" t="inlineStr">
@@ -3077,32 +3073,32 @@
       </c>
       <c r="H33" s="11" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I33" s="11" t="inlineStr">
         <is>
-          <t>17/06/2026</t>
+          <t>19/06/2026</t>
         </is>
       </c>
       <c r="J33" s="11" t="n">
         <v>3</v>
       </c>
       <c r="K33" s="11" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="L33" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-33991</t>
+          <t>PDMDEP-34070</t>
         </is>
       </c>
       <c r="M33" s="11" t="inlineStr">
         <is>
-          <t>00170408</t>
+          <t>00170468</t>
         </is>
       </c>
       <c r="N33" s="12" t="n">
-        <v>510</v>
+        <v>300</v>
       </c>
       <c r="O33" s="16" t="n">
         <v>0</v>
@@ -3114,32 +3110,32 @@
     <row r="34">
       <c r="A34" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-33949</t>
+          <t>PDMDEP-33985</t>
         </is>
       </c>
       <c r="B34" s="14" t="inlineStr">
         <is>
-          <t>[Commune de Colmar] - Modélisation Littéralis Expert et Démarrage Prod</t>
+          <t>[COMMUNE DE QUIMPERLE] - Migration GEODP 1 vers GEODP 2 (Placier)</t>
         </is>
       </c>
       <c r="C34" s="14" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D34" s="14" t="inlineStr">
         <is>
-          <t>Commune de Colmar</t>
+          <t>COMMUNE DE QUIMPERLE</t>
         </is>
       </c>
       <c r="E34" s="14" t="inlineStr">
         <is>
-          <t>Modélisation Littéralis Expert</t>
+          <t>Migration GEODP 1 vers GEODP 2 (Placier)</t>
         </is>
       </c>
       <c r="F34" s="14" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G34" s="14" t="inlineStr">
@@ -3149,64 +3145,64 @@
       </c>
       <c r="H34" s="14" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I34" s="14" t="inlineStr">
         <is>
-          <t>16/06/2026</t>
+          <t>17/06/2026</t>
         </is>
       </c>
       <c r="J34" s="14" t="n">
         <v>3</v>
       </c>
       <c r="K34" s="14" t="n">
-        <v>2</v>
+        <v>0.5</v>
       </c>
       <c r="L34" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-33955</t>
+          <t>PDMDEP-33991</t>
         </is>
       </c>
       <c r="M34" s="14" t="inlineStr">
         <is>
-          <t>00170302</t>
+          <t>00170408</t>
         </is>
       </c>
       <c r="N34" s="15" t="n">
-        <v>242.9</v>
-      </c>
-      <c r="O34" s="15" t="n">
-        <v>1242.9</v>
+        <v>510</v>
+      </c>
+      <c r="O34" s="16" t="n">
+        <v>0</v>
       </c>
       <c r="P34" s="15" t="n">
-        <v>621.45</v>
+        <v>0</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-33940</t>
+          <t>PDMDEP-33949</t>
         </is>
       </c>
       <c r="B35" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">[Commune de Thionville] - AME </t>
+          <t>[Commune de Colmar] - Modélisation Littéralis Expert et Démarrage Prod</t>
         </is>
       </c>
       <c r="C35" s="11" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D35" s="11" t="inlineStr">
         <is>
-          <t>Commune de Thionville</t>
+          <t>Commune de Colmar</t>
         </is>
       </c>
       <c r="E35" s="11" t="inlineStr">
         <is>
-          <t>AME Littéralis Expert</t>
+          <t>Modélisation Littéralis Expert</t>
         </is>
       </c>
       <c r="F35" s="11" t="inlineStr">
@@ -3233,37 +3229,37 @@
         <v>3</v>
       </c>
       <c r="K35" s="11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L35" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-33944</t>
+          <t>PDMDEP-33955</t>
         </is>
       </c>
       <c r="M35" s="11" t="inlineStr">
         <is>
-          <t>00170299</t>
+          <t>00170302</t>
         </is>
       </c>
       <c r="N35" s="12" t="n">
-        <v>220</v>
-      </c>
-      <c r="O35" s="16" t="n">
-        <v>0</v>
+        <v>242.9</v>
+      </c>
+      <c r="O35" s="12" t="n">
+        <v>1242.9</v>
       </c>
       <c r="P35" s="12" t="n">
-        <v>0</v>
+        <v>621.45</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-33813</t>
+          <t>PDMDEP-33940</t>
         </is>
       </c>
       <c r="B36" s="14" t="inlineStr">
         <is>
-          <t>[METROPOLE TOULON-PROVENCE-MEDITERRANEE] - Modélisation Seyne S/ Mer</t>
+          <t xml:space="preserve">[Commune de Thionville] - AME </t>
         </is>
       </c>
       <c r="C36" s="14" t="inlineStr">
@@ -3273,12 +3269,12 @@
       </c>
       <c r="D36" s="14" t="inlineStr">
         <is>
-          <t>METROPOLE TOULON-PROVENCE-MEDITERRANEE</t>
+          <t>Commune de Thionville</t>
         </is>
       </c>
       <c r="E36" s="14" t="inlineStr">
         <is>
-          <t>Modélisation Seyne S/ Mer</t>
+          <t>AME Littéralis Expert</t>
         </is>
       </c>
       <c r="F36" s="14" t="inlineStr">
@@ -3298,44 +3294,44 @@
       </c>
       <c r="I36" s="14" t="inlineStr">
         <is>
-          <t>11/06/2026</t>
+          <t>16/06/2026</t>
         </is>
       </c>
       <c r="J36" s="14" t="n">
         <v>3</v>
       </c>
       <c r="K36" s="14" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="L36" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-33817</t>
+          <t>PDMDEP-33944</t>
         </is>
       </c>
       <c r="M36" s="14" t="inlineStr">
         <is>
-          <t>00169865</t>
+          <t>00170299</t>
         </is>
       </c>
       <c r="N36" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O36" s="15" t="n">
-        <v>65.73</v>
+        <v>220</v>
+      </c>
+      <c r="O36" s="16" t="n">
+        <v>0</v>
       </c>
       <c r="P36" s="15" t="n">
-        <v>52.58</v>
+        <v>0</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-33804</t>
+          <t>PDMDEP-33813</t>
         </is>
       </c>
       <c r="B37" s="11" t="inlineStr">
         <is>
-          <t>[CD 73)] - Purge arrêtés temporaires</t>
+          <t>[METROPOLE TOULON-PROVENCE-MEDITERRANEE] - Modélisation Seyne S/ Mer</t>
         </is>
       </c>
       <c r="C37" s="11" t="inlineStr">
@@ -3345,12 +3341,12 @@
       </c>
       <c r="D37" s="11" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DE LA SAVOIE (CD 73)</t>
+          <t>METROPOLE TOULON-PROVENCE-MEDITERRANEE</t>
         </is>
       </c>
       <c r="E37" s="11" t="inlineStr">
         <is>
-          <t>Purge arrêtés temporaires</t>
+          <t>Modélisation Seyne S/ Mer</t>
         </is>
       </c>
       <c r="F37" s="11" t="inlineStr">
@@ -3377,52 +3373,52 @@
         <v>3</v>
       </c>
       <c r="K37" s="11" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="L37" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-33808</t>
+          <t>PDMDEP-33817</t>
         </is>
       </c>
       <c r="M37" s="11" t="inlineStr">
         <is>
-          <t>00169856</t>
+          <t>00169865</t>
         </is>
       </c>
       <c r="N37" s="12" t="n">
-        <v>1890</v>
-      </c>
-      <c r="O37" s="16" t="n">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="O37" s="12" t="n">
+        <v>65.73</v>
       </c>
       <c r="P37" s="12" t="n">
-        <v>0</v>
+        <v>52.58</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-33790</t>
+          <t>PDMDEP-33804</t>
         </is>
       </c>
       <c r="B38" s="14" t="inlineStr">
         <is>
-          <t>[CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD91)] - Commande modélisation supplémentaire - 6,5j</t>
+          <t>[CD 73)] - Purge arrêtés temporaires</t>
         </is>
       </c>
       <c r="C38" s="14" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D38" s="14" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD 91)</t>
+          <t>CONSEIL DEPARTEMENTAL DE LA SAVOIE (CD 73)</t>
         </is>
       </c>
       <c r="E38" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Commande modélisation supplémentaire </t>
+          <t>Purge arrêtés temporaires</t>
         </is>
       </c>
       <c r="F38" s="14" t="inlineStr">
@@ -3442,44 +3438,44 @@
       </c>
       <c r="I38" s="14" t="inlineStr">
         <is>
-          <t>09/06/2026</t>
+          <t>11/06/2026</t>
         </is>
       </c>
       <c r="J38" s="14" t="n">
         <v>3</v>
       </c>
       <c r="K38" s="14" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="L38" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-33794</t>
+          <t>PDMDEP-33808</t>
         </is>
       </c>
       <c r="M38" s="14" t="inlineStr">
         <is>
-          <t>00169697</t>
+          <t>00169856</t>
         </is>
       </c>
       <c r="N38" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O38" s="15" t="n">
-        <v>266.2</v>
+        <v>1890</v>
+      </c>
+      <c r="O38" s="16" t="n">
+        <v>0</v>
       </c>
       <c r="P38" s="15" t="n">
-        <v>70.98999999999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-33739</t>
+          <t>PDMDEP-33790</t>
         </is>
       </c>
       <c r="B39" s="11" t="inlineStr">
         <is>
-          <t>[COMMUNE DU POIRE SUR VIE (MAIRIE)] - UPSELL Pastell + Portail DA DPA</t>
+          <t>[CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD91)] - Commande modélisation supplémentaire - 6,5j</t>
         </is>
       </c>
       <c r="C39" s="11" t="inlineStr">
@@ -3489,12 +3485,12 @@
       </c>
       <c r="D39" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DU POIRE SUR VIE (MAIRIE)</t>
+          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD 91)</t>
         </is>
       </c>
       <c r="E39" s="11" t="inlineStr">
         <is>
-          <t>UPSELL PASTELL + DA DPA</t>
+          <t xml:space="preserve">Commande modélisation supplémentaire </t>
         </is>
       </c>
       <c r="F39" s="11" t="inlineStr">
@@ -3514,59 +3510,59 @@
       </c>
       <c r="I39" s="11" t="inlineStr">
         <is>
-          <t>08/06/2026</t>
+          <t>09/06/2026</t>
         </is>
       </c>
       <c r="J39" s="11" t="n">
         <v>3</v>
       </c>
       <c r="K39" s="11" t="n">
-        <v>1.5</v>
+        <v>3.75</v>
       </c>
       <c r="L39" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-33745</t>
+          <t>PDMDEP-33794</t>
         </is>
       </c>
       <c r="M39" s="11" t="inlineStr">
         <is>
-          <t>00169509</t>
+          <t>00169697</t>
         </is>
       </c>
       <c r="N39" s="12" t="n">
-        <v>920</v>
-      </c>
-      <c r="O39" s="16" t="n">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="O39" s="12" t="n">
+        <v>266.2</v>
       </c>
       <c r="P39" s="12" t="n">
-        <v>0</v>
+        <v>70.98999999999999</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-33729</t>
+          <t>PDMDEP-33739</t>
         </is>
       </c>
       <c r="B40" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">[VILLE DE NEUILLY SUR SEINE - Direction des systèmes d'information] - MONTEE DE VERSION LITT EXP  test et prod </t>
+          <t>[COMMUNE DU POIRE SUR VIE (MAIRIE)] - UPSELL Pastell + Portail DA DPA</t>
         </is>
       </c>
       <c r="C40" s="14" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D40" s="14" t="inlineStr">
         <is>
-          <t>VILLE DE NEUILLY SUR SEINE - Direction des systèmes d'information</t>
+          <t>COMMUNE DU POIRE SUR VIE (MAIRIE)</t>
         </is>
       </c>
       <c r="E40" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">MONTEE DE VERSION LITT EXP  test et prod </t>
+          <t>UPSELL PASTELL + DA DPA</t>
         </is>
       </c>
       <c r="F40" s="14" t="inlineStr">
@@ -3593,37 +3589,37 @@
         <v>3</v>
       </c>
       <c r="K40" s="14" t="n">
-        <v>0.75</v>
+        <v>1.5</v>
       </c>
       <c r="L40" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-33733</t>
+          <t>PDMDEP-33745</t>
         </is>
       </c>
       <c r="M40" s="14" t="inlineStr">
         <is>
-          <t>00169480</t>
+          <t>00169509</t>
         </is>
       </c>
       <c r="N40" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O40" s="15" t="n">
-        <v>679.5</v>
+        <v>920</v>
+      </c>
+      <c r="O40" s="16" t="n">
+        <v>0</v>
       </c>
       <c r="P40" s="15" t="n">
-        <v>906</v>
+        <v>0</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-33699</t>
+          <t>PDMDEP-33729</t>
         </is>
       </c>
       <c r="B41" s="11" t="inlineStr">
         <is>
-          <t>[CD 35)] - Montée de version Littéralis - 1 journée d'assistance fonctionnelle à distance</t>
+          <t xml:space="preserve">[VILLE DE NEUILLY SUR SEINE - Direction des systèmes d'information] - MONTEE DE VERSION LITT EXP  test et prod </t>
         </is>
       </c>
       <c r="C41" s="11" t="inlineStr">
@@ -3633,12 +3629,12 @@
       </c>
       <c r="D41" s="11" t="inlineStr">
         <is>
-          <t>DEPARTEMENT D'ILLE ET VILAINE (CD 35)</t>
+          <t>VILLE DE NEUILLY SUR SEINE - Direction des systèmes d'information</t>
         </is>
       </c>
       <c r="E41" s="11" t="inlineStr">
         <is>
-          <t>Montée de version Littéralis - 1 journée d'assistance fonctionnelle à distance</t>
+          <t xml:space="preserve">MONTEE DE VERSION LITT EXP  test et prod </t>
         </is>
       </c>
       <c r="F41" s="11" t="inlineStr">
@@ -3658,7 +3654,7 @@
       </c>
       <c r="I41" s="11" t="inlineStr">
         <is>
-          <t>05/06/2026</t>
+          <t>08/06/2026</t>
         </is>
       </c>
       <c r="J41" s="11" t="n">
@@ -3669,53 +3665,53 @@
       </c>
       <c r="L41" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-33703</t>
+          <t>PDMDEP-33733</t>
         </is>
       </c>
       <c r="M41" s="11" t="inlineStr">
         <is>
-          <t>00169363</t>
+          <t>00169480</t>
         </is>
       </c>
       <c r="N41" s="12" t="n">
         <v>0</v>
       </c>
       <c r="O41" s="12" t="n">
-        <v>540</v>
+        <v>679.5</v>
       </c>
       <c r="P41" s="12" t="n">
-        <v>720</v>
+        <v>906</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-33610</t>
+          <t>PDMDEP-33699</t>
         </is>
       </c>
       <c r="B42" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">[COMMUNE DE MORLAIX] - Migration GEODP Placier hors matériel </t>
+          <t>[CD 35)] - Montée de version Littéralis - 1 journée d'assistance fonctionnelle à distance</t>
         </is>
       </c>
       <c r="C42" s="14" t="inlineStr">
         <is>
-          <t>Estelle LEDUC</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D42" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE MORLAIX</t>
+          <t>DEPARTEMENT D'ILLE ET VILAINE (CD 35)</t>
         </is>
       </c>
       <c r="E42" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">MIGRATION GEODP PLACIER hors matériel </t>
+          <t>Montée de version Littéralis - 1 journée d'assistance fonctionnelle à distance</t>
         </is>
       </c>
       <c r="F42" s="14" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G42" s="14" t="inlineStr">
@@ -3725,64 +3721,64 @@
       </c>
       <c r="H42" s="14" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I42" s="14" t="inlineStr">
         <is>
-          <t>02/06/2026</t>
+          <t>05/06/2026</t>
         </is>
       </c>
       <c r="J42" s="14" t="n">
         <v>3</v>
       </c>
       <c r="K42" s="14" t="n">
-        <v>0</v>
+        <v>0.75</v>
       </c>
       <c r="L42" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-33616</t>
+          <t>PDMDEP-33703</t>
         </is>
       </c>
       <c r="M42" s="14" t="inlineStr">
         <is>
-          <t>00169015</t>
+          <t>00169363</t>
         </is>
       </c>
       <c r="N42" s="15" t="n">
         <v>0</v>
       </c>
       <c r="O42" s="15" t="n">
-        <v>505</v>
+        <v>540</v>
       </c>
       <c r="P42" s="15" t="n">
-        <v>0</v>
+        <v>720</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-33597</t>
+          <t>PDMDEP-33610</t>
         </is>
       </c>
       <c r="B43" s="11" t="inlineStr">
         <is>
-          <t>[Commune de Trets] - Ajout d'un Module Caisse sur GEODP avec paiement CB</t>
+          <t xml:space="preserve">[COMMUNE DE MORLAIX] - Migration GEODP Placier hors matériel </t>
         </is>
       </c>
       <c r="C43" s="11" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Estelle LEDUC</t>
         </is>
       </c>
       <c r="D43" s="11" t="inlineStr">
         <is>
-          <t>Commune de Trets</t>
+          <t>COMMUNE DE MORLAIX</t>
         </is>
       </c>
       <c r="E43" s="11" t="inlineStr">
         <is>
-          <t>Ajout d'un Module Caisse sur GEODP avec paiement CB</t>
+          <t xml:space="preserve">MIGRATION GEODP PLACIER hors matériel </t>
         </is>
       </c>
       <c r="F43" s="11" t="inlineStr">
@@ -3797,7 +3793,7 @@
       </c>
       <c r="H43" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I43" s="11" t="inlineStr">
@@ -3809,23 +3805,23 @@
         <v>3</v>
       </c>
       <c r="K43" s="11" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L43" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-33605</t>
+          <t>PDMDEP-33616</t>
         </is>
       </c>
       <c r="M43" s="11" t="inlineStr">
         <is>
-          <t>00168993</t>
+          <t>00169015</t>
         </is>
       </c>
       <c r="N43" s="12" t="n">
         <v>0</v>
       </c>
       <c r="O43" s="12" t="n">
-        <v>0</v>
+        <v>505</v>
       </c>
       <c r="P43" s="12" t="n">
         <v>0</v>
@@ -3834,12 +3830,12 @@
     <row r="44">
       <c r="A44" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-33500</t>
+          <t>PDMDEP-33597</t>
         </is>
       </c>
       <c r="B44" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">[Mairie de Carcès ] - GEODP PLACIER avec PAIEMENT CB </t>
+          <t>[Commune de Trets] - Ajout d'un Module Caisse sur GEODP avec paiement CB</t>
         </is>
       </c>
       <c r="C44" s="14" t="inlineStr">
@@ -3849,12 +3845,12 @@
       </c>
       <c r="D44" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mairie de Carcès </t>
+          <t>Commune de Trets</t>
         </is>
       </c>
       <c r="E44" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">GEODP PLACIER avec PAIEMENT CB </t>
+          <t>Ajout d'un Module Caisse sur GEODP avec paiement CB</t>
         </is>
       </c>
       <c r="F44" s="14" t="inlineStr">
@@ -3869,69 +3865,69 @@
       </c>
       <c r="H44" s="14" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I44" s="14" t="inlineStr">
         <is>
-          <t>29/05/2026</t>
+          <t>02/06/2026</t>
         </is>
       </c>
       <c r="J44" s="14" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K44" s="14" t="n">
-        <v>1.5</v>
+        <v>3</v>
       </c>
       <c r="L44" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-33509</t>
+          <t>PDMDEP-33605</t>
         </is>
       </c>
       <c r="M44" s="14" t="inlineStr">
         <is>
-          <t>00168117</t>
+          <t>00168993</t>
         </is>
       </c>
       <c r="N44" s="15" t="n">
         <v>0</v>
       </c>
       <c r="O44" s="15" t="n">
-        <v>691.9</v>
+        <v>0</v>
       </c>
       <c r="P44" s="15" t="n">
-        <v>461.27</v>
+        <v>0</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-33471</t>
+          <t>PDMDEP-33500</t>
         </is>
       </c>
       <c r="B45" s="11" t="inlineStr">
         <is>
-          <t>[COMMUNE D AUCH] - FDS Facture LiS</t>
+          <t xml:space="preserve">[Mairie de Carcès ] - GEODP PLACIER avec PAIEMENT CB </t>
         </is>
       </c>
       <c r="C45" s="11" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D45" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE D AUCH</t>
+          <t xml:space="preserve">Mairie de Carcès </t>
         </is>
       </c>
       <c r="E45" s="11" t="inlineStr">
         <is>
-          <t>FDS Facture LiS</t>
+          <t xml:space="preserve">GEODP PLACIER avec PAIEMENT CB </t>
         </is>
       </c>
       <c r="F45" s="11" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G45" s="11" t="inlineStr">
@@ -3941,69 +3937,69 @@
       </c>
       <c r="H45" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I45" s="11" t="inlineStr">
         <is>
-          <t>28/05/2026</t>
+          <t>29/05/2026</t>
         </is>
       </c>
       <c r="J45" s="11" t="n">
         <v>4</v>
       </c>
       <c r="K45" s="11" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="L45" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-33475</t>
+          <t>PDMDEP-33509</t>
         </is>
       </c>
       <c r="M45" s="11" t="inlineStr">
         <is>
-          <t>00168025</t>
+          <t>00168117</t>
         </is>
       </c>
       <c r="N45" s="12" t="n">
-        <v>171.4</v>
-      </c>
-      <c r="O45" s="16" t="n">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="O45" s="12" t="n">
+        <v>691.9</v>
       </c>
       <c r="P45" s="12" t="n">
-        <v>0</v>
+        <v>461.27</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-33431</t>
+          <t>PDMDEP-33471</t>
         </is>
       </c>
       <c r="B46" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">[COMMUNE DE VERSAILLES] - Migration multi-modules (hors taxi) </t>
+          <t>[COMMUNE D AUCH] - FDS Facture LiS</t>
         </is>
       </c>
       <c r="C46" s="14" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D46" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">COMMUNE DE VERSAILLES </t>
+          <t>COMMUNE D AUCH</t>
         </is>
       </c>
       <c r="E46" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Migration multi-modules (hors taxi) </t>
+          <t>FDS Facture LiS</t>
         </is>
       </c>
       <c r="F46" s="14" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G46" s="14" t="inlineStr">
@@ -4013,12 +4009,12 @@
       </c>
       <c r="H46" s="14" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I46" s="14" t="inlineStr">
         <is>
-          <t>27/05/2026</t>
+          <t>28/05/2026</t>
         </is>
       </c>
       <c r="J46" s="14" t="n">
@@ -4029,19 +4025,19 @@
       </c>
       <c r="L46" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-33440</t>
+          <t>PDMDEP-33475</t>
         </is>
       </c>
       <c r="M46" s="14" t="inlineStr">
         <is>
-          <t>00166923</t>
+          <t>00168025</t>
         </is>
       </c>
       <c r="N46" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O46" s="15" t="n">
-        <v>3339.2</v>
+        <v>171.4</v>
+      </c>
+      <c r="O46" s="16" t="n">
+        <v>0</v>
       </c>
       <c r="P46" s="15" t="n">
         <v>0</v>
@@ -4050,27 +4046,27 @@
     <row r="47">
       <c r="A47" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-33395</t>
+          <t>PDMDEP-33431</t>
         </is>
       </c>
       <c r="B47" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">[COMMUNE DE MONTBELIARD] - Mise en place paiement CB sur PAX présent sur la commune </t>
+          <t xml:space="preserve">[COMMUNE DE VERSAILLES] - Migration multi-modules (hors taxi) </t>
         </is>
       </c>
       <c r="C47" s="11" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D47" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE MONTBELIARD</t>
+          <t xml:space="preserve">COMMUNE DE VERSAILLES </t>
         </is>
       </c>
       <c r="E47" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mise en place paiement CB sur PAX présent sur la commune </t>
+          <t xml:space="preserve">Migration multi-modules (hors taxi) </t>
         </is>
       </c>
       <c r="F47" s="11" t="inlineStr">
@@ -4085,12 +4081,12 @@
       </c>
       <c r="H47" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I47" s="11" t="inlineStr">
         <is>
-          <t>26/05/2026</t>
+          <t>27/05/2026</t>
         </is>
       </c>
       <c r="J47" s="11" t="n">
@@ -4101,19 +4097,19 @@
       </c>
       <c r="L47" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-33401</t>
+          <t>PDMDEP-33440</t>
         </is>
       </c>
       <c r="M47" s="11" t="inlineStr">
         <is>
-          <t>00167624</t>
+          <t>00166923</t>
         </is>
       </c>
       <c r="N47" s="12" t="n">
-        <v>344</v>
-      </c>
-      <c r="O47" s="16" t="n">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="O47" s="12" t="n">
+        <v>3339.2</v>
       </c>
       <c r="P47" s="12" t="n">
         <v>0</v>
@@ -4122,27 +4118,27 @@
     <row r="48">
       <c r="A48" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-33266</t>
+          <t>PDMDEP-33395</t>
         </is>
       </c>
       <c r="B48" s="14" t="inlineStr">
         <is>
-          <t>[MAIRIE DE CAPBRETON] - Commune dispose de Geodp Terrasses, nouveau module pour leurs marchés</t>
+          <t xml:space="preserve">[COMMUNE DE MONTBELIARD] - Mise en place paiement CB sur PAX présent sur la commune </t>
         </is>
       </c>
       <c r="C48" s="14" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D48" s="14" t="inlineStr">
         <is>
-          <t>MAIRIE DE CAPBRETON</t>
+          <t>COMMUNE DE MONTBELIARD</t>
         </is>
       </c>
       <c r="E48" s="14" t="inlineStr">
         <is>
-          <t>Commune dispose de Geodp Terrasses, nouveau module pour leurs marchés</t>
+          <t xml:space="preserve">Mise en place paiement CB sur PAX présent sur la commune </t>
         </is>
       </c>
       <c r="F48" s="14" t="inlineStr">
@@ -4162,7 +4158,7 @@
       </c>
       <c r="I48" s="14" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>26/05/2026</t>
         </is>
       </c>
       <c r="J48" s="14" t="n">
@@ -4173,16 +4169,16 @@
       </c>
       <c r="L48" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-33272</t>
+          <t>PDMDEP-33401</t>
         </is>
       </c>
       <c r="M48" s="14" t="inlineStr">
         <is>
-          <t>00166910</t>
+          <t>00167624</t>
         </is>
       </c>
       <c r="N48" s="15" t="n">
-        <v>500</v>
+        <v>344</v>
       </c>
       <c r="O48" s="16" t="n">
         <v>0</v>
@@ -4194,27 +4190,27 @@
     <row r="49">
       <c r="A49" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-33239</t>
+          <t>PDMDEP-33266</t>
         </is>
       </c>
       <c r="B49" s="11" t="inlineStr">
         <is>
-          <t>[MAIRIE DE LODEVE] - Migracier activité Placier vers Geodp V2</t>
+          <t>[MAIRIE DE CAPBRETON] - Commune dispose de Geodp Terrasses, nouveau module pour leurs marchés</t>
         </is>
       </c>
       <c r="C49" s="11" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D49" s="11" t="inlineStr">
         <is>
-          <t>MAIRIE DE LODEVE</t>
+          <t>MAIRIE DE CAPBRETON</t>
         </is>
       </c>
       <c r="E49" s="11" t="inlineStr">
         <is>
-          <t>Migracier activité Placier vers Geodp V2</t>
+          <t>Commune dispose de Geodp Terrasses, nouveau module pour leurs marchés</t>
         </is>
       </c>
       <c r="F49" s="11" t="inlineStr">
@@ -4229,12 +4225,12 @@
       </c>
       <c r="H49" s="11" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I49" s="11" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="J49" s="11" t="n">
@@ -4245,16 +4241,16 @@
       </c>
       <c r="L49" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-33245</t>
+          <t>PDMDEP-33272</t>
         </is>
       </c>
       <c r="M49" s="11" t="inlineStr">
         <is>
-          <t>00166748</t>
+          <t>00166910</t>
         </is>
       </c>
       <c r="N49" s="12" t="n">
-        <v>149</v>
+        <v>500</v>
       </c>
       <c r="O49" s="16" t="n">
         <v>0</v>
@@ -4266,32 +4262,32 @@
     <row r="50">
       <c r="A50" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-33227</t>
+          <t>PDMDEP-33239</t>
         </is>
       </c>
       <c r="B50" s="14" t="inlineStr">
         <is>
-          <t>[METROPOLE EUROPEENNE DE LILLE] - MEL Crédits 21 heures (3j)     mai 2026</t>
+          <t>[MAIRIE DE LODEVE] - Migracier activité Placier vers Geodp V2</t>
         </is>
       </c>
       <c r="C50" s="14" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D50" s="14" t="inlineStr">
         <is>
-          <t>METROPOLE EUROPEENNE DE LILLE</t>
+          <t>MAIRIE DE LODEVE</t>
         </is>
       </c>
       <c r="E50" s="14" t="inlineStr">
         <is>
-          <t>21 crédits d'heure</t>
+          <t>Migracier activité Placier vers Geodp V2</t>
         </is>
       </c>
       <c r="F50" s="14" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G50" s="14" t="inlineStr">
@@ -4301,38 +4297,38 @@
       </c>
       <c r="H50" s="14" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I50" s="14" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="J50" s="14" t="n">
         <v>4</v>
       </c>
       <c r="K50" s="14" t="n">
-        <v>0.62</v>
+        <v>0</v>
       </c>
       <c r="L50" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-33232</t>
+          <t>PDMDEP-33245</t>
         </is>
       </c>
       <c r="M50" s="14" t="inlineStr">
         <is>
-          <t>00166708</t>
+          <t>00166748</t>
         </is>
       </c>
       <c r="N50" s="15" t="n">
-        <v>625</v>
+        <v>149</v>
       </c>
       <c r="O50" s="16" t="n">
-        <v>337.5</v>
+        <v>0</v>
       </c>
       <c r="P50" s="15" t="n">
-        <v>540</v>
+        <v>0</v>
       </c>
     </row>
     <row r="51">
@@ -4389,53 +4385,53 @@
       </c>
       <c r="L51" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-33231</t>
+          <t>PDMDEP-33232</t>
         </is>
       </c>
       <c r="M51" s="11" t="inlineStr">
         <is>
-          <t>00166707</t>
+          <t>00166708</t>
         </is>
       </c>
       <c r="N51" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O51" s="12" t="n">
-        <v>16</v>
+        <v>625</v>
+      </c>
+      <c r="O51" s="16" t="n">
+        <v>337.5</v>
       </c>
       <c r="P51" s="12" t="n">
-        <v>25.6</v>
+        <v>540</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-33170</t>
+          <t>PDMDEP-33227</t>
         </is>
       </c>
       <c r="B52" s="14" t="inlineStr">
         <is>
-          <t>[Commune de Bonneville] - MIGRATION GEODP PLACIER ON PREM VERS SAAS</t>
+          <t>[METROPOLE EUROPEENNE DE LILLE] - MEL Crédits 21 heures (3j)     mai 2026</t>
         </is>
       </c>
       <c r="C52" s="14" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D52" s="14" t="inlineStr">
         <is>
-          <t>Commune de Bonneville</t>
+          <t>METROPOLE EUROPEENNE DE LILLE</t>
         </is>
       </c>
       <c r="E52" s="14" t="inlineStr">
         <is>
-          <t>MIGRATION GEODP PLACIER ON PREM VERS SAAS</t>
+          <t>21 crédits d'heure</t>
         </is>
       </c>
       <c r="F52" s="14" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G52" s="14" t="inlineStr">
@@ -4445,49 +4441,49 @@
       </c>
       <c r="H52" s="14" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I52" s="14" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="J52" s="14" t="n">
         <v>4</v>
       </c>
       <c r="K52" s="14" t="n">
-        <v>0</v>
+        <v>0.62</v>
       </c>
       <c r="L52" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-33177</t>
+          <t>PDMDEP-33231</t>
         </is>
       </c>
       <c r="M52" s="14" t="inlineStr">
         <is>
-          <t>00166356</t>
+          <t>00166707</t>
         </is>
       </c>
       <c r="N52" s="15" t="n">
-        <v>910</v>
-      </c>
-      <c r="O52" s="16" t="n">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="O52" s="15" t="n">
+        <v>16</v>
       </c>
       <c r="P52" s="15" t="n">
-        <v>0</v>
+        <v>25.6</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-33064</t>
+          <t>PDMDEP-33170</t>
         </is>
       </c>
       <c r="B53" s="11" t="inlineStr">
         <is>
-          <t>[MAIRIE DE LONGWY] - Migration GEODP 1 vers GEODP 2 (Placier)</t>
+          <t>[Commune de Bonneville] - MIGRATION GEODP PLACIER ON PREM VERS SAAS</t>
         </is>
       </c>
       <c r="C53" s="11" t="inlineStr">
@@ -4497,12 +4493,12 @@
       </c>
       <c r="D53" s="11" t="inlineStr">
         <is>
-          <t>MAIRIE DE LONGWY</t>
+          <t>Commune de Bonneville</t>
         </is>
       </c>
       <c r="E53" s="11" t="inlineStr">
         <is>
-          <t>Migration GEODP 1 vers GEODP 2 (Placier)</t>
+          <t>MIGRATION GEODP PLACIER ON PREM VERS SAAS</t>
         </is>
       </c>
       <c r="F53" s="11" t="inlineStr">
@@ -4522,27 +4518,27 @@
       </c>
       <c r="I53" s="11" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="J53" s="11" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K53" s="11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L53" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-33073</t>
+          <t>PDMDEP-33177</t>
         </is>
       </c>
       <c r="M53" s="11" t="inlineStr">
         <is>
-          <t>00165708</t>
+          <t>00166356</t>
         </is>
       </c>
       <c r="N53" s="12" t="n">
-        <v>1207</v>
+        <v>910</v>
       </c>
       <c r="O53" s="16" t="n">
         <v>0</v>
@@ -4554,32 +4550,32 @@
     <row r="54">
       <c r="A54" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-32984</t>
+          <t>PDMDEP-33064</t>
         </is>
       </c>
       <c r="B54" s="14" t="inlineStr">
         <is>
-          <t>[COMMUNE DE MONTELIMAR] - Interface Civil net finance avec Littéralis</t>
+          <t>[MAIRIE DE LONGWY] - Migration GEODP 1 vers GEODP 2 (Placier)</t>
         </is>
       </c>
       <c r="C54" s="14" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D54" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE MONTELIMAR</t>
+          <t>MAIRIE DE LONGWY</t>
         </is>
       </c>
       <c r="E54" s="14" t="inlineStr">
         <is>
-          <t>Interface Civil net finance avec Littéralis</t>
+          <t>Migration GEODP 1 vers GEODP 2 (Placier)</t>
         </is>
       </c>
       <c r="F54" s="14" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G54" s="14" t="inlineStr">
@@ -4589,32 +4585,32 @@
       </c>
       <c r="H54" s="14" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I54" s="14" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="J54" s="14" t="n">
         <v>5</v>
       </c>
       <c r="K54" s="14" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L54" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-32990</t>
+          <t>PDMDEP-33073</t>
         </is>
       </c>
       <c r="M54" s="14" t="inlineStr">
         <is>
-          <t>00165270</t>
+          <t>00165708</t>
         </is>
       </c>
       <c r="N54" s="15" t="n">
-        <v>500</v>
+        <v>1207</v>
       </c>
       <c r="O54" s="16" t="n">
         <v>0</v>
@@ -4626,27 +4622,27 @@
     <row r="55">
       <c r="A55" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-32768</t>
+          <t>PDMDEP-32984</t>
         </is>
       </c>
       <c r="B55" s="11" t="inlineStr">
         <is>
-          <t>[VILLE DE REIMS] - MV app/ infra + màj carto - ON prem</t>
+          <t>[COMMUNE DE MONTELIMAR] - Interface Civil net finance avec Littéralis</t>
         </is>
       </c>
       <c r="C55" s="11" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D55" s="11" t="inlineStr">
         <is>
-          <t>VILLE DE REIMS</t>
+          <t>COMMUNE DE MONTELIMAR</t>
         </is>
       </c>
       <c r="E55" s="11" t="inlineStr">
         <is>
-          <t>MV app/ infra + màj carto</t>
+          <t>Interface Civil net finance avec Littéralis</t>
         </is>
       </c>
       <c r="F55" s="11" t="inlineStr">
@@ -4666,29 +4662,29 @@
       </c>
       <c r="I55" s="11" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="J55" s="11" t="n">
         <v>5</v>
       </c>
       <c r="K55" s="11" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="L55" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-32772</t>
+          <t>PDMDEP-32990</t>
         </is>
       </c>
       <c r="M55" s="11" t="inlineStr">
         <is>
-          <t>00163806</t>
+          <t>00165270</t>
         </is>
       </c>
       <c r="N55" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O55" s="12" t="n">
+        <v>500</v>
+      </c>
+      <c r="O55" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P55" s="12" t="n">
@@ -4698,12 +4694,12 @@
     <row r="56">
       <c r="A56" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-32552</t>
+          <t>PDMDEP-32768</t>
         </is>
       </c>
       <c r="B56" s="14" t="inlineStr">
         <is>
-          <t>[CHALON SUR SAONE] - Littéralis - Intégration et paramétrage des redevances d'occupation du domaine public</t>
+          <t>[VILLE DE REIMS] - MV app/ infra + màj carto - ON prem</t>
         </is>
       </c>
       <c r="C56" s="14" t="inlineStr">
@@ -4713,12 +4709,12 @@
       </c>
       <c r="D56" s="14" t="inlineStr">
         <is>
-          <t>VILLE DE CHALON SUR SAONE</t>
+          <t>VILLE DE REIMS</t>
         </is>
       </c>
       <c r="E56" s="14" t="inlineStr">
         <is>
-          <t>Littéralis - Intégration et paramétrage des redevances d'occupation du domaine public</t>
+          <t>MV app/ infra + màj carto</t>
         </is>
       </c>
       <c r="F56" s="14" t="inlineStr">
@@ -4738,29 +4734,29 @@
       </c>
       <c r="I56" s="14" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="J56" s="14" t="n">
         <v>5</v>
       </c>
       <c r="K56" s="14" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="L56" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-32556</t>
+          <t>PDMDEP-32772</t>
         </is>
       </c>
       <c r="M56" s="14" t="inlineStr">
         <is>
-          <t>00162313</t>
+          <t>00163806</t>
         </is>
       </c>
       <c r="N56" s="15" t="n">
-        <v>142.1</v>
-      </c>
-      <c r="O56" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O56" s="15" t="n">
         <v>0</v>
       </c>
       <c r="P56" s="15" t="n">
@@ -4770,32 +4766,32 @@
     <row r="57">
       <c r="A57" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-32461</t>
+          <t>PDMDEP-32552</t>
         </is>
       </c>
       <c r="B57" s="11" t="inlineStr">
         <is>
-          <t>[NANTES METROPOLE - VDC] - Migration GEODP 1 vers GEODP 2</t>
+          <t>[CHALON SUR SAONE] - Littéralis - Intégration et paramétrage des redevances d'occupation du domaine public</t>
         </is>
       </c>
       <c r="C57" s="11" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D57" s="11" t="inlineStr">
         <is>
-          <t>NANTES METROPOLE - VDC</t>
+          <t>VILLE DE CHALON SUR SAONE</t>
         </is>
       </c>
       <c r="E57" s="11" t="inlineStr">
         <is>
-          <t>Migration GEODP 1 vers GEODP 2</t>
+          <t>Littéralis - Intégration et paramétrage des redevances d'occupation du domaine public</t>
         </is>
       </c>
       <c r="F57" s="11" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G57" s="11" t="inlineStr">
@@ -4805,32 +4801,32 @@
       </c>
       <c r="H57" s="11" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I57" s="11" t="inlineStr">
         <is>
-          <t>30/03/2026</t>
+          <t>01/04/2026</t>
         </is>
       </c>
       <c r="J57" s="11" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K57" s="11" t="n">
         <v>0</v>
       </c>
       <c r="L57" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-32470</t>
+          <t>PDMDEP-32556</t>
         </is>
       </c>
       <c r="M57" s="11" t="inlineStr">
         <is>
-          <t>00161950</t>
+          <t>00162313</t>
         </is>
       </c>
       <c r="N57" s="12" t="n">
-        <v>2335</v>
+        <v>142.1</v>
       </c>
       <c r="O57" s="16" t="n">
         <v>0</v>
@@ -4842,32 +4838,32 @@
     <row r="58">
       <c r="A58" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-32442</t>
+          <t>PDMDEP-32461</t>
         </is>
       </c>
       <c r="B58" s="14" t="inlineStr">
         <is>
-          <t>[COMMUNE DE CHAMBERY] - Montée de version LiEx Test et prod  (03/26)</t>
+          <t>[NANTES METROPOLE - VDC] - Migration GEODP 1 vers GEODP 2</t>
         </is>
       </c>
       <c r="C58" s="14" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D58" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE CHAMBERY</t>
+          <t>NANTES METROPOLE - VDC</t>
         </is>
       </c>
       <c r="E58" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Montée de version LiEx Test et prod </t>
+          <t>Migration GEODP 1 vers GEODP 2</t>
         </is>
       </c>
       <c r="F58" s="14" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G58" s="14" t="inlineStr">
@@ -4877,34 +4873,34 @@
       </c>
       <c r="H58" s="14" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I58" s="14" t="inlineStr">
         <is>
-          <t>27/03/2026</t>
+          <t>30/03/2026</t>
         </is>
       </c>
       <c r="J58" s="14" t="n">
         <v>6</v>
       </c>
       <c r="K58" s="14" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="L58" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-32446</t>
+          <t>PDMDEP-32470</t>
         </is>
       </c>
       <c r="M58" s="14" t="inlineStr">
         <is>
-          <t>00161842</t>
+          <t>00161950</t>
         </is>
       </c>
       <c r="N58" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O58" s="15" t="n">
+        <v>2335</v>
+      </c>
+      <c r="O58" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P58" s="15" t="n">
@@ -4914,32 +4910,32 @@
     <row r="59">
       <c r="A59" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-32366</t>
+          <t>PDMDEP-32442</t>
         </is>
       </c>
       <c r="B59" s="11" t="inlineStr">
         <is>
-          <t>[Commune de Pleneuf Val André] - Migration de GEODP-Placier simple</t>
+          <t>[COMMUNE DE CHAMBERY] - Montée de version LiEx Test et prod  (03/26)</t>
         </is>
       </c>
       <c r="C59" s="11" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D59" s="11" t="inlineStr">
         <is>
-          <t>Commune de Pleneuf Val André</t>
+          <t>COMMUNE DE CHAMBERY</t>
         </is>
       </c>
       <c r="E59" s="11" t="inlineStr">
         <is>
-          <t>Migration de GEODP-Placier simple</t>
+          <t xml:space="preserve">Montée de version LiEx Test et prod </t>
         </is>
       </c>
       <c r="F59" s="11" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G59" s="11" t="inlineStr">
@@ -4949,28 +4945,28 @@
       </c>
       <c r="H59" s="11" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I59" s="11" t="inlineStr">
         <is>
-          <t>26/03/2026</t>
+          <t>27/03/2026</t>
         </is>
       </c>
       <c r="J59" s="11" t="n">
         <v>6</v>
       </c>
       <c r="K59" s="11" t="n">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
       <c r="L59" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-32372</t>
+          <t>PDMDEP-32446</t>
         </is>
       </c>
       <c r="M59" s="11" t="inlineStr">
         <is>
-          <t>00161594</t>
+          <t>00161842</t>
         </is>
       </c>
       <c r="N59" s="12" t="n">
@@ -4986,12 +4982,12 @@
     <row r="60">
       <c r="A60" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-32331</t>
+          <t>PDMDEP-32366</t>
         </is>
       </c>
       <c r="B60" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">[COMMUNE DE CHALONS EN CHAMPAGNE] - Migration GEODP Placier </t>
+          <t>[Commune de Pleneuf Val André] - Migration de GEODP-Placier simple</t>
         </is>
       </c>
       <c r="C60" s="14" t="inlineStr">
@@ -5001,12 +4997,12 @@
       </c>
       <c r="D60" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE CHALONS EN CHAMPAGNE</t>
+          <t>Commune de Pleneuf Val André</t>
         </is>
       </c>
       <c r="E60" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Migration GEODP Placier </t>
+          <t>Migration de GEODP-Placier simple</t>
         </is>
       </c>
       <c r="F60" s="14" t="inlineStr">
@@ -5026,29 +5022,29 @@
       </c>
       <c r="I60" s="14" t="inlineStr">
         <is>
-          <t>25/03/2026</t>
+          <t>26/03/2026</t>
         </is>
       </c>
       <c r="J60" s="14" t="n">
         <v>6</v>
       </c>
       <c r="K60" s="14" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="L60" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-32340</t>
+          <t>PDMDEP-32372</t>
         </is>
       </c>
       <c r="M60" s="14" t="inlineStr">
         <is>
-          <t>00161493</t>
+          <t>00161594</t>
         </is>
       </c>
       <c r="N60" s="15" t="n">
-        <v>450</v>
-      </c>
-      <c r="O60" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O60" s="15" t="n">
         <v>0</v>
       </c>
       <c r="P60" s="15" t="n">
@@ -5058,32 +5054,32 @@
     <row r="61">
       <c r="A61" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-32264</t>
+          <t>PDMDEP-32331</t>
         </is>
       </c>
       <c r="B61" s="11" t="inlineStr">
         <is>
-          <t>[CA DU NIORTAIS] - Modélisation 5j</t>
+          <t xml:space="preserve">[COMMUNE DE CHALONS EN CHAMPAGNE] - Migration GEODP Placier </t>
         </is>
       </c>
       <c r="C61" s="11" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D61" s="11" t="inlineStr">
         <is>
-          <t>CA DU NIORTAIS</t>
+          <t>COMMUNE DE CHALONS EN CHAMPAGNE</t>
         </is>
       </c>
       <c r="E61" s="11" t="inlineStr">
         <is>
-          <t>Modélisation</t>
+          <t xml:space="preserve">Migration GEODP Placier </t>
         </is>
       </c>
       <c r="F61" s="11" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G61" s="11" t="inlineStr">
@@ -5093,69 +5089,69 @@
       </c>
       <c r="H61" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I61" s="11" t="inlineStr">
         <is>
-          <t>23/03/2026</t>
+          <t>25/03/2026</t>
         </is>
       </c>
       <c r="J61" s="11" t="n">
         <v>6</v>
       </c>
       <c r="K61" s="11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L61" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-32268</t>
+          <t>PDMDEP-32340</t>
         </is>
       </c>
       <c r="M61" s="11" t="inlineStr">
         <is>
-          <t>00161073</t>
+          <t>00161493</t>
         </is>
       </c>
       <c r="N61" s="12" t="n">
-        <v>910</v>
+        <v>450</v>
       </c>
       <c r="O61" s="16" t="n">
-        <v>136.5</v>
+        <v>0</v>
       </c>
       <c r="P61" s="12" t="n">
-        <v>68.25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-32086</t>
+          <t>PDMDEP-32264</t>
         </is>
       </c>
       <c r="B62" s="14" t="inlineStr">
         <is>
-          <t>[COMMUNE DE VITRY LE FRANCOIS] - Acquisition Geodp Placier</t>
+          <t>[CA DU NIORTAIS] - Modélisation 5j</t>
         </is>
       </c>
       <c r="C62" s="14" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D62" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE VITRY LE FRANCOIS</t>
+          <t>CA DU NIORTAIS</t>
         </is>
       </c>
       <c r="E62" s="14" t="inlineStr">
         <is>
-          <t>Acquisition Geodp Placier</t>
+          <t>Modélisation</t>
         </is>
       </c>
       <c r="F62" s="14" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G62" s="14" t="inlineStr">
@@ -5165,49 +5161,49 @@
       </c>
       <c r="H62" s="14" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I62" s="14" t="inlineStr">
         <is>
-          <t>17/03/2026</t>
+          <t>23/03/2026</t>
         </is>
       </c>
       <c r="J62" s="14" t="n">
         <v>6</v>
       </c>
       <c r="K62" s="14" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L62" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-32095</t>
+          <t>PDMDEP-32268</t>
         </is>
       </c>
       <c r="M62" s="14" t="inlineStr">
         <is>
-          <t>00160474</t>
+          <t>00161073</t>
         </is>
       </c>
       <c r="N62" s="15" t="n">
-        <v>590.15</v>
+        <v>910</v>
       </c>
       <c r="O62" s="16" t="n">
-        <v>0</v>
+        <v>136.5</v>
       </c>
       <c r="P62" s="15" t="n">
-        <v>0</v>
+        <v>68.25</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-32065</t>
+          <t>PDMDEP-32086</t>
         </is>
       </c>
       <c r="B63" s="11" t="inlineStr">
         <is>
-          <t>[COMMUNE DE MONTBRISON] - Migration GeODP Placier + Ajout Civil Net Finance</t>
+          <t>[COMMUNE DE VITRY LE FRANCOIS] - Acquisition Geodp Placier</t>
         </is>
       </c>
       <c r="C63" s="11" t="inlineStr">
@@ -5217,12 +5213,12 @@
       </c>
       <c r="D63" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE MONTBRISON</t>
+          <t>COMMUNE DE VITRY LE FRANCOIS</t>
         </is>
       </c>
       <c r="E63" s="11" t="inlineStr">
         <is>
-          <t>Migration GeODP Placier + Ajout Civil Net Finance</t>
+          <t>Acquisition Geodp Placier</t>
         </is>
       </c>
       <c r="F63" s="11" t="inlineStr">
@@ -5237,12 +5233,12 @@
       </c>
       <c r="H63" s="11" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I63" s="11" t="inlineStr">
         <is>
-          <t>16/03/2026</t>
+          <t>17/03/2026</t>
         </is>
       </c>
       <c r="J63" s="11" t="n">
@@ -5253,19 +5249,19 @@
       </c>
       <c r="L63" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-32074</t>
+          <t>PDMDEP-32095</t>
         </is>
       </c>
       <c r="M63" s="11" t="inlineStr">
         <is>
-          <t>00160409</t>
+          <t>00160474</t>
         </is>
       </c>
       <c r="N63" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O63" s="12" t="n">
-        <v>823.65</v>
+        <v>590.15</v>
+      </c>
+      <c r="O63" s="16" t="n">
+        <v>0</v>
       </c>
       <c r="P63" s="12" t="n">
         <v>0</v>
@@ -5274,12 +5270,12 @@
     <row r="64">
       <c r="A64" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-31996</t>
+          <t>PDMDEP-32065</t>
         </is>
       </c>
       <c r="B64" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">[Commune de Cluny] - Ajout d'un module caisse + Paiement cb </t>
+          <t>[COMMUNE DE MONTBRISON] - Migration GeODP Placier + Ajout Civil Net Finance</t>
         </is>
       </c>
       <c r="C64" s="14" t="inlineStr">
@@ -5289,12 +5285,12 @@
       </c>
       <c r="D64" s="14" t="inlineStr">
         <is>
-          <t>Commune de Cluny</t>
+          <t>COMMUNE DE MONTBRISON</t>
         </is>
       </c>
       <c r="E64" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ajout d'un module caisse + Paiement cb </t>
+          <t>Migration GeODP Placier + Ajout Civil Net Finance</t>
         </is>
       </c>
       <c r="F64" s="14" t="inlineStr">
@@ -5309,12 +5305,12 @@
       </c>
       <c r="H64" s="14" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I64" s="14" t="inlineStr">
         <is>
-          <t>12/03/2026</t>
+          <t>16/03/2026</t>
         </is>
       </c>
       <c r="J64" s="14" t="n">
@@ -5325,19 +5321,19 @@
       </c>
       <c r="L64" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-32002</t>
+          <t>PDMDEP-32074</t>
         </is>
       </c>
       <c r="M64" s="14" t="inlineStr">
         <is>
-          <t>00160078</t>
+          <t>00160409</t>
         </is>
       </c>
       <c r="N64" s="15" t="n">
-        <v>285</v>
-      </c>
-      <c r="O64" s="16" t="n">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="O64" s="15" t="n">
+        <v>823.65</v>
       </c>
       <c r="P64" s="15" t="n">
         <v>0</v>
@@ -5346,32 +5342,32 @@
     <row r="65">
       <c r="A65" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-31967</t>
+          <t>PDMDEP-31996</t>
         </is>
       </c>
       <c r="B65" s="11" t="inlineStr">
         <is>
-          <t>[DEPARTEMENT DU LOT -CD46] - Réinstallation nouveau serveur de la base de test et prod ainsi que Montée de version test et prod</t>
+          <t xml:space="preserve">[Commune de Cluny] - Ajout d'un module caisse + Paiement cb </t>
         </is>
       </c>
       <c r="C65" s="11" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D65" s="11" t="inlineStr">
         <is>
-          <t>DEPARTEMENT DU LOT -CD46</t>
+          <t>Commune de Cluny</t>
         </is>
       </c>
       <c r="E65" s="11" t="inlineStr">
         <is>
-          <t>Réinstallation nouveau serveur de la base de test et prod ainsi que Montée de version test et prod</t>
+          <t xml:space="preserve">Ajout d'un module caisse + Paiement cb </t>
         </is>
       </c>
       <c r="F65" s="11" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G65" s="11" t="inlineStr">
@@ -5386,27 +5382,27 @@
       </c>
       <c r="I65" s="11" t="inlineStr">
         <is>
-          <t>11/03/2026</t>
+          <t>12/03/2026</t>
         </is>
       </c>
       <c r="J65" s="11" t="n">
         <v>6</v>
       </c>
       <c r="K65" s="11" t="n">
-        <v>0.75</v>
+        <v>0</v>
       </c>
       <c r="L65" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-31971</t>
+          <t>PDMDEP-32002</t>
         </is>
       </c>
       <c r="M65" s="11" t="inlineStr">
         <is>
-          <t>00159863</t>
+          <t>00160078</t>
         </is>
       </c>
       <c r="N65" s="12" t="n">
-        <v>1325</v>
+        <v>285</v>
       </c>
       <c r="O65" s="16" t="n">
         <v>0</v>
@@ -5418,12 +5414,12 @@
     <row r="66">
       <c r="A66" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-31947</t>
+          <t>PDMDEP-31967</t>
         </is>
       </c>
       <c r="B66" s="14" t="inlineStr">
         <is>
-          <t>[DEPARTEMENT DE LA MOSELLE (CD 57)] - SSO/LDAP</t>
+          <t>[DEPARTEMENT DU LOT -CD46] - Réinstallation nouveau serveur de la base de test et prod ainsi que Montée de version test et prod</t>
         </is>
       </c>
       <c r="C66" s="14" t="inlineStr">
@@ -5433,12 +5429,12 @@
       </c>
       <c r="D66" s="14" t="inlineStr">
         <is>
-          <t>DEPARTEMENT DE LA MOSELLE (CD 57)</t>
+          <t>DEPARTEMENT DU LOT -CD46</t>
         </is>
       </c>
       <c r="E66" s="14" t="inlineStr">
         <is>
-          <t>SSO/LDAP</t>
+          <t>Réinstallation nouveau serveur de la base de test et prod ainsi que Montée de version test et prod</t>
         </is>
       </c>
       <c r="F66" s="14" t="inlineStr">
@@ -5458,27 +5454,27 @@
       </c>
       <c r="I66" s="14" t="inlineStr">
         <is>
-          <t>10/03/2026</t>
+          <t>11/03/2026</t>
         </is>
       </c>
       <c r="J66" s="14" t="n">
         <v>6</v>
       </c>
       <c r="K66" s="14" t="n">
-        <v>0</v>
+        <v>0.75</v>
       </c>
       <c r="L66" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-31951</t>
+          <t>PDMDEP-31971</t>
         </is>
       </c>
       <c r="M66" s="14" t="inlineStr">
         <is>
-          <t>00159724</t>
+          <t>00159863</t>
         </is>
       </c>
       <c r="N66" s="15" t="n">
-        <v>120</v>
+        <v>1325</v>
       </c>
       <c r="O66" s="16" t="n">
         <v>0</v>
@@ -5490,32 +5486,32 @@
     <row r="67">
       <c r="A67" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-31908</t>
+          <t>PDMDEP-31947</t>
         </is>
       </c>
       <c r="B67" s="11" t="inlineStr">
         <is>
-          <t>[Commune de GUINGAMP] - Migration GEODP Placier 2 + Ajout du paiement CB + Acquisition du TPE PAX A920</t>
+          <t>[DEPARTEMENT DE LA MOSELLE (CD 57)] - SSO/LDAP</t>
         </is>
       </c>
       <c r="C67" s="11" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D67" s="11" t="inlineStr">
         <is>
-          <t>Commune de GUINGAMP</t>
+          <t>DEPARTEMENT DE LA MOSELLE (CD 57)</t>
         </is>
       </c>
       <c r="E67" s="11" t="inlineStr">
         <is>
-          <t>Migration GEODP Placier 2 + Ajout du paiement CB + Acquisition du TPE PAX A920</t>
+          <t>SSO/LDAP</t>
         </is>
       </c>
       <c r="F67" s="11" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G67" s="11" t="inlineStr">
@@ -5525,7 +5521,7 @@
       </c>
       <c r="H67" s="11" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I67" s="11" t="inlineStr">
@@ -5541,16 +5537,16 @@
       </c>
       <c r="L67" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-31917</t>
+          <t>PDMDEP-31951</t>
         </is>
       </c>
       <c r="M67" s="11" t="inlineStr">
         <is>
-          <t>00159608</t>
+          <t>00159724</t>
         </is>
       </c>
       <c r="N67" s="12" t="n">
-        <v>588</v>
+        <v>120</v>
       </c>
       <c r="O67" s="16" t="n">
         <v>0</v>
@@ -5562,12 +5558,12 @@
     <row r="68">
       <c r="A68" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-31812</t>
+          <t>PDMDEP-31908</t>
         </is>
       </c>
       <c r="B68" s="14" t="inlineStr">
         <is>
-          <t>[COMMUNE PROVINS] - Migration V2 classique</t>
+          <t>[Commune de GUINGAMP] - Migration GEODP Placier 2 + Ajout du paiement CB + Acquisition du TPE PAX A920</t>
         </is>
       </c>
       <c r="C68" s="14" t="inlineStr">
@@ -5577,12 +5573,12 @@
       </c>
       <c r="D68" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE PROVINS</t>
+          <t>Commune de GUINGAMP</t>
         </is>
       </c>
       <c r="E68" s="14" t="inlineStr">
         <is>
-          <t>Migration V2 classique</t>
+          <t>Migration GEODP Placier 2 + Ajout du paiement CB + Acquisition du TPE PAX A920</t>
         </is>
       </c>
       <c r="F68" s="14" t="inlineStr">
@@ -5602,29 +5598,29 @@
       </c>
       <c r="I68" s="14" t="inlineStr">
         <is>
-          <t>06/03/2026</t>
+          <t>10/03/2026</t>
         </is>
       </c>
       <c r="J68" s="14" t="n">
         <v>6</v>
       </c>
       <c r="K68" s="14" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L68" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-31821</t>
+          <t>PDMDEP-31917</t>
         </is>
       </c>
       <c r="M68" s="14" t="inlineStr">
         <is>
-          <t>00159471</t>
+          <t>00159608</t>
         </is>
       </c>
       <c r="N68" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O68" s="15" t="n">
+        <v>588</v>
+      </c>
+      <c r="O68" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P68" s="15" t="n">
@@ -5634,27 +5630,27 @@
     <row r="69">
       <c r="A69" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-31649</t>
+          <t>PDMDEP-31812</t>
         </is>
       </c>
       <c r="B69" s="11" t="inlineStr">
         <is>
-          <t>[MAIRIE DE GUILLESTRE] - GeoDP Placier</t>
+          <t>[COMMUNE PROVINS] - Migration V2 classique</t>
         </is>
       </c>
       <c r="C69" s="11" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D69" s="11" t="inlineStr">
         <is>
-          <t>MAIRIE DE GUILLESTRE</t>
+          <t>COMMUNE PROVINS</t>
         </is>
       </c>
       <c r="E69" s="11" t="inlineStr">
         <is>
-          <t>GeoDP Placier</t>
+          <t>Migration V2 classique</t>
         </is>
       </c>
       <c r="F69" s="11" t="inlineStr">
@@ -5669,34 +5665,34 @@
       </c>
       <c r="H69" s="11" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I69" s="11" t="inlineStr">
         <is>
-          <t>27/02/2026</t>
+          <t>06/03/2026</t>
         </is>
       </c>
       <c r="J69" s="11" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K69" s="11" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L69" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-31658</t>
+          <t>PDMDEP-31821</t>
         </is>
       </c>
       <c r="M69" s="11" t="inlineStr">
         <is>
-          <t>00158175</t>
+          <t>00159471</t>
         </is>
       </c>
       <c r="N69" s="12" t="n">
-        <v>203.5</v>
-      </c>
-      <c r="O69" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O69" s="12" t="n">
         <v>0</v>
       </c>
       <c r="P69" s="12" t="n">
@@ -5706,12 +5702,12 @@
     <row r="70">
       <c r="A70" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-31589</t>
+          <t>PDMDEP-31649</t>
         </is>
       </c>
       <c r="B70" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">[COMMUNE DE LEVALLOIS PERRET] - Migration GEODP - 3 MODULES + mise en service export finance </t>
+          <t>[MAIRIE DE GUILLESTRE] - GeoDP Placier</t>
         </is>
       </c>
       <c r="C70" s="14" t="inlineStr">
@@ -5721,12 +5717,12 @@
       </c>
       <c r="D70" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE LEVALLOIS PERRET</t>
+          <t>MAIRIE DE GUILLESTRE</t>
         </is>
       </c>
       <c r="E70" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Migration GEODP - 3 MODULES + mise en service export finance </t>
+          <t>GeoDP Placier</t>
         </is>
       </c>
       <c r="F70" s="14" t="inlineStr">
@@ -5741,12 +5737,12 @@
       </c>
       <c r="H70" s="14" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I70" s="14" t="inlineStr">
         <is>
-          <t>26/02/2026</t>
+          <t>27/02/2026</t>
         </is>
       </c>
       <c r="J70" s="14" t="n">
@@ -5757,16 +5753,16 @@
       </c>
       <c r="L70" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-31596</t>
+          <t>PDMDEP-31658</t>
         </is>
       </c>
       <c r="M70" s="14" t="inlineStr">
         <is>
-          <t>00157967</t>
+          <t>00158175</t>
         </is>
       </c>
       <c r="N70" s="15" t="n">
-        <v>300</v>
+        <v>203.5</v>
       </c>
       <c r="O70" s="16" t="n">
         <v>0</v>
@@ -5778,32 +5774,32 @@
     <row r="71">
       <c r="A71" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-31540</t>
+          <t>PDMDEP-31589</t>
         </is>
       </c>
       <c r="B71" s="11" t="inlineStr">
         <is>
-          <t>[COMMUNE DE MONTELIMAR] - Modélisation LiEx et redevances</t>
+          <t xml:space="preserve">[COMMUNE DE LEVALLOIS PERRET] - Migration GEODP - 3 MODULES + mise en service export finance </t>
         </is>
       </c>
       <c r="C71" s="11" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D71" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE MONTELIMAR</t>
+          <t>COMMUNE DE LEVALLOIS PERRET</t>
         </is>
       </c>
       <c r="E71" s="11" t="inlineStr">
         <is>
-          <t>Modélisation LiEx</t>
+          <t xml:space="preserve">Migration GEODP - 3 MODULES + mise en service export finance </t>
         </is>
       </c>
       <c r="F71" s="11" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G71" s="11" t="inlineStr">
@@ -5813,12 +5809,12 @@
       </c>
       <c r="H71" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I71" s="11" t="inlineStr">
         <is>
-          <t>24/02/2026</t>
+          <t>26/02/2026</t>
         </is>
       </c>
       <c r="J71" s="11" t="n">
@@ -5829,16 +5825,16 @@
       </c>
       <c r="L71" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-31546</t>
+          <t>PDMDEP-31596</t>
         </is>
       </c>
       <c r="M71" s="11" t="inlineStr">
         <is>
-          <t>00157816</t>
+          <t>00157967</t>
         </is>
       </c>
       <c r="N71" s="12" t="n">
-        <v>700</v>
+        <v>300</v>
       </c>
       <c r="O71" s="16" t="n">
         <v>0</v>
@@ -5850,27 +5846,27 @@
     <row r="72">
       <c r="A72" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-31464</t>
+          <t>PDMDEP-31540</t>
         </is>
       </c>
       <c r="B72" s="14" t="inlineStr">
         <is>
-          <t>[CD 17] - Modélisation PV - 2 jours</t>
+          <t>[COMMUNE DE MONTELIMAR] - Modélisation LiEx et redevances</t>
         </is>
       </c>
       <c r="C72" s="14" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D72" s="14" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DE LA CHARENTE MARITIME (CD 17)</t>
+          <t>COMMUNE DE MONTELIMAR</t>
         </is>
       </c>
       <c r="E72" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">2 jours de modélisation - nouveau modèle </t>
+          <t>Modélisation LiEx</t>
         </is>
       </c>
       <c r="F72" s="14" t="inlineStr">
@@ -5890,29 +5886,29 @@
       </c>
       <c r="I72" s="14" t="inlineStr">
         <is>
-          <t>19/02/2026</t>
+          <t>24/02/2026</t>
         </is>
       </c>
       <c r="J72" s="14" t="n">
         <v>7</v>
       </c>
       <c r="K72" s="14" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="L72" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-31468</t>
+          <t>PDMDEP-31546</t>
         </is>
       </c>
       <c r="M72" s="14" t="inlineStr">
         <is>
-          <t>00157346</t>
+          <t>00157816</t>
         </is>
       </c>
       <c r="N72" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O72" s="15" t="n">
+        <v>700</v>
+      </c>
+      <c r="O72" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P72" s="15" t="n">
@@ -5922,32 +5918,32 @@
     <row r="73">
       <c r="A73" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-31351</t>
+          <t>PDMDEP-31464</t>
         </is>
       </c>
       <c r="B73" s="11" t="inlineStr">
         <is>
-          <t>[COMMUNE DE LAISSAC-SEVERAC L'EGLISE] - Migration vers GeoDP V2</t>
+          <t>[CD 17] - Modélisation PV - 2 jours</t>
         </is>
       </c>
       <c r="C73" s="11" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D73" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE LAISSAC-SEVERAC L'EGLISE</t>
+          <t>CONSEIL DEPARTEMENTAL DE LA CHARENTE MARITIME (CD 17)</t>
         </is>
       </c>
       <c r="E73" s="11" t="inlineStr">
         <is>
-          <t>Migration vers GeoDP V2</t>
+          <t xml:space="preserve">2 jours de modélisation - nouveau modèle </t>
         </is>
       </c>
       <c r="F73" s="11" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G73" s="11" t="inlineStr">
@@ -5957,34 +5953,34 @@
       </c>
       <c r="H73" s="11" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I73" s="11" t="inlineStr">
         <is>
-          <t>17/02/2026</t>
+          <t>19/02/2026</t>
         </is>
       </c>
       <c r="J73" s="11" t="n">
         <v>7</v>
       </c>
       <c r="K73" s="11" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="L73" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-31360</t>
+          <t>PDMDEP-31468</t>
         </is>
       </c>
       <c r="M73" s="11" t="inlineStr">
         <is>
-          <t>00157041</t>
+          <t>00157346</t>
         </is>
       </c>
       <c r="N73" s="12" t="n">
-        <v>210</v>
-      </c>
-      <c r="O73" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O73" s="12" t="n">
         <v>0</v>
       </c>
       <c r="P73" s="12" t="n">
@@ -5994,12 +5990,12 @@
     <row r="74">
       <c r="A74" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-31319</t>
+          <t>PDMDEP-31351</t>
         </is>
       </c>
       <c r="B74" s="14" t="inlineStr">
         <is>
-          <t>[COMMUNE DE LARMOR PLAGE] - Migration de GEODP-Placier simple</t>
+          <t>[COMMUNE DE LAISSAC-SEVERAC L'EGLISE] - Migration vers GeoDP V2</t>
         </is>
       </c>
       <c r="C74" s="14" t="inlineStr">
@@ -6009,12 +6005,12 @@
       </c>
       <c r="D74" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE LARMOR PLAGE</t>
+          <t>COMMUNE DE LAISSAC-SEVERAC L'EGLISE</t>
         </is>
       </c>
       <c r="E74" s="14" t="inlineStr">
         <is>
-          <t>Migration de GEODP-Placier simple</t>
+          <t>Migration vers GeoDP V2</t>
         </is>
       </c>
       <c r="F74" s="14" t="inlineStr">
@@ -6045,19 +6041,19 @@
       </c>
       <c r="L74" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-31328</t>
+          <t>PDMDEP-31360</t>
         </is>
       </c>
       <c r="M74" s="14" t="inlineStr">
         <is>
-          <t>00156518</t>
+          <t>00157041</t>
         </is>
       </c>
       <c r="N74" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O74" s="15" t="n">
-        <v>281</v>
+        <v>210</v>
+      </c>
+      <c r="O74" s="16" t="n">
+        <v>0</v>
       </c>
       <c r="P74" s="15" t="n">
         <v>0</v>
@@ -6066,12 +6062,12 @@
     <row r="75">
       <c r="A75" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-31188</t>
+          <t>PDMDEP-31319</t>
         </is>
       </c>
       <c r="B75" s="11" t="inlineStr">
         <is>
-          <t>[COMMUNE D HENDAYE] - Migration 1 activité GEODP2</t>
+          <t>[COMMUNE DE LARMOR PLAGE] - Migration de GEODP-Placier simple</t>
         </is>
       </c>
       <c r="C75" s="11" t="inlineStr">
@@ -6081,12 +6077,12 @@
       </c>
       <c r="D75" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE D HENDAYE</t>
+          <t>COMMUNE DE LARMOR PLAGE</t>
         </is>
       </c>
       <c r="E75" s="11" t="inlineStr">
         <is>
-          <t>Migration 1 activité GEODP2</t>
+          <t>Migration de GEODP-Placier simple</t>
         </is>
       </c>
       <c r="F75" s="11" t="inlineStr">
@@ -6106,7 +6102,7 @@
       </c>
       <c r="I75" s="11" t="inlineStr">
         <is>
-          <t>12/02/2026</t>
+          <t>17/02/2026</t>
         </is>
       </c>
       <c r="J75" s="11" t="n">
@@ -6117,19 +6113,19 @@
       </c>
       <c r="L75" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-31197</t>
+          <t>PDMDEP-31328</t>
         </is>
       </c>
       <c r="M75" s="11" t="inlineStr">
         <is>
-          <t>00156556</t>
+          <t>00156518</t>
         </is>
       </c>
       <c r="N75" s="12" t="n">
-        <v>130</v>
-      </c>
-      <c r="O75" s="16" t="n">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="O75" s="12" t="n">
+        <v>281</v>
       </c>
       <c r="P75" s="12" t="n">
         <v>0</v>
@@ -6138,12 +6134,12 @@
     <row r="76">
       <c r="A76" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-31036</t>
+          <t>PDMDEP-31188</t>
         </is>
       </c>
       <c r="B76" s="14" t="inlineStr">
         <is>
-          <t>[COMMUNE DE SARLAT LA CANEDA] - Migration V2 classique + abo CB</t>
+          <t>[COMMUNE D HENDAYE] - Migration 1 activité GEODP2</t>
         </is>
       </c>
       <c r="C76" s="14" t="inlineStr">
@@ -6153,12 +6149,12 @@
       </c>
       <c r="D76" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE SARLAT LA CANEDA</t>
+          <t>COMMUNE D HENDAYE</t>
         </is>
       </c>
       <c r="E76" s="14" t="inlineStr">
         <is>
-          <t>Migration V2 classique + abo CB</t>
+          <t>Migration 1 activité GEODP2</t>
         </is>
       </c>
       <c r="F76" s="14" t="inlineStr">
@@ -6178,7 +6174,7 @@
       </c>
       <c r="I76" s="14" t="inlineStr">
         <is>
-          <t>10/02/2026</t>
+          <t>12/02/2026</t>
         </is>
       </c>
       <c r="J76" s="14" t="n">
@@ -6189,16 +6185,16 @@
       </c>
       <c r="L76" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-31045</t>
+          <t>PDMDEP-31197</t>
         </is>
       </c>
       <c r="M76" s="14" t="inlineStr">
         <is>
-          <t>00156095</t>
+          <t>00156556</t>
         </is>
       </c>
       <c r="N76" s="15" t="n">
-        <v>255</v>
+        <v>130</v>
       </c>
       <c r="O76" s="16" t="n">
         <v>0</v>
@@ -6210,12 +6206,12 @@
     <row r="77">
       <c r="A77" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-30330</t>
+          <t>PDMDEP-31036</t>
         </is>
       </c>
       <c r="B77" s="11" t="inlineStr">
         <is>
-          <t>[COMMUNE DE ALENCON] - Migration 1 activité GEODP2</t>
+          <t>[COMMUNE DE SARLAT LA CANEDA] - Migration V2 classique + abo CB</t>
         </is>
       </c>
       <c r="C77" s="11" t="inlineStr">
@@ -6225,12 +6221,12 @@
       </c>
       <c r="D77" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE ALENCON</t>
+          <t>COMMUNE DE SARLAT LA CANEDA</t>
         </is>
       </c>
       <c r="E77" s="11" t="inlineStr">
         <is>
-          <t>Migration 1 activité GEODP2</t>
+          <t>Migration V2 classique + abo CB</t>
         </is>
       </c>
       <c r="F77" s="11" t="inlineStr">
@@ -6250,27 +6246,27 @@
       </c>
       <c r="I77" s="11" t="inlineStr">
         <is>
-          <t>28/01/2026</t>
+          <t>10/02/2026</t>
         </is>
       </c>
       <c r="J77" s="11" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="K77" s="11" t="n">
         <v>0</v>
       </c>
       <c r="L77" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-30335</t>
+          <t>PDMDEP-31045</t>
         </is>
       </c>
       <c r="M77" s="11" t="inlineStr">
         <is>
-          <t>00154411</t>
+          <t>00156095</t>
         </is>
       </c>
       <c r="N77" s="12" t="n">
-        <v>140</v>
+        <v>255</v>
       </c>
       <c r="O77" s="16" t="n">
         <v>0</v>
@@ -6282,32 +6278,32 @@
     <row r="78">
       <c r="A78" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-30196</t>
+          <t>PDMDEP-30330</t>
         </is>
       </c>
       <c r="B78" s="14" t="inlineStr">
         <is>
-          <t>[DEPARTEMENT DU MORBIHAN (CD 56)] - Paramétrage interface Pastell</t>
+          <t>[COMMUNE DE ALENCON] - Migration 1 activité GEODP2</t>
         </is>
       </c>
       <c r="C78" s="14" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D78" s="14" t="inlineStr">
         <is>
-          <t>CD56</t>
+          <t>COMMUNE DE ALENCON</t>
         </is>
       </c>
       <c r="E78" s="14" t="inlineStr">
         <is>
-          <t>Paramétrage interface Pastell</t>
+          <t>Migration 1 activité GEODP2</t>
         </is>
       </c>
       <c r="F78" s="14" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G78" s="14" t="inlineStr">
@@ -6317,32 +6313,32 @@
       </c>
       <c r="H78" s="14" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I78" s="14" t="inlineStr">
         <is>
-          <t>21/01/2026</t>
+          <t>28/01/2026</t>
         </is>
       </c>
       <c r="J78" s="14" t="n">
         <v>8</v>
       </c>
       <c r="K78" s="14" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="L78" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-30197</t>
+          <t>PDMDEP-30335</t>
         </is>
       </c>
       <c r="M78" s="14" t="inlineStr">
         <is>
-          <t>00153939</t>
+          <t>00154411</t>
         </is>
       </c>
       <c r="N78" s="15" t="n">
-        <v>690</v>
+        <v>140</v>
       </c>
       <c r="O78" s="16" t="n">
         <v>0</v>
@@ -6354,27 +6350,27 @@
     <row r="79">
       <c r="A79" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-29606</t>
+          <t>PDMDEP-30196</t>
         </is>
       </c>
       <c r="B79" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve"> [BIARRITZ] - Paramétrages complémentaires + Vision</t>
+          <t>[DEPARTEMENT DU MORBIHAN (CD 56)] - Paramétrage interface Pastell</t>
         </is>
       </c>
       <c r="C79" s="11" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D79" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE BIARRITZ</t>
+          <t>CD56</t>
         </is>
       </c>
       <c r="E79" s="11" t="inlineStr">
         <is>
-          <t>Paramétrages complémentaires + Vision</t>
+          <t>Paramétrage interface Pastell</t>
         </is>
       </c>
       <c r="F79" s="11" t="inlineStr">
@@ -6394,29 +6390,29 @@
       </c>
       <c r="I79" s="11" t="inlineStr">
         <is>
-          <t>09/01/2026</t>
+          <t>21/01/2026</t>
         </is>
       </c>
       <c r="J79" s="11" t="n">
         <v>8</v>
       </c>
       <c r="K79" s="11" t="n">
-        <v>0.75</v>
+        <v>1.5</v>
       </c>
       <c r="L79" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-30431</t>
+          <t>PDMDEP-30197</t>
         </is>
       </c>
       <c r="M79" s="11" t="inlineStr">
         <is>
-          <t>00154684</t>
+          <t>00153939</t>
         </is>
       </c>
       <c r="N79" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O79" s="12" t="n">
+        <v>690</v>
+      </c>
+      <c r="O79" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P79" s="12" t="n">
@@ -6477,18 +6473,18 @@
       </c>
       <c r="L80" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-29625</t>
+          <t>PDMDEP-30431</t>
         </is>
       </c>
       <c r="M80" s="14" t="inlineStr">
         <is>
-          <t>00145091</t>
+          <t>00154684</t>
         </is>
       </c>
       <c r="N80" s="15" t="n">
-        <v>187.5</v>
-      </c>
-      <c r="O80" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O80" s="15" t="n">
         <v>0</v>
       </c>
       <c r="P80" s="15" t="n">
@@ -6549,16 +6545,16 @@
       </c>
       <c r="L81" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-29608</t>
+          <t>PDMDEP-29625</t>
         </is>
       </c>
       <c r="M81" s="11" t="inlineStr">
         <is>
-          <t>00152338</t>
+          <t>00145091</t>
         </is>
       </c>
       <c r="N81" s="12" t="n">
-        <v>787.5</v>
+        <v>187.5</v>
       </c>
       <c r="O81" s="16" t="n">
         <v>0</v>
@@ -6570,32 +6566,32 @@
     <row r="82">
       <c r="A82" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-28306</t>
+          <t>PDMDEP-29606</t>
         </is>
       </c>
       <c r="B82" s="14" t="inlineStr">
         <is>
-          <t>Commune de CLAMART - GEODP2 migration</t>
+          <t xml:space="preserve"> [BIARRITZ] - Paramétrages complémentaires + Vision</t>
         </is>
       </c>
       <c r="C82" s="14" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D82" s="14" t="inlineStr">
         <is>
-          <t>Commune de CLAMART</t>
+          <t>COMMUNE DE BIARRITZ</t>
         </is>
       </c>
       <c r="E82" s="14" t="inlineStr">
         <is>
-          <t>Migration V2</t>
+          <t>Paramétrages complémentaires + Vision</t>
         </is>
       </c>
       <c r="F82" s="14" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G82" s="14" t="inlineStr">
@@ -6605,35 +6601,35 @@
       </c>
       <c r="H82" s="14" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I82" s="14" t="inlineStr">
         <is>
-          <t>28/11/2025</t>
+          <t>09/01/2026</t>
         </is>
       </c>
       <c r="J82" s="14" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="K82" s="14" t="n">
-        <v>0</v>
+        <v>0.75</v>
       </c>
       <c r="L82" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-28310</t>
+          <t>PDMDEP-29608</t>
         </is>
       </c>
       <c r="M82" s="14" t="inlineStr">
         <is>
-          <t>00145374</t>
+          <t>00152338</t>
         </is>
       </c>
       <c r="N82" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O82" s="15" t="n">
-        <v>362.5</v>
+        <v>787.5</v>
+      </c>
+      <c r="O82" s="16" t="n">
+        <v>0</v>
       </c>
       <c r="P82" s="15" t="n">
         <v>0</v>
@@ -6642,30 +6638,32 @@
     <row r="83">
       <c r="A83" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-28174</t>
+          <t>PDMDEP-28306</t>
         </is>
       </c>
       <c r="B83" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE BOBIGNY - LITTERALIS</t>
+          <t>Commune de CLAMART - GEODP2 migration</t>
         </is>
       </c>
       <c r="C83" s="11" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D83" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE BOBIGNY</t>
-        </is>
-      </c>
-      <c r="E83" s="11" t="n">
-        <v/>
+          <t>Commune de CLAMART</t>
+        </is>
+      </c>
+      <c r="E83" s="11" t="inlineStr">
+        <is>
+          <t>Migration V2</t>
+        </is>
       </c>
       <c r="F83" s="11" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G83" s="11" t="inlineStr">
@@ -6675,35 +6673,35 @@
       </c>
       <c r="H83" s="11" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I83" s="11" t="inlineStr">
         <is>
-          <t>25/11/2025</t>
+          <t>28/11/2025</t>
         </is>
       </c>
       <c r="J83" s="11" t="n">
         <v>10</v>
       </c>
       <c r="K83" s="11" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="L83" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-28175</t>
+          <t>PDMDEP-28310</t>
         </is>
       </c>
       <c r="M83" s="11" t="inlineStr">
         <is>
-          <t>00145001</t>
+          <t>00145374</t>
         </is>
       </c>
       <c r="N83" s="12" t="n">
         <v>0</v>
       </c>
       <c r="O83" s="12" t="n">
-        <v>0</v>
+        <v>362.5</v>
       </c>
       <c r="P83" s="12" t="n">
         <v>0</v>
@@ -6712,12 +6710,12 @@
     <row r="84">
       <c r="A84" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-28095</t>
+          <t>PDMDEP-28174</t>
         </is>
       </c>
       <c r="B84" s="14" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD91) - LITTERALIS</t>
+          <t>COMMUNE DE BOBIGNY - LITTERALIS</t>
         </is>
       </c>
       <c r="C84" s="14" t="inlineStr">
@@ -6727,13 +6725,11 @@
       </c>
       <c r="D84" s="14" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD 91)</t>
-        </is>
-      </c>
-      <c r="E84" s="14" t="inlineStr">
-        <is>
-          <t>Déploiement Littéralis Expert</t>
-        </is>
+          <t>COMMUNE DE BOBIGNY</t>
+        </is>
+      </c>
+      <c r="E84" s="14" t="n">
+        <v/>
       </c>
       <c r="F84" s="14" t="inlineStr">
         <is>
@@ -6752,23 +6748,23 @@
       </c>
       <c r="I84" s="14" t="inlineStr">
         <is>
-          <t>24/11/2025</t>
+          <t>25/11/2025</t>
         </is>
       </c>
       <c r="J84" s="14" t="n">
         <v>10</v>
       </c>
       <c r="K84" s="14" t="n">
-        <v>0.95</v>
+        <v>2.75</v>
       </c>
       <c r="L84" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-28206</t>
+          <t>PDMDEP-28175</t>
         </is>
       </c>
       <c r="M84" s="14" t="inlineStr">
         <is>
-          <t>00144864</t>
+          <t>00145001</t>
         </is>
       </c>
       <c r="N84" s="15" t="n">
@@ -6835,12 +6831,12 @@
       </c>
       <c r="L85" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-28205</t>
+          <t>PDMDEP-28206</t>
         </is>
       </c>
       <c r="M85" s="11" t="inlineStr">
         <is>
-          <t>00144863</t>
+          <t>00144864</t>
         </is>
       </c>
       <c r="N85" s="12" t="n">
@@ -6907,12 +6903,12 @@
       </c>
       <c r="L86" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-28204</t>
+          <t>PDMDEP-28205</t>
         </is>
       </c>
       <c r="M86" s="14" t="inlineStr">
         <is>
-          <t>00144862</t>
+          <t>00144863</t>
         </is>
       </c>
       <c r="N86" s="15" t="n">
@@ -6979,12 +6975,12 @@
       </c>
       <c r="L87" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-28203</t>
+          <t>PDMDEP-28204</t>
         </is>
       </c>
       <c r="M87" s="11" t="inlineStr">
         <is>
-          <t>00144860</t>
+          <t>00144862</t>
         </is>
       </c>
       <c r="N87" s="12" t="n">
@@ -7051,18 +7047,18 @@
       </c>
       <c r="L88" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-28202</t>
+          <t>PDMDEP-28203</t>
         </is>
       </c>
       <c r="M88" s="14" t="inlineStr">
         <is>
-          <t>00144857</t>
+          <t>00144860</t>
         </is>
       </c>
       <c r="N88" s="15" t="n">
-        <v>1320</v>
-      </c>
-      <c r="O88" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O88" s="15" t="n">
         <v>0</v>
       </c>
       <c r="P88" s="15" t="n">
@@ -7072,12 +7068,12 @@
     <row r="89">
       <c r="A89" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-27634</t>
+          <t>PDMDEP-28095</t>
         </is>
       </c>
       <c r="B89" s="11" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DU VAUCLUSE (CD 84) - Direction des Routes - LITTERALIS</t>
+          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD91) - LITTERALIS</t>
         </is>
       </c>
       <c r="C89" s="11" t="inlineStr">
@@ -7087,11 +7083,13 @@
       </c>
       <c r="D89" s="11" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DU VAUCLUSE (CD 84) - Direction des Routes</t>
-        </is>
-      </c>
-      <c r="E89" s="11" t="n">
-        <v/>
+          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD 91)</t>
+        </is>
+      </c>
+      <c r="E89" s="11" t="inlineStr">
+        <is>
+          <t>Déploiement Littéralis Expert</t>
+        </is>
       </c>
       <c r="F89" s="11" t="inlineStr">
         <is>
@@ -7105,34 +7103,34 @@
       </c>
       <c r="H89" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I89" s="11" t="inlineStr">
         <is>
-          <t>21/11/2025</t>
+          <t>24/11/2025</t>
         </is>
       </c>
       <c r="J89" s="11" t="n">
         <v>10</v>
       </c>
       <c r="K89" s="11" t="n">
-        <v>0.5</v>
+        <v>0.95</v>
       </c>
       <c r="L89" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-27642</t>
+          <t>PDMDEP-28202</t>
         </is>
       </c>
       <c r="M89" s="11" t="inlineStr">
         <is>
-          <t>00143935</t>
+          <t>00144857</t>
         </is>
       </c>
       <c r="N89" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O89" s="12" t="n">
+        <v>1320</v>
+      </c>
+      <c r="O89" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P89" s="12" t="n">
@@ -7142,12 +7140,12 @@
     <row r="90">
       <c r="A90" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-26831</t>
+          <t>PDMDEP-27634</t>
         </is>
       </c>
       <c r="B90" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve"> [CD74] - Maj Ref carto dans le cadre de la maintenance</t>
+          <t>CONSEIL DEPARTEMENTAL DU VAUCLUSE (CD 84) - Direction des Routes - LITTERALIS</t>
         </is>
       </c>
       <c r="C90" s="14" t="inlineStr">
@@ -7157,34 +7155,48 @@
       </c>
       <c r="D90" s="14" t="inlineStr">
         <is>
-          <t>CD74</t>
-        </is>
-      </c>
-      <c r="E90" s="14" t="inlineStr">
-        <is>
-          <t>MAJ carto</t>
-        </is>
-      </c>
-      <c r="F90" s="14" t="inlineStr"/>
+          <t>CONSEIL DEPARTEMENTAL DU VAUCLUSE (CD 84) - Direction des Routes</t>
+        </is>
+      </c>
+      <c r="E90" s="14" t="n">
+        <v/>
+      </c>
+      <c r="F90" s="14" t="inlineStr">
+        <is>
+          <t>LITTERALIS</t>
+        </is>
+      </c>
       <c r="G90" s="14" t="inlineStr">
         <is>
-          <t>Maintenance</t>
-        </is>
-      </c>
-      <c r="H90" s="14" t="inlineStr"/>
+          <t>Projet</t>
+        </is>
+      </c>
+      <c r="H90" s="14" t="inlineStr">
+        <is>
+          <t>Vente additionnelle</t>
+        </is>
+      </c>
       <c r="I90" s="14" t="inlineStr">
         <is>
-          <t>05/11/2025</t>
+          <t>21/11/2025</t>
         </is>
       </c>
       <c r="J90" s="14" t="n">
         <v>10</v>
       </c>
       <c r="K90" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="L90" s="14" t="inlineStr"/>
-      <c r="M90" s="14" t="inlineStr"/>
+        <v>0.5</v>
+      </c>
+      <c r="L90" s="14" t="inlineStr">
+        <is>
+          <t>PDMDEP-27642</t>
+        </is>
+      </c>
+      <c r="M90" s="14" t="inlineStr">
+        <is>
+          <t>00143935</t>
+        </is>
+      </c>
       <c r="N90" s="15" t="n">
         <v>0</v>
       </c>
@@ -7198,12 +7210,12 @@
     <row r="91">
       <c r="A91" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-26813</t>
+          <t>PDMDEP-26831</t>
         </is>
       </c>
       <c r="B91" s="11" t="inlineStr">
         <is>
-          <t>[VILLEJUIF] - Litteralis Modèle facture + param Civil Net</t>
+          <t xml:space="preserve"> [CD74] - Maj Ref carto dans le cadre de la maintenance</t>
         </is>
       </c>
       <c r="C91" s="11" t="inlineStr">
@@ -7213,48 +7225,34 @@
       </c>
       <c r="D91" s="11" t="inlineStr">
         <is>
-          <t>VILLE DE VILLEJUIF</t>
-        </is>
-      </c>
-      <c r="E91" s="11" t="n">
-        <v/>
-      </c>
-      <c r="F91" s="11" t="inlineStr">
-        <is>
-          <t>LITTERALIS</t>
-        </is>
-      </c>
+          <t>CD74</t>
+        </is>
+      </c>
+      <c r="E91" s="11" t="inlineStr">
+        <is>
+          <t>MAJ carto</t>
+        </is>
+      </c>
+      <c r="F91" s="11" t="inlineStr"/>
       <c r="G91" s="11" t="inlineStr">
         <is>
-          <t>Projet</t>
-        </is>
-      </c>
-      <c r="H91" s="11" t="inlineStr">
-        <is>
-          <t>Vente additionnelle</t>
-        </is>
-      </c>
+          <t>Maintenance</t>
+        </is>
+      </c>
+      <c r="H91" s="11" t="inlineStr"/>
       <c r="I91" s="11" t="inlineStr">
         <is>
-          <t>04/11/2025</t>
+          <t>05/11/2025</t>
         </is>
       </c>
       <c r="J91" s="11" t="n">
         <v>10</v>
       </c>
       <c r="K91" s="11" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="L91" s="11" t="inlineStr">
-        <is>
-          <t>PDMDEP-26814</t>
-        </is>
-      </c>
-      <c r="M91" s="11" t="inlineStr">
-        <is>
-          <t>00142941</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="L91" s="11" t="inlineStr"/>
+      <c r="M91" s="11" t="inlineStr"/>
       <c r="N91" s="12" t="n">
         <v>0</v>
       </c>
@@ -7268,12 +7266,12 @@
     <row r="92">
       <c r="A92" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-24866</t>
+          <t>PDMDEP-26813</t>
         </is>
       </c>
       <c r="B92" s="14" t="inlineStr">
         <is>
-          <t>[MAUGES SUR LOIRE] - LITTERALIS</t>
+          <t>[VILLEJUIF] - Litteralis Modèle facture + param Civil Net</t>
         </is>
       </c>
       <c r="C92" s="14" t="inlineStr">
@@ -7283,7 +7281,7 @@
       </c>
       <c r="D92" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE NOUVELLE DE MAUGES SUR LOIRE</t>
+          <t>VILLE DE VILLEJUIF</t>
         </is>
       </c>
       <c r="E92" s="14" t="n">
@@ -7301,34 +7299,34 @@
       </c>
       <c r="H92" s="14" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I92" s="14" t="inlineStr">
         <is>
-          <t>16/10/2025</t>
+          <t>04/11/2025</t>
         </is>
       </c>
       <c r="J92" s="14" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="K92" s="14" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="L92" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-27017</t>
+          <t>PDMDEP-26814</t>
         </is>
       </c>
       <c r="M92" s="14" t="inlineStr">
         <is>
-          <t>00141205</t>
+          <t>00142941</t>
         </is>
       </c>
       <c r="N92" s="15" t="n">
-        <v>1212</v>
-      </c>
-      <c r="O92" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O92" s="15" t="n">
         <v>0</v>
       </c>
       <c r="P92" s="15" t="n">
@@ -7338,12 +7336,12 @@
     <row r="93">
       <c r="A93" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-23918</t>
+          <t>PDMDEP-24866</t>
         </is>
       </c>
       <c r="B93" s="11" t="inlineStr">
         <is>
-          <t>[CD94 - VAL DE MARNE] - Déploiement Littéralis Expert</t>
+          <t>[MAUGES SUR LOIRE] - LITTERALIS</t>
         </is>
       </c>
       <c r="C93" s="11" t="inlineStr">
@@ -7353,7 +7351,7 @@
       </c>
       <c r="D93" s="11" t="inlineStr">
         <is>
-          <t>DEPARTEMENT DU VAL DE MARNE (CD 94)</t>
+          <t>COMMUNE NOUVELLE DE MAUGES SUR LOIRE</t>
         </is>
       </c>
       <c r="E93" s="11" t="n">
@@ -7376,44 +7374,44 @@
       </c>
       <c r="I93" s="11" t="inlineStr">
         <is>
-          <t>26/08/2025</t>
+          <t>16/10/2025</t>
         </is>
       </c>
       <c r="J93" s="11" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="K93" s="11" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="L93" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-28055</t>
+          <t>PDMDEP-27017</t>
         </is>
       </c>
       <c r="M93" s="11" t="inlineStr">
         <is>
-          <t>499132</t>
+          <t>00141205</t>
         </is>
       </c>
       <c r="N93" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O93" s="12" t="n">
-        <v>416.188</v>
+        <v>1212</v>
+      </c>
+      <c r="O93" s="16" t="n">
+        <v>0</v>
       </c>
       <c r="P93" s="12" t="n">
-        <v>277.46</v>
+        <v>0</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-23750</t>
+          <t>PDMDEP-23918</t>
         </is>
       </c>
       <c r="B94" s="14" t="inlineStr">
         <is>
-          <t>MEL - LITTERALIS x AXION</t>
+          <t>[CD94 - VAL DE MARNE] - Déploiement Littéralis Expert</t>
         </is>
       </c>
       <c r="C94" s="14" t="inlineStr">
@@ -7423,13 +7421,11 @@
       </c>
       <c r="D94" s="14" t="inlineStr">
         <is>
-          <t>METROPOLE EUROPEENNE DE LILLE</t>
-        </is>
-      </c>
-      <c r="E94" s="14" t="inlineStr">
-        <is>
-          <t>AXION</t>
-        </is>
+          <t>DEPARTEMENT DU VAL DE MARNE (CD 94)</t>
+        </is>
+      </c>
+      <c r="E94" s="14" t="n">
+        <v/>
       </c>
       <c r="F94" s="14" t="inlineStr">
         <is>
@@ -7438,54 +7434,54 @@
       </c>
       <c r="G94" s="14" t="inlineStr">
         <is>
-          <t>Rework</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H94" s="14" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I94" s="14" t="inlineStr">
         <is>
-          <t>08/08/2025</t>
+          <t>26/08/2025</t>
         </is>
       </c>
       <c r="J94" s="14" t="n">
         <v>13</v>
       </c>
       <c r="K94" s="14" t="n">
-        <v>0.25</v>
+        <v>1.5</v>
       </c>
       <c r="L94" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-27033</t>
+          <t>PDMDEP-28055</t>
         </is>
       </c>
       <c r="M94" s="14" t="inlineStr">
         <is>
-          <t>497304</t>
+          <t>499132</t>
         </is>
       </c>
       <c r="N94" s="15" t="n">
         <v>0</v>
       </c>
       <c r="O94" s="15" t="n">
-        <v>0</v>
+        <v>416.188</v>
       </c>
       <c r="P94" s="15" t="n">
-        <v>0</v>
+        <v>277.46</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-23323</t>
+          <t>PDMDEP-23750</t>
         </is>
       </c>
       <c r="B95" s="11" t="inlineStr">
         <is>
-          <t>[BAGNOLET] - LITTERALIS projet</t>
+          <t>MEL - LITTERALIS x AXION</t>
         </is>
       </c>
       <c r="C95" s="11" t="inlineStr">
@@ -7495,11 +7491,13 @@
       </c>
       <c r="D95" s="11" t="inlineStr">
         <is>
-          <t>VILLE DE BAGNOLET</t>
-        </is>
-      </c>
-      <c r="E95" s="11" t="n">
-        <v/>
+          <t>METROPOLE EUROPEENNE DE LILLE</t>
+        </is>
+      </c>
+      <c r="E95" s="11" t="inlineStr">
+        <is>
+          <t>AXION</t>
+        </is>
       </c>
       <c r="F95" s="11" t="inlineStr">
         <is>
@@ -7508,33 +7506,33 @@
       </c>
       <c r="G95" s="11" t="inlineStr">
         <is>
-          <t>Projet</t>
+          <t>Rework</t>
         </is>
       </c>
       <c r="H95" s="11" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I95" s="11" t="inlineStr">
         <is>
-          <t>21/07/2025</t>
+          <t>08/08/2025</t>
         </is>
       </c>
       <c r="J95" s="11" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="K95" s="11" t="n">
-        <v>1.5</v>
+        <v>0.25</v>
       </c>
       <c r="L95" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-27570</t>
+          <t>PDMDEP-27033</t>
         </is>
       </c>
       <c r="M95" s="11" t="inlineStr">
         <is>
-          <t>493613</t>
+          <t>497304</t>
         </is>
       </c>
       <c r="N95" s="12" t="n">
@@ -7550,12 +7548,12 @@
     <row r="96">
       <c r="A96" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-22757</t>
+          <t>PDMDEP-23323</t>
         </is>
       </c>
       <c r="B96" s="14" t="inlineStr">
         <is>
-          <t>BREST METROPOLE - DEPLOIEMENT DE LITTERALIS EXPERT</t>
+          <t>[BAGNOLET] - LITTERALIS projet</t>
         </is>
       </c>
       <c r="C96" s="14" t="inlineStr">
@@ -7565,7 +7563,7 @@
       </c>
       <c r="D96" s="14" t="inlineStr">
         <is>
-          <t>BREST METROPOLE</t>
+          <t>VILLE DE BAGNOLET</t>
         </is>
       </c>
       <c r="E96" s="14" t="n">
@@ -7588,23 +7586,23 @@
       </c>
       <c r="I96" s="14" t="inlineStr">
         <is>
-          <t>01/07/2025</t>
+          <t>21/07/2025</t>
         </is>
       </c>
       <c r="J96" s="14" t="n">
         <v>14</v>
       </c>
       <c r="K96" s="14" t="n">
-        <v>0.06</v>
+        <v>1.5</v>
       </c>
       <c r="L96" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-30081</t>
+          <t>PDMDEP-27570</t>
         </is>
       </c>
       <c r="M96" s="14" t="inlineStr">
         <is>
-          <t>00152628</t>
+          <t>493613</t>
         </is>
       </c>
       <c r="N96" s="15" t="n">
@@ -7669,12 +7667,12 @@
       </c>
       <c r="L97" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-30080</t>
+          <t>PDMDEP-30081</t>
         </is>
       </c>
       <c r="M97" s="11" t="inlineStr">
         <is>
-          <t>00152635</t>
+          <t>00152628</t>
         </is>
       </c>
       <c r="N97" s="12" t="n">
@@ -7705,7 +7703,7 @@
       </c>
       <c r="D98" s="14" t="inlineStr">
         <is>
-          <t>Brest Métropole</t>
+          <t>BREST METROPOLE</t>
         </is>
       </c>
       <c r="E98" s="14" t="n">
@@ -7739,12 +7737,12 @@
       </c>
       <c r="L98" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-30079</t>
+          <t>PDMDEP-30080</t>
         </is>
       </c>
       <c r="M98" s="14" t="inlineStr">
         <is>
-          <t>00152632</t>
+          <t>00152635</t>
         </is>
       </c>
       <c r="N98" s="15" t="n">
@@ -7775,7 +7773,7 @@
       </c>
       <c r="D99" s="11" t="inlineStr">
         <is>
-          <t>BREST METROPOLE</t>
+          <t>Brest Métropole</t>
         </is>
       </c>
       <c r="E99" s="11" t="n">
@@ -7809,12 +7807,12 @@
       </c>
       <c r="L99" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-27365</t>
+          <t>PDMDEP-30079</t>
         </is>
       </c>
       <c r="M99" s="11" t="inlineStr">
         <is>
-          <t>491593</t>
+          <t>00152632</t>
         </is>
       </c>
       <c r="N99" s="12" t="n">
@@ -7830,12 +7828,12 @@
     <row r="100">
       <c r="A100" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-22126</t>
+          <t>PDMDEP-22757</t>
         </is>
       </c>
       <c r="B100" s="14" t="inlineStr">
         <is>
-          <t>[MEL Lille] - LITTERALIS - 3 jours de modélisation / param / accomp (21h)</t>
+          <t>BREST METROPOLE - DEPLOIEMENT DE LITTERALIS EXPERT</t>
         </is>
       </c>
       <c r="C100" s="14" t="inlineStr">
@@ -7845,7 +7843,7 @@
       </c>
       <c r="D100" s="14" t="inlineStr">
         <is>
-          <t>Métropole Européenne de Lille</t>
+          <t>BREST METROPOLE</t>
         </is>
       </c>
       <c r="E100" s="14" t="n">
@@ -7863,28 +7861,28 @@
       </c>
       <c r="H100" s="14" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I100" s="14" t="inlineStr">
         <is>
-          <t>02/06/2025</t>
+          <t>01/07/2025</t>
         </is>
       </c>
       <c r="J100" s="14" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="K100" s="14" t="n">
-        <v>0.25</v>
+        <v>0.06</v>
       </c>
       <c r="L100" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-27368</t>
+          <t>PDMDEP-27365</t>
         </is>
       </c>
       <c r="M100" s="14" t="inlineStr">
         <is>
-          <t>484163</t>
+          <t>491593</t>
         </is>
       </c>
       <c r="N100" s="15" t="n">
@@ -7900,22 +7898,22 @@
     <row r="101">
       <c r="A101" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-21661</t>
+          <t>PDMDEP-22126</t>
         </is>
       </c>
       <c r="B101" s="11" t="inlineStr">
         <is>
-          <t>[Grand Dax] - Pastell</t>
+          <t>[MEL Lille] - LITTERALIS - 3 jours de modélisation / param / accomp (21h)</t>
         </is>
       </c>
       <c r="C101" s="11" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D101" s="11" t="inlineStr">
         <is>
-          <t>GRAND DAX</t>
+          <t>Métropole Européenne de Lille</t>
         </is>
       </c>
       <c r="E101" s="11" t="n">
@@ -7938,29 +7936,29 @@
       </c>
       <c r="I101" s="11" t="inlineStr">
         <is>
-          <t>07/05/2025</t>
+          <t>02/06/2025</t>
         </is>
       </c>
       <c r="J101" s="11" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="K101" s="11" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="L101" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-27373</t>
+          <t>PDMDEP-27368</t>
         </is>
       </c>
       <c r="M101" s="11" t="inlineStr">
         <is>
-          <t>466234</t>
+          <t>484163</t>
         </is>
       </c>
       <c r="N101" s="12" t="n">
-        <v>401</v>
-      </c>
-      <c r="O101" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O101" s="12" t="n">
         <v>0</v>
       </c>
       <c r="P101" s="12" t="n">
@@ -7970,12 +7968,12 @@
     <row r="102">
       <c r="A102" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-21222</t>
+          <t>PDMDEP-21661</t>
         </is>
       </c>
       <c r="B102" s="14" t="inlineStr">
         <is>
-          <t>[Issy les Moulineaux] Litteralis Expert</t>
+          <t>[Grand Dax] - Pastell</t>
         </is>
       </c>
       <c r="C102" s="14" t="inlineStr">
@@ -7985,7 +7983,7 @@
       </c>
       <c r="D102" s="14" t="inlineStr">
         <is>
-          <t>ISSY LES MOULINEAUX</t>
+          <t>GRAND DAX</t>
         </is>
       </c>
       <c r="E102" s="14" t="n">
@@ -8003,34 +8001,34 @@
       </c>
       <c r="H102" s="14" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I102" s="14" t="inlineStr">
         <is>
-          <t>23/04/2025</t>
+          <t>07/05/2025</t>
         </is>
       </c>
       <c r="J102" s="14" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="K102" s="14" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="L102" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-28036</t>
+          <t>PDMDEP-27373</t>
         </is>
       </c>
       <c r="M102" s="14" t="inlineStr">
         <is>
-          <t>483799</t>
+          <t>466234</t>
         </is>
       </c>
       <c r="N102" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O102" s="15" t="n">
+        <v>401</v>
+      </c>
+      <c r="O102" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P102" s="15" t="n">
@@ -8040,22 +8038,22 @@
     <row r="103">
       <c r="A103" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-21165</t>
+          <t>PDMDEP-21222</t>
         </is>
       </c>
       <c r="B103" s="11" t="inlineStr">
         <is>
-          <t>[Montreuil] Mise à jour carto (SaaS)</t>
+          <t>[Issy les Moulineaux] Litteralis Expert</t>
         </is>
       </c>
       <c r="C103" s="11" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D103" s="11" t="inlineStr">
         <is>
-          <t>MONTREUIL</t>
+          <t>ISSY LES MOULINEAUX</t>
         </is>
       </c>
       <c r="E103" s="11" t="n">
@@ -8073,28 +8071,28 @@
       </c>
       <c r="H103" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I103" s="11" t="inlineStr">
         <is>
-          <t>18/04/2025</t>
+          <t>23/04/2025</t>
         </is>
       </c>
       <c r="J103" s="11" t="n">
         <v>17</v>
       </c>
       <c r="K103" s="11" t="n">
-        <v>1</v>
+        <v>4.25</v>
       </c>
       <c r="L103" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-28035</t>
+          <t>PDMDEP-28036</t>
         </is>
       </c>
       <c r="M103" s="11" t="inlineStr">
         <is>
-          <t>468660</t>
+          <t>483799</t>
         </is>
       </c>
       <c r="N103" s="12" t="n">
@@ -8110,22 +8108,22 @@
     <row r="104">
       <c r="A104" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-20907</t>
+          <t>PDMDEP-21165</t>
         </is>
       </c>
       <c r="B104" s="14" t="inlineStr">
         <is>
-          <t>[Saint-Pierre (Réunion)] Accompagnement modélisation AME Littéralis Expert</t>
+          <t>[Montreuil] Mise à jour carto (SaaS)</t>
         </is>
       </c>
       <c r="C104" s="14" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D104" s="14" t="inlineStr">
         <is>
-          <t>SAINT PIERRE (LA REUNION)</t>
+          <t>MONTREUIL</t>
         </is>
       </c>
       <c r="E104" s="14" t="n">
@@ -8148,29 +8146,29 @@
       </c>
       <c r="I104" s="14" t="inlineStr">
         <is>
-          <t>14/04/2025</t>
+          <t>18/04/2025</t>
         </is>
       </c>
       <c r="J104" s="14" t="n">
         <v>17</v>
       </c>
       <c r="K104" s="14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L104" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-28034</t>
+          <t>PDMDEP-28035</t>
         </is>
       </c>
       <c r="M104" s="14" t="inlineStr">
         <is>
-          <t>475575</t>
+          <t>468660</t>
         </is>
       </c>
       <c r="N104" s="15" t="n">
-        <v>230</v>
-      </c>
-      <c r="O104" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O104" s="15" t="n">
         <v>0</v>
       </c>
       <c r="P104" s="15" t="n">
@@ -8180,12 +8178,12 @@
     <row r="105">
       <c r="A105" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-19909</t>
+          <t>PDMDEP-20907</t>
         </is>
       </c>
       <c r="B105" s="11" t="inlineStr">
         <is>
-          <t>[CD 29] Interface Pastell</t>
+          <t>[Saint-Pierre (Réunion)] Accompagnement modélisation AME Littéralis Expert</t>
         </is>
       </c>
       <c r="C105" s="11" t="inlineStr">
@@ -8195,7 +8193,7 @@
       </c>
       <c r="D105" s="11" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DU FINISTERE (CD29)</t>
+          <t>SAINT PIERRE (LA REUNION)</t>
         </is>
       </c>
       <c r="E105" s="11" t="n">
@@ -8218,29 +8216,29 @@
       </c>
       <c r="I105" s="11" t="inlineStr">
         <is>
-          <t>11/03/2025</t>
+          <t>14/04/2025</t>
         </is>
       </c>
       <c r="J105" s="11" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="K105" s="11" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="L105" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-27568</t>
+          <t>PDMDEP-28034</t>
         </is>
       </c>
       <c r="M105" s="11" t="inlineStr">
         <is>
-          <t>471958</t>
+          <t>475575</t>
         </is>
       </c>
       <c r="N105" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O105" s="12" t="n">
+        <v>230</v>
+      </c>
+      <c r="O105" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P105" s="12" t="n">
@@ -8250,22 +8248,22 @@
     <row r="106">
       <c r="A106" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-19558</t>
+          <t>PDMDEP-19909</t>
         </is>
       </c>
       <c r="B106" s="14" t="inlineStr">
         <is>
-          <t>[VILLEFONTAINE] - Litteralis Expert SAAS</t>
+          <t>[CD 29] Interface Pastell</t>
         </is>
       </c>
       <c r="C106" s="14" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D106" s="14" t="inlineStr">
         <is>
-          <t>VILLEFONTAINE</t>
+          <t>CONSEIL DEPARTEMENTAL DU FINISTERE (CD29)</t>
         </is>
       </c>
       <c r="E106" s="14" t="n">
@@ -8283,28 +8281,28 @@
       </c>
       <c r="H106" s="14" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I106" s="14" t="inlineStr">
         <is>
-          <t>28/02/2025</t>
+          <t>11/03/2025</t>
         </is>
       </c>
       <c r="J106" s="14" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="K106" s="14" t="n">
         <v>0.5</v>
       </c>
       <c r="L106" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-28215</t>
+          <t>PDMDEP-27568</t>
         </is>
       </c>
       <c r="M106" s="14" t="inlineStr">
         <is>
-          <t>458306</t>
+          <t>471958</t>
         </is>
       </c>
       <c r="N106" s="15" t="n">
@@ -8369,12 +8367,12 @@
       </c>
       <c r="L107" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-28214</t>
+          <t>PDMDEP-28215</t>
         </is>
       </c>
       <c r="M107" s="11" t="inlineStr">
         <is>
-          <t>458286</t>
+          <t>458306</t>
         </is>
       </c>
       <c r="N107" s="12" t="n">
@@ -8390,12 +8388,12 @@
     <row r="108">
       <c r="A108" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-18241</t>
+          <t>PDMDEP-19558</t>
         </is>
       </c>
       <c r="B108" s="14" t="inlineStr">
         <is>
-          <t>[CD74 - HAUTE SAVOIE] - Interface LiEx Maj Ref BG</t>
+          <t>[VILLEFONTAINE] - Litteralis Expert SAAS</t>
         </is>
       </c>
       <c r="C108" s="14" t="inlineStr">
@@ -8405,7 +8403,7 @@
       </c>
       <c r="D108" s="14" t="inlineStr">
         <is>
-          <t>CD 74 - HAUTE SAVOIE</t>
+          <t>VILLEFONTAINE</t>
         </is>
       </c>
       <c r="E108" s="14" t="n">
@@ -8418,27 +8416,35 @@
       </c>
       <c r="G108" s="14" t="inlineStr">
         <is>
-          <t>Rework</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H108" s="14" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I108" s="14" t="inlineStr">
         <is>
-          <t>20/12/2024</t>
+          <t>28/02/2025</t>
         </is>
       </c>
       <c r="J108" s="14" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="K108" s="14" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="L108" s="14" t="inlineStr"/>
-      <c r="M108" s="14" t="inlineStr"/>
+        <v>0.5</v>
+      </c>
+      <c r="L108" s="14" t="inlineStr">
+        <is>
+          <t>PDMDEP-28214</t>
+        </is>
+      </c>
+      <c r="M108" s="14" t="inlineStr">
+        <is>
+          <t>458286</t>
+        </is>
+      </c>
       <c r="N108" s="15" t="n">
         <v>0</v>
       </c>
@@ -8452,22 +8458,22 @@
     <row r="109">
       <c r="A109" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-18240</t>
+          <t>PDMDEP-18241</t>
         </is>
       </c>
       <c r="B109" s="11" t="inlineStr">
         <is>
-          <t>[BIARRITZ] - Projet Littéralis Expert (Cmde1 - Mise en service - abo)</t>
+          <t>[CD74 - HAUTE SAVOIE] - Interface LiEx Maj Ref BG</t>
         </is>
       </c>
       <c r="C109" s="11" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D109" s="11" t="inlineStr">
         <is>
-          <t>Biarritz</t>
+          <t>CD 74 - HAUTE SAVOIE</t>
         </is>
       </c>
       <c r="E109" s="11" t="n">
@@ -8485,7 +8491,7 @@
       </c>
       <c r="H109" s="11" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I109" s="11" t="inlineStr">
@@ -8497,7 +8503,7 @@
         <v>21</v>
       </c>
       <c r="K109" s="11" t="n">
-        <v>3.08</v>
+        <v>5.5</v>
       </c>
       <c r="L109" s="11" t="inlineStr"/>
       <c r="M109" s="11" t="inlineStr"/>
@@ -8514,22 +8520,22 @@
     <row r="110">
       <c r="A110" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-18115</t>
+          <t>PDMDEP-18240</t>
         </is>
       </c>
       <c r="B110" s="14" t="inlineStr">
         <is>
-          <t>[Bischwiller] Migration + Pax + M2M</t>
+          <t>[BIARRITZ] - Projet Littéralis Expert (Cmde1 - Mise en service - abo)</t>
         </is>
       </c>
       <c r="C110" s="14" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D110" s="14" t="inlineStr">
         <is>
-          <t>BISCHWILLER</t>
+          <t>Biarritz</t>
         </is>
       </c>
       <c r="E110" s="14" t="n">
@@ -8537,44 +8543,36 @@
       </c>
       <c r="F110" s="14" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G110" s="14" t="inlineStr">
         <is>
-          <t>Projet</t>
+          <t>Rework</t>
         </is>
       </c>
       <c r="H110" s="14" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I110" s="14" t="inlineStr">
         <is>
-          <t>17/12/2024</t>
+          <t>20/12/2024</t>
         </is>
       </c>
       <c r="J110" s="14" t="n">
         <v>21</v>
       </c>
       <c r="K110" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="L110" s="14" t="inlineStr">
-        <is>
-          <t>PDMDEP-28019</t>
-        </is>
-      </c>
-      <c r="M110" s="14" t="inlineStr">
-        <is>
-          <t>455151</t>
-        </is>
-      </c>
+        <v>4.83</v>
+      </c>
+      <c r="L110" s="14" t="inlineStr"/>
+      <c r="M110" s="14" t="inlineStr"/>
       <c r="N110" s="15" t="n">
-        <v>240</v>
-      </c>
-      <c r="O110" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O110" s="15" t="n">
         <v>0</v>
       </c>
       <c r="P110" s="15" t="n">
@@ -8584,22 +8582,22 @@
     <row r="111">
       <c r="A111" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-18037</t>
+          <t>PDMDEP-18115</t>
         </is>
       </c>
       <c r="B111" s="11" t="inlineStr">
         <is>
-          <t>[LE PERREUX SUR MARNE] Modélisation/Paramétrage 2J civil net finances</t>
+          <t>[Bischwiller] Migration + Pax + M2M</t>
         </is>
       </c>
       <c r="C111" s="11" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D111" s="11" t="inlineStr">
         <is>
-          <t>LE PERREUX SUR MARNE</t>
+          <t>BISCHWILLER</t>
         </is>
       </c>
       <c r="E111" s="11" t="n">
@@ -8607,7 +8605,7 @@
       </c>
       <c r="F111" s="11" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G111" s="11" t="inlineStr">
@@ -8617,12 +8615,12 @@
       </c>
       <c r="H111" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I111" s="11" t="inlineStr">
         <is>
-          <t>12/12/2024</t>
+          <t>17/12/2024</t>
         </is>
       </c>
       <c r="J111" s="11" t="n">
@@ -8633,16 +8631,16 @@
       </c>
       <c r="L111" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-28023</t>
+          <t>PDMDEP-28019</t>
         </is>
       </c>
       <c r="M111" s="11" t="inlineStr">
         <is>
-          <t>454387</t>
+          <t>455151</t>
         </is>
       </c>
       <c r="N111" s="12" t="n">
-        <v>557.145</v>
+        <v>240</v>
       </c>
       <c r="O111" s="16" t="n">
         <v>0</v>
@@ -8654,22 +8652,22 @@
     <row r="112">
       <c r="A112" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-14118</t>
+          <t>PDMDEP-18037</t>
         </is>
       </c>
       <c r="B112" s="14" t="inlineStr">
         <is>
-          <t>[SURESNES] Interface FAST-Parapheur</t>
+          <t>[LE PERREUX SUR MARNE] Modélisation/Paramétrage 2J civil net finances</t>
         </is>
       </c>
       <c r="C112" s="14" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D112" s="14" t="inlineStr">
         <is>
-          <t>Suresnes</t>
+          <t>LE PERREUX SUR MARNE</t>
         </is>
       </c>
       <c r="E112" s="14" t="n">
@@ -8682,7 +8680,7 @@
       </c>
       <c r="G112" s="14" t="inlineStr">
         <is>
-          <t>Rework</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H112" s="14" t="inlineStr">
@@ -8692,21 +8690,29 @@
       </c>
       <c r="I112" s="14" t="inlineStr">
         <is>
-          <t>01/02/2024</t>
+          <t>12/12/2024</t>
         </is>
       </c>
       <c r="J112" s="14" t="n">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="K112" s="14" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="L112" s="14" t="inlineStr"/>
-      <c r="M112" s="14" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="L112" s="14" t="inlineStr">
+        <is>
+          <t>PDMDEP-28023</t>
+        </is>
+      </c>
+      <c r="M112" s="14" t="inlineStr">
+        <is>
+          <t>454387</t>
+        </is>
+      </c>
       <c r="N112" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O112" s="15" t="n">
+        <v>557.145</v>
+      </c>
+      <c r="O112" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P112" s="15" t="n">
@@ -8716,12 +8722,12 @@
     <row r="113">
       <c r="A113" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-13128</t>
+          <t>PDMDEP-14118</t>
         </is>
       </c>
       <c r="B113" s="11" t="inlineStr">
         <is>
-          <t>[VALENCIENNES] Littéralis Prime - RAF FAST PARAPHEUR - Déjà facturé</t>
+          <t>[SURESNES] Interface FAST-Parapheur</t>
         </is>
       </c>
       <c r="C113" s="11" t="inlineStr">
@@ -8731,7 +8737,7 @@
       </c>
       <c r="D113" s="11" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Suresnes</t>
         </is>
       </c>
       <c r="E113" s="11" t="n">
@@ -8749,19 +8755,19 @@
       </c>
       <c r="H113" s="11" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I113" s="11" t="inlineStr">
         <is>
-          <t>30/10/2023</t>
+          <t>01/02/2024</t>
         </is>
       </c>
       <c r="J113" s="11" t="n">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="K113" s="11" t="n">
-        <v>3.58</v>
+        <v>0.5</v>
       </c>
       <c r="L113" s="11" t="inlineStr"/>
       <c r="M113" s="11" t="inlineStr"/>
@@ -8778,22 +8784,22 @@
     <row r="114">
       <c r="A114" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-12747</t>
+          <t>PDMDEP-13128</t>
         </is>
       </c>
       <c r="B114" s="14" t="inlineStr">
         <is>
-          <t>[FOUGERES] ARPEGE</t>
+          <t>[VALENCIENNES] Littéralis Prime - RAF FAST PARAPHEUR - Déjà facturé</t>
         </is>
       </c>
       <c r="C114" s="14" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D114" s="14" t="inlineStr">
         <is>
-          <t>FOUGERES</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="E114" s="14" t="n">
@@ -8806,35 +8812,27 @@
       </c>
       <c r="G114" s="14" t="inlineStr">
         <is>
-          <t>Projet</t>
+          <t>Rework</t>
         </is>
       </c>
       <c r="H114" s="14" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I114" s="14" t="inlineStr">
         <is>
-          <t>26/09/2023</t>
+          <t>30/10/2023</t>
         </is>
       </c>
       <c r="J114" s="14" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="K114" s="14" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="L114" s="14" t="inlineStr">
-        <is>
-          <t>PDMDEP-27990</t>
-        </is>
-      </c>
-      <c r="M114" s="14" t="inlineStr">
-        <is>
-          <t>406296</t>
-        </is>
-      </c>
+        <v>3.58</v>
+      </c>
+      <c r="L114" s="14" t="inlineStr"/>
+      <c r="M114" s="14" t="inlineStr"/>
       <c r="N114" s="15" t="n">
         <v>0</v>
       </c>
@@ -8848,22 +8846,22 @@
     <row r="115">
       <c r="A115" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-12708</t>
+          <t>PDMDEP-12747</t>
         </is>
       </c>
       <c r="B115" s="11" t="inlineStr">
         <is>
-          <t>[CD56 - MORBIHAN] LITTERALIS EXPERT</t>
+          <t>[FOUGERES] ARPEGE</t>
         </is>
       </c>
       <c r="C115" s="11" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D115" s="11" t="inlineStr">
         <is>
-          <t>CD 56 MORBIHAN</t>
+          <t>FOUGERES</t>
         </is>
       </c>
       <c r="E115" s="11" t="n">
@@ -8876,23 +8874,35 @@
       </c>
       <c r="G115" s="11" t="inlineStr">
         <is>
-          <t>Rework</t>
-        </is>
-      </c>
-      <c r="H115" s="11" t="inlineStr"/>
+          <t>Projet</t>
+        </is>
+      </c>
+      <c r="H115" s="11" t="inlineStr">
+        <is>
+          <t>Vente additionnelle</t>
+        </is>
+      </c>
       <c r="I115" s="11" t="inlineStr">
         <is>
-          <t>22/09/2023</t>
+          <t>26/09/2023</t>
         </is>
       </c>
       <c r="J115" s="11" t="n">
         <v>36</v>
       </c>
       <c r="K115" s="11" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="L115" s="11" t="inlineStr"/>
-      <c r="M115" s="11" t="inlineStr"/>
+        <v>1.5</v>
+      </c>
+      <c r="L115" s="11" t="inlineStr">
+        <is>
+          <t>PDMDEP-27990</t>
+        </is>
+      </c>
+      <c r="M115" s="11" t="inlineStr">
+        <is>
+          <t>406296</t>
+        </is>
+      </c>
       <c r="N115" s="12" t="n">
         <v>0</v>
       </c>
@@ -8906,24 +8916,26 @@
     <row r="116">
       <c r="A116" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-11477</t>
+          <t>PDMDEP-12708</t>
         </is>
       </c>
       <c r="B116" s="14" t="inlineStr">
         <is>
-          <t>[MONTPELLIER MMM - Module AC] LITTERALIS EXPERT</t>
-        </is>
-      </c>
-      <c r="C116" s="14" t="inlineStr"/>
+          <t>[CD56 - MORBIHAN] LITTERALIS EXPERT</t>
+        </is>
+      </c>
+      <c r="C116" s="14" t="inlineStr">
+        <is>
+          <t>Remy VINCENT</t>
+        </is>
+      </c>
       <c r="D116" s="14" t="inlineStr">
         <is>
-          <t>MONTPELLIER MMM</t>
-        </is>
-      </c>
-      <c r="E116" s="14" t="inlineStr">
-        <is>
-          <t>Déploiement Module AC</t>
-        </is>
+          <t>CD 56 MORBIHAN</t>
+        </is>
+      </c>
+      <c r="E116" s="14" t="n">
+        <v/>
       </c>
       <c r="F116" s="14" t="inlineStr">
         <is>
@@ -8935,21 +8947,17 @@
           <t>Rework</t>
         </is>
       </c>
-      <c r="H116" s="14" t="inlineStr">
-        <is>
-          <t>Nouveau déploiement</t>
-        </is>
-      </c>
+      <c r="H116" s="14" t="inlineStr"/>
       <c r="I116" s="14" t="inlineStr">
         <is>
-          <t>03/09/2023</t>
+          <t>22/09/2023</t>
         </is>
       </c>
       <c r="J116" s="14" t="n">
         <v>36</v>
       </c>
       <c r="K116" s="14" t="n">
-        <v>2.75</v>
+        <v>0.75</v>
       </c>
       <c r="L116" s="14" t="inlineStr"/>
       <c r="M116" s="14" t="inlineStr"/>
@@ -8966,89 +8974,149 @@
     <row r="117">
       <c r="A117" s="10" t="inlineStr">
         <is>
-          <t>PSC-1270</t>
+          <t>PDMDEP-11477</t>
         </is>
       </c>
       <c r="B117" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE CASTELNAUDARY</t>
+          <t>[MONTPELLIER MMM - Module AC] LITTERALIS EXPERT</t>
         </is>
       </c>
       <c r="C117" s="11" t="inlineStr"/>
       <c r="D117" s="11" t="inlineStr">
         <is>
+          <t>MONTPELLIER MMM</t>
+        </is>
+      </c>
+      <c r="E117" s="11" t="inlineStr">
+        <is>
+          <t>Déploiement Module AC</t>
+        </is>
+      </c>
+      <c r="F117" s="11" t="inlineStr">
+        <is>
+          <t>LITTERALIS</t>
+        </is>
+      </c>
+      <c r="G117" s="11" t="inlineStr">
+        <is>
+          <t>Rework</t>
+        </is>
+      </c>
+      <c r="H117" s="11" t="inlineStr">
+        <is>
+          <t>Nouveau déploiement</t>
+        </is>
+      </c>
+      <c r="I117" s="11" t="inlineStr">
+        <is>
+          <t>03/09/2023</t>
+        </is>
+      </c>
+      <c r="J117" s="11" t="n">
+        <v>36</v>
+      </c>
+      <c r="K117" s="11" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="L117" s="11" t="inlineStr"/>
+      <c r="M117" s="11" t="inlineStr"/>
+      <c r="N117" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O117" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="P117" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="13" t="inlineStr">
+        <is>
+          <t>PSC-1270</t>
+        </is>
+      </c>
+      <c r="B118" s="14" t="inlineStr">
+        <is>
           <t>COMMUNE DE CASTELNAUDARY</t>
         </is>
       </c>
-      <c r="E117" s="11" t="inlineStr"/>
-      <c r="F117" s="11" t="inlineStr">
+      <c r="C118" s="14" t="inlineStr"/>
+      <c r="D118" s="14" t="inlineStr">
+        <is>
+          <t>COMMUNE DE CASTELNAUDARY</t>
+        </is>
+      </c>
+      <c r="E118" s="14" t="inlineStr"/>
+      <c r="F118" s="14" t="inlineStr">
         <is>
           <t>LITTERALIS</t>
         </is>
       </c>
-      <c r="G117" s="11" t="inlineStr">
+      <c r="G118" s="14" t="inlineStr">
         <is>
           <t>Projet</t>
         </is>
       </c>
-      <c r="H117" s="11" t="inlineStr"/>
-      <c r="I117" s="11" t="inlineStr">
+      <c r="H118" s="14" t="inlineStr"/>
+      <c r="I118" s="14" t="inlineStr">
         <is>
           <t>19/05/2026</t>
         </is>
       </c>
-      <c r="J117" s="11" t="n">
+      <c r="J118" s="14" t="n">
         <v>4</v>
       </c>
-      <c r="K117" s="11" t="n">
+      <c r="K118" s="14" t="n">
         <v>3</v>
       </c>
-      <c r="L117" s="11" t="inlineStr">
+      <c r="L118" s="14" t="inlineStr">
         <is>
           <t>PDMDEP-33362</t>
         </is>
       </c>
-      <c r="M117" s="11" t="inlineStr">
+      <c r="M118" s="14" t="inlineStr">
         <is>
           <t>00167140</t>
         </is>
       </c>
-      <c r="N117" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O117" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="P117" s="12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="118">
-      <c r="A118" s="17" t="inlineStr">
+      <c r="N118" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O118" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="P118" s="15" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="17" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B118" s="17" t="inlineStr"/>
-      <c r="C118" s="17" t="inlineStr"/>
-      <c r="D118" s="17" t="inlineStr"/>
-      <c r="E118" s="17" t="inlineStr"/>
-      <c r="F118" s="17" t="inlineStr"/>
-      <c r="G118" s="17" t="inlineStr"/>
-      <c r="H118" s="17" t="inlineStr"/>
-      <c r="I118" s="17" t="inlineStr"/>
-      <c r="J118" s="17" t="inlineStr"/>
-      <c r="K118" s="17" t="inlineStr"/>
-      <c r="L118" s="17" t="inlineStr"/>
-      <c r="M118" s="17" t="inlineStr"/>
-      <c r="N118" s="18" t="n">
+      <c r="B119" s="17" t="inlineStr"/>
+      <c r="C119" s="17" t="inlineStr"/>
+      <c r="D119" s="17" t="inlineStr"/>
+      <c r="E119" s="17" t="inlineStr"/>
+      <c r="F119" s="17" t="inlineStr"/>
+      <c r="G119" s="17" t="inlineStr"/>
+      <c r="H119" s="17" t="inlineStr"/>
+      <c r="I119" s="17" t="inlineStr"/>
+      <c r="J119" s="17" t="inlineStr"/>
+      <c r="K119" s="17" t="inlineStr"/>
+      <c r="L119" s="17" t="inlineStr"/>
+      <c r="M119" s="17" t="inlineStr"/>
+      <c r="N119" s="18" t="n">
         <v>47526.995</v>
       </c>
-      <c r="O118" s="18" t="n">
-        <v>17574.178</v>
-      </c>
-      <c r="P118" s="18" t="n">
-        <v>178.31</v>
+      <c r="O119" s="18" t="n">
+        <v>17672.678</v>
+      </c>
+      <c r="P119" s="18" t="n">
+        <v>174.87</v>
       </c>
     </row>
   </sheetData>
@@ -9167,6 +9235,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A115" r:id="rId111"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A116" r:id="rId112"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A117" r:id="rId113"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A118" r:id="rId114"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -9924,16 +9993,16 @@
         </is>
       </c>
       <c r="B5" s="14" t="n">
-        <v>53.17</v>
+        <v>53.92</v>
       </c>
       <c r="C5" s="14" t="n">
-        <v>16.42</v>
+        <v>18.17</v>
       </c>
       <c r="D5" s="14" t="n">
         <v>7.25</v>
       </c>
       <c r="E5" s="14" t="n">
-        <v>76.83</v>
+        <v>79.33</v>
       </c>
       <c r="F5" s="14" t="n">
         <v>11.17</v>
@@ -9943,7 +10012,7 @@
       </c>
       <c r="H5" s="21" t="inlineStr">
         <is>
-          <t>11.8%</t>
+          <t>12.2%</t>
         </is>
       </c>
     </row>
@@ -9985,7 +10054,7 @@
         </is>
       </c>
       <c r="B8" s="23" t="n">
-        <v>53.75</v>
+        <v>54.5</v>
       </c>
     </row>
   </sheetData>
@@ -10070,10 +10139,10 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>393393</v>
+        <v>393294</v>
       </c>
       <c r="C5" s="24" t="n">
-        <v>167739</v>
+        <v>167641</v>
       </c>
       <c r="D5" s="24" t="n">
         <v>225654</v>
@@ -10120,10 +10189,10 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>230128</v>
+        <v>230029</v>
       </c>
       <c r="C7" s="26" t="n">
-        <v>106174</v>
+        <v>106075</v>
       </c>
       <c r="D7" s="26" t="n">
         <v>123954</v>
@@ -10149,7 +10218,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I19"/>
+  <dimension ref="A1:I20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -10173,7 +10242,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Épics créées ce mois — 12 commande(s)</t>
+          <t>Épics créées ce mois — 13 commande(s)</t>
         </is>
       </c>
     </row>
@@ -10228,22 +10297,22 @@
     <row r="5">
       <c r="A5" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-35606</t>
+          <t>PDMDEP-35636</t>
         </is>
       </c>
       <c r="B5" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-35597</t>
+          <t>PDMDEP-35627</t>
         </is>
       </c>
       <c r="C5" s="14" t="inlineStr">
         <is>
-          <t>09/09/2026</t>
+          <t>10/09/2026</t>
         </is>
       </c>
       <c r="D5" s="14" t="inlineStr">
         <is>
-          <t>COMMUNAUTE URBAINE ANGERS LOIRE METROPOLE</t>
+          <t>COMMUNE D'ANNEMASSE</t>
         </is>
       </c>
       <c r="E5" s="14" t="inlineStr">
@@ -10263,7 +10332,7 @@
       </c>
       <c r="H5" s="14" t="inlineStr">
         <is>
-          <t>00181049</t>
+          <t>00181182</t>
         </is>
       </c>
       <c r="I5" s="25" t="n">
@@ -10273,22 +10342,22 @@
     <row r="6">
       <c r="A6" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-35587</t>
+          <t>PDMDEP-35606</t>
         </is>
       </c>
       <c r="B6" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-35583</t>
+          <t>PDMDEP-35597</t>
         </is>
       </c>
       <c r="C6" s="11" t="inlineStr">
         <is>
-          <t>08/09/2026</t>
+          <t>09/09/2026</t>
         </is>
       </c>
       <c r="D6" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE CHAMBERY</t>
+          <t>COMMUNAUTE URBAINE ANGERS LOIRE METROPOLE</t>
         </is>
       </c>
       <c r="E6" s="11" t="inlineStr">
@@ -10298,7 +10367,7 @@
       </c>
       <c r="F6" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="G6" s="11" t="inlineStr">
@@ -10308,7 +10377,7 @@
       </c>
       <c r="H6" s="11" t="inlineStr">
         <is>
-          <t>00180931</t>
+          <t>00181049</t>
         </is>
       </c>
       <c r="I6" s="26" t="n">
@@ -10318,22 +10387,22 @@
     <row r="7">
       <c r="A7" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-35532</t>
+          <t>PDMDEP-35587</t>
         </is>
       </c>
       <c r="B7" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-35518</t>
+          <t>PDMDEP-35583</t>
         </is>
       </c>
       <c r="C7" s="14" t="inlineStr">
         <is>
-          <t>07/09/2026</t>
+          <t>08/09/2026</t>
         </is>
       </c>
       <c r="D7" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE PRIVAS</t>
+          <t>COMMUNE DE CHAMBERY</t>
         </is>
       </c>
       <c r="E7" s="14" t="inlineStr">
@@ -10343,34 +10412,42 @@
       </c>
       <c r="F7" s="14" t="inlineStr">
         <is>
-          <t>Migration</t>
-        </is>
-      </c>
-      <c r="G7" s="14" t="inlineStr"/>
-      <c r="H7" s="14" t="inlineStr"/>
+          <t>Vente additionnelle</t>
+        </is>
+      </c>
+      <c r="G7" s="14" t="inlineStr">
+        <is>
+          <t>Services</t>
+        </is>
+      </c>
+      <c r="H7" s="14" t="inlineStr">
+        <is>
+          <t>00180931</t>
+        </is>
+      </c>
       <c r="I7" s="25" t="n">
-        <v>1450</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-35478</t>
+          <t>PDMDEP-35532</t>
         </is>
       </c>
       <c r="B8" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-35469</t>
+          <t>PDMDEP-35518</t>
         </is>
       </c>
       <c r="C8" s="11" t="inlineStr">
         <is>
-          <t>04/09/2026</t>
+          <t>07/09/2026</t>
         </is>
       </c>
       <c r="D8" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE VENCE</t>
+          <t>COMMUNE DE PRIVAS</t>
         </is>
       </c>
       <c r="E8" s="11" t="inlineStr">
@@ -10383,39 +10460,31 @@
           <t>Migration</t>
         </is>
       </c>
-      <c r="G8" s="11" t="inlineStr">
-        <is>
-          <t>Services</t>
-        </is>
-      </c>
-      <c r="H8" s="11" t="inlineStr">
-        <is>
-          <t>00180643</t>
-        </is>
-      </c>
+      <c r="G8" s="11" t="inlineStr"/>
+      <c r="H8" s="11" t="inlineStr"/>
       <c r="I8" s="26" t="n">
-        <v>6285</v>
+        <v>1450</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-35410</t>
+          <t>PDMDEP-35478</t>
         </is>
       </c>
       <c r="B9" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-35401</t>
+          <t>PDMDEP-35469</t>
         </is>
       </c>
       <c r="C9" s="14" t="inlineStr">
         <is>
-          <t>01/09/2026</t>
+          <t>04/09/2026</t>
         </is>
       </c>
       <c r="D9" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Commune de Saint Cast le Guildo </t>
+          <t>COMMUNE DE VENCE</t>
         </is>
       </c>
       <c r="E9" s="14" t="inlineStr">
@@ -10435,22 +10504,22 @@
       </c>
       <c r="H9" s="14" t="inlineStr">
         <is>
-          <t>00173074</t>
+          <t>00180643</t>
         </is>
       </c>
       <c r="I9" s="25" t="n">
-        <v>1200</v>
+        <v>6285</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-35392</t>
+          <t>PDMDEP-35410</t>
         </is>
       </c>
       <c r="B10" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-35385</t>
+          <t>PDMDEP-35401</t>
         </is>
       </c>
       <c r="C10" s="11" t="inlineStr">
@@ -10460,7 +10529,7 @@
       </c>
       <c r="D10" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE ROUEN</t>
+          <t xml:space="preserve">Commune de Saint Cast le Guildo </t>
         </is>
       </c>
       <c r="E10" s="11" t="inlineStr">
@@ -10480,42 +10549,42 @@
       </c>
       <c r="H10" s="11" t="inlineStr">
         <is>
-          <t>00179700</t>
+          <t>00173074</t>
         </is>
       </c>
       <c r="I10" s="26" t="n">
-        <v>28915.01</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-35622</t>
+          <t>PDMDEP-35392</t>
         </is>
       </c>
       <c r="B11" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-35618</t>
+          <t>PDMDEP-35385</t>
         </is>
       </c>
       <c r="C11" s="14" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>01/09/2026</t>
         </is>
       </c>
       <c r="D11" s="14" t="inlineStr">
         <is>
-          <t>Commune de la Roche-sur-Yon</t>
+          <t>COMMUNE DE ROUEN</t>
         </is>
       </c>
       <c r="E11" s="14" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="F11" s="14" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="G11" s="14" t="inlineStr">
@@ -10525,32 +10594,32 @@
       </c>
       <c r="H11" s="14" t="inlineStr">
         <is>
-          <t>00181123</t>
+          <t>00179700</t>
         </is>
       </c>
       <c r="I11" s="25" t="n">
-        <v>0</v>
+        <v>28915.01</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-35576</t>
+          <t>PDMDEP-35622</t>
         </is>
       </c>
       <c r="B12" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-35572</t>
+          <t>PDMDEP-35618</t>
         </is>
       </c>
       <c r="C12" s="11" t="inlineStr">
         <is>
-          <t>08/09/2026</t>
+          <t>10/09/2026</t>
         </is>
       </c>
       <c r="D12" s="11" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DE L'ARIEGE (CD 09)</t>
+          <t>Commune de la Roche-sur-Yon</t>
         </is>
       </c>
       <c r="E12" s="11" t="inlineStr">
@@ -10570,7 +10639,7 @@
       </c>
       <c r="H12" s="11" t="inlineStr">
         <is>
-          <t>00180891</t>
+          <t>00181123</t>
         </is>
       </c>
       <c r="I12" s="26" t="n">
@@ -10580,12 +10649,12 @@
     <row r="13">
       <c r="A13" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-35567</t>
+          <t>PDMDEP-35576</t>
         </is>
       </c>
       <c r="B13" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-35561</t>
+          <t>PDMDEP-35572</t>
         </is>
       </c>
       <c r="C13" s="14" t="inlineStr">
@@ -10595,7 +10664,7 @@
       </c>
       <c r="D13" s="14" t="inlineStr">
         <is>
-          <t>DEPARTEMENT DU MORBIHAN (CD 56)</t>
+          <t>CONSEIL DEPARTEMENTAL DE L'ARIEGE (CD 09)</t>
         </is>
       </c>
       <c r="E13" s="14" t="inlineStr">
@@ -10615,7 +10684,7 @@
       </c>
       <c r="H13" s="14" t="inlineStr">
         <is>
-          <t>00180878</t>
+          <t>00180891</t>
         </is>
       </c>
       <c r="I13" s="25" t="n">
@@ -10625,22 +10694,22 @@
     <row r="14">
       <c r="A14" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-35511</t>
+          <t>PDMDEP-35567</t>
         </is>
       </c>
       <c r="B14" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-35504</t>
+          <t>PDMDEP-35561</t>
         </is>
       </c>
       <c r="C14" s="11" t="inlineStr">
         <is>
-          <t>07/09/2026</t>
+          <t>08/09/2026</t>
         </is>
       </c>
       <c r="D14" s="11" t="inlineStr">
         <is>
-          <t>[TEST]</t>
+          <t>DEPARTEMENT DU MORBIHAN (CD 56)</t>
         </is>
       </c>
       <c r="E14" s="11" t="inlineStr">
@@ -10650,7 +10719,7 @@
       </c>
       <c r="F14" s="11" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="G14" s="11" t="inlineStr">
@@ -10660,7 +10729,7 @@
       </c>
       <c r="H14" s="11" t="inlineStr">
         <is>
-          <t>0015489263</t>
+          <t>00180878</t>
         </is>
       </c>
       <c r="I14" s="26" t="n">
@@ -10670,22 +10739,22 @@
     <row r="15">
       <c r="A15" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-35464</t>
+          <t>PDMDEP-35511</t>
         </is>
       </c>
       <c r="B15" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-35460</t>
+          <t>PDMDEP-35504</t>
         </is>
       </c>
       <c r="C15" s="14" t="inlineStr">
         <is>
-          <t>04/09/2026</t>
+          <t>07/09/2026</t>
         </is>
       </c>
       <c r="D15" s="14" t="inlineStr">
         <is>
-          <t>DEPARTEMENT DE LA CHARENTE (CD 16)</t>
+          <t>[TEST]</t>
         </is>
       </c>
       <c r="E15" s="14" t="inlineStr">
@@ -10695,7 +10764,7 @@
       </c>
       <c r="F15" s="14" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="G15" s="14" t="inlineStr">
@@ -10705,83 +10774,107 @@
       </c>
       <c r="H15" s="14" t="inlineStr">
         <is>
-          <t>00180631</t>
+          <t>0015489263</t>
         </is>
       </c>
       <c r="I15" s="25" t="n">
-        <v>455</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="11" t="inlineStr">
         <is>
+          <t>PDMDEP-35464</t>
+        </is>
+      </c>
+      <c r="B16" s="11" t="inlineStr">
+        <is>
+          <t>PDMDEP-35460</t>
+        </is>
+      </c>
+      <c r="C16" s="11" t="inlineStr">
+        <is>
+          <t>04/09/2026</t>
+        </is>
+      </c>
+      <c r="D16" s="11" t="inlineStr">
+        <is>
+          <t>DEPARTEMENT DE LA CHARENTE (CD 16)</t>
+        </is>
+      </c>
+      <c r="E16" s="11" t="inlineStr">
+        <is>
+          <t>LITTERALIS</t>
+        </is>
+      </c>
+      <c r="F16" s="11" t="inlineStr">
+        <is>
+          <t>Vente additionnelle</t>
+        </is>
+      </c>
+      <c r="G16" s="11" t="inlineStr">
+        <is>
+          <t>Services</t>
+        </is>
+      </c>
+      <c r="H16" s="11" t="inlineStr">
+        <is>
+          <t>00180631</t>
+        </is>
+      </c>
+      <c r="I16" s="26" t="n">
+        <v>455</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="14" t="inlineStr">
+        <is>
           <t>PDMDEP-35439</t>
         </is>
       </c>
-      <c r="B16" s="11" t="inlineStr">
+      <c r="B17" s="14" t="inlineStr">
         <is>
           <t>PDMDEP-35435</t>
         </is>
       </c>
-      <c r="C16" s="11" t="inlineStr">
+      <c r="C17" s="14" t="inlineStr">
         <is>
           <t>03/09/2026</t>
         </is>
       </c>
-      <c r="D16" s="11" t="inlineStr">
+      <c r="D17" s="14" t="inlineStr">
         <is>
           <t>DEPARTEMENT DES HAUTS-DE-SEINE</t>
         </is>
       </c>
-      <c r="E16" s="11" t="inlineStr">
+      <c r="E17" s="14" t="inlineStr">
         <is>
           <t>LITTERALIS</t>
         </is>
       </c>
-      <c r="F16" s="11" t="inlineStr">
+      <c r="F17" s="14" t="inlineStr">
         <is>
           <t>Vente additionnelle</t>
         </is>
       </c>
-      <c r="G16" s="11" t="inlineStr">
+      <c r="G17" s="14" t="inlineStr">
         <is>
           <t>Services</t>
         </is>
       </c>
-      <c r="H16" s="11" t="inlineStr">
+      <c r="H17" s="14" t="inlineStr">
         <is>
           <t>00180506</t>
         </is>
       </c>
-      <c r="I16" s="26" t="n">
+      <c r="I17" s="25" t="n">
         <v>3974</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="17" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="B17" s="17" t="n"/>
-      <c r="C17" s="17" t="n"/>
-      <c r="D17" s="17" t="n"/>
-      <c r="E17" s="17" t="n"/>
-      <c r="F17" s="17" t="n"/>
-      <c r="G17" s="17" t="n"/>
-      <c r="H17" s="17" t="inlineStr">
-        <is>
-          <t>12 commande(s)</t>
-        </is>
-      </c>
-      <c r="I17" s="24" t="n">
-        <v>42279</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="17" t="inlineStr">
         <is>
-          <t>dont Littéralis</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="B18" s="17" t="n"/>
@@ -10792,17 +10885,17 @@
       <c r="G18" s="17" t="n"/>
       <c r="H18" s="17" t="inlineStr">
         <is>
-          <t>6 commande(s)</t>
+          <t>13 commande(s)</t>
         </is>
       </c>
       <c r="I18" s="24" t="n">
-        <v>4429</v>
+        <v>42279</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="17" t="inlineStr">
         <is>
-          <t>dont GEODP</t>
+          <t>dont Littéralis</t>
         </is>
       </c>
       <c r="B19" s="17" t="n"/>
@@ -10817,6 +10910,27 @@
         </is>
       </c>
       <c r="I19" s="24" t="n">
+        <v>4429</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="17" t="inlineStr">
+        <is>
+          <t>dont GEODP</t>
+        </is>
+      </c>
+      <c r="B20" s="17" t="n"/>
+      <c r="C20" s="17" t="n"/>
+      <c r="D20" s="17" t="n"/>
+      <c r="E20" s="17" t="n"/>
+      <c r="F20" s="17" t="n"/>
+      <c r="G20" s="17" t="n"/>
+      <c r="H20" s="17" t="inlineStr">
+        <is>
+          <t>7 commande(s)</t>
+        </is>
+      </c>
+      <c r="I20" s="24" t="n">
         <v>37850</v>
       </c>
     </row>

--- a/jira_export_2026-09-10.xlsx
+++ b/jira_export_2026-09-10.xlsx
@@ -815,7 +815,7 @@
     <row r="16" ht="26" customHeight="1">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>172 h</t>
+          <t>180 h</t>
         </is>
       </c>
       <c r="B16" s="7" t="n"/>
@@ -829,7 +829,7 @@
       <c r="F16" s="7" t="n"/>
       <c r="G16" s="8" t="inlineStr">
         <is>
-          <t>45.3%</t>
+          <t>47.2%</t>
         </is>
       </c>
       <c r="H16" s="7" t="n"/>
@@ -900,7 +900,7 @@
       <c r="F25" s="7" t="n"/>
       <c r="G25" s="6" t="inlineStr">
         <is>
-          <t>276</t>
+          <t>277</t>
         </is>
       </c>
       <c r="H25" s="7" t="n"/>
@@ -1169,7 +1169,7 @@
         <v>0</v>
       </c>
       <c r="K6" s="14" t="n">
-        <v>1</v>
+        <v>2.5</v>
       </c>
       <c r="L6" s="14" t="inlineStr">
         <is>
@@ -1661,7 +1661,7 @@
         <v>1</v>
       </c>
       <c r="K13" s="11" t="n">
-        <v>5.5</v>
+        <v>7</v>
       </c>
       <c r="L13" s="11" t="inlineStr"/>
       <c r="M13" s="11" t="inlineStr"/>
@@ -5965,7 +5965,7 @@
         <v>7</v>
       </c>
       <c r="K73" s="11" t="n">
-        <v>0.5</v>
+        <v>0.75</v>
       </c>
       <c r="L73" s="11" t="inlineStr">
         <is>
@@ -8565,7 +8565,7 @@
         <v>21</v>
       </c>
       <c r="K110" s="14" t="n">
-        <v>4.83</v>
+        <v>5.08</v>
       </c>
       <c r="L110" s="14" t="inlineStr"/>
       <c r="M110" s="14" t="inlineStr"/>
@@ -9116,7 +9116,7 @@
         <v>17672.678</v>
       </c>
       <c r="P119" s="18" t="n">
-        <v>174.87</v>
+        <v>169.02</v>
       </c>
     </row>
   </sheetData>
@@ -9993,26 +9993,26 @@
         </is>
       </c>
       <c r="B5" s="14" t="n">
-        <v>53.92</v>
+        <v>55.67</v>
       </c>
       <c r="C5" s="14" t="n">
-        <v>18.17</v>
+        <v>18.42</v>
       </c>
       <c r="D5" s="14" t="n">
-        <v>7.25</v>
+        <v>8.75</v>
       </c>
       <c r="E5" s="14" t="n">
-        <v>79.33</v>
+        <v>82.83</v>
       </c>
       <c r="F5" s="14" t="n">
-        <v>11.17</v>
+        <v>14.17</v>
       </c>
       <c r="G5" s="14" t="n">
         <v>652.05</v>
       </c>
       <c r="H5" s="21" t="inlineStr">
         <is>
-          <t>12.2%</t>
+          <t>12.7%</t>
         </is>
       </c>
     </row>
@@ -10054,7 +10054,7 @@
         </is>
       </c>
       <c r="B8" s="23" t="n">
-        <v>54.5</v>
+        <v>55.25</v>
       </c>
     </row>
   </sheetData>
@@ -10139,10 +10139,10 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>393294</v>
+        <v>395029</v>
       </c>
       <c r="C5" s="24" t="n">
-        <v>167641</v>
+        <v>169376</v>
       </c>
       <c r="D5" s="24" t="n">
         <v>225654</v>
@@ -10164,10 +10164,10 @@
         </is>
       </c>
       <c r="B6" s="25" t="n">
-        <v>163265</v>
+        <v>165000</v>
       </c>
       <c r="C6" s="25" t="n">
-        <v>61566</v>
+        <v>63301</v>
       </c>
       <c r="D6" s="25" t="n">
         <v>101700</v>
@@ -10218,7 +10218,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I20"/>
+  <dimension ref="A1:I21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -10242,7 +10242,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Épics créées ce mois — 13 commande(s)</t>
+          <t>Épics créées ce mois — 14 commande(s)</t>
         </is>
       </c>
     </row>
@@ -10604,12 +10604,12 @@
     <row r="12">
       <c r="A12" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-35622</t>
+          <t>PDMDEP-35652</t>
         </is>
       </c>
       <c r="B12" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-35618</t>
+          <t>PDMDEP-35646</t>
         </is>
       </c>
       <c r="C12" s="11" t="inlineStr">
@@ -10619,7 +10619,7 @@
       </c>
       <c r="D12" s="11" t="inlineStr">
         <is>
-          <t>Commune de la Roche-sur-Yon</t>
+          <t>VILLE DE GEX</t>
         </is>
       </c>
       <c r="E12" s="11" t="inlineStr">
@@ -10639,7 +10639,7 @@
       </c>
       <c r="H12" s="11" t="inlineStr">
         <is>
-          <t>00181123</t>
+          <t>00181167</t>
         </is>
       </c>
       <c r="I12" s="26" t="n">
@@ -10649,22 +10649,22 @@
     <row r="13">
       <c r="A13" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-35576</t>
+          <t>PDMDEP-35622</t>
         </is>
       </c>
       <c r="B13" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-35572</t>
+          <t>PDMDEP-35618</t>
         </is>
       </c>
       <c r="C13" s="14" t="inlineStr">
         <is>
-          <t>08/09/2026</t>
+          <t>10/09/2026</t>
         </is>
       </c>
       <c r="D13" s="14" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DE L'ARIEGE (CD 09)</t>
+          <t>Commune de la Roche-sur-Yon</t>
         </is>
       </c>
       <c r="E13" s="14" t="inlineStr">
@@ -10684,7 +10684,7 @@
       </c>
       <c r="H13" s="14" t="inlineStr">
         <is>
-          <t>00180891</t>
+          <t>00181123</t>
         </is>
       </c>
       <c r="I13" s="25" t="n">
@@ -10694,12 +10694,12 @@
     <row r="14">
       <c r="A14" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-35567</t>
+          <t>PDMDEP-35576</t>
         </is>
       </c>
       <c r="B14" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-35561</t>
+          <t>PDMDEP-35572</t>
         </is>
       </c>
       <c r="C14" s="11" t="inlineStr">
@@ -10709,7 +10709,7 @@
       </c>
       <c r="D14" s="11" t="inlineStr">
         <is>
-          <t>DEPARTEMENT DU MORBIHAN (CD 56)</t>
+          <t>CONSEIL DEPARTEMENTAL DE L'ARIEGE (CD 09)</t>
         </is>
       </c>
       <c r="E14" s="11" t="inlineStr">
@@ -10729,7 +10729,7 @@
       </c>
       <c r="H14" s="11" t="inlineStr">
         <is>
-          <t>00180878</t>
+          <t>00180891</t>
         </is>
       </c>
       <c r="I14" s="26" t="n">
@@ -10739,22 +10739,22 @@
     <row r="15">
       <c r="A15" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-35511</t>
+          <t>PDMDEP-35567</t>
         </is>
       </c>
       <c r="B15" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-35504</t>
+          <t>PDMDEP-35561</t>
         </is>
       </c>
       <c r="C15" s="14" t="inlineStr">
         <is>
-          <t>07/09/2026</t>
+          <t>08/09/2026</t>
         </is>
       </c>
       <c r="D15" s="14" t="inlineStr">
         <is>
-          <t>[TEST]</t>
+          <t>DEPARTEMENT DU MORBIHAN (CD 56)</t>
         </is>
       </c>
       <c r="E15" s="14" t="inlineStr">
@@ -10764,7 +10764,7 @@
       </c>
       <c r="F15" s="14" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="G15" s="14" t="inlineStr">
@@ -10774,7 +10774,7 @@
       </c>
       <c r="H15" s="14" t="inlineStr">
         <is>
-          <t>0015489263</t>
+          <t>00180878</t>
         </is>
       </c>
       <c r="I15" s="25" t="n">
@@ -10784,22 +10784,22 @@
     <row r="16">
       <c r="A16" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-35464</t>
+          <t>PDMDEP-35511</t>
         </is>
       </c>
       <c r="B16" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-35460</t>
+          <t>PDMDEP-35504</t>
         </is>
       </c>
       <c r="C16" s="11" t="inlineStr">
         <is>
-          <t>04/09/2026</t>
+          <t>07/09/2026</t>
         </is>
       </c>
       <c r="D16" s="11" t="inlineStr">
         <is>
-          <t>DEPARTEMENT DE LA CHARENTE (CD 16)</t>
+          <t>[TEST]</t>
         </is>
       </c>
       <c r="E16" s="11" t="inlineStr">
@@ -10809,7 +10809,7 @@
       </c>
       <c r="F16" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="G16" s="11" t="inlineStr">
@@ -10819,83 +10819,107 @@
       </c>
       <c r="H16" s="11" t="inlineStr">
         <is>
-          <t>00180631</t>
+          <t>0015489263</t>
         </is>
       </c>
       <c r="I16" s="26" t="n">
-        <v>455</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="14" t="inlineStr">
         <is>
+          <t>PDMDEP-35464</t>
+        </is>
+      </c>
+      <c r="B17" s="14" t="inlineStr">
+        <is>
+          <t>PDMDEP-35460</t>
+        </is>
+      </c>
+      <c r="C17" s="14" t="inlineStr">
+        <is>
+          <t>04/09/2026</t>
+        </is>
+      </c>
+      <c r="D17" s="14" t="inlineStr">
+        <is>
+          <t>DEPARTEMENT DE LA CHARENTE (CD 16)</t>
+        </is>
+      </c>
+      <c r="E17" s="14" t="inlineStr">
+        <is>
+          <t>LITTERALIS</t>
+        </is>
+      </c>
+      <c r="F17" s="14" t="inlineStr">
+        <is>
+          <t>Vente additionnelle</t>
+        </is>
+      </c>
+      <c r="G17" s="14" t="inlineStr">
+        <is>
+          <t>Services</t>
+        </is>
+      </c>
+      <c r="H17" s="14" t="inlineStr">
+        <is>
+          <t>00180631</t>
+        </is>
+      </c>
+      <c r="I17" s="25" t="n">
+        <v>455</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="11" t="inlineStr">
+        <is>
           <t>PDMDEP-35439</t>
         </is>
       </c>
-      <c r="B17" s="14" t="inlineStr">
+      <c r="B18" s="11" t="inlineStr">
         <is>
           <t>PDMDEP-35435</t>
         </is>
       </c>
-      <c r="C17" s="14" t="inlineStr">
+      <c r="C18" s="11" t="inlineStr">
         <is>
           <t>03/09/2026</t>
         </is>
       </c>
-      <c r="D17" s="14" t="inlineStr">
+      <c r="D18" s="11" t="inlineStr">
         <is>
           <t>DEPARTEMENT DES HAUTS-DE-SEINE</t>
         </is>
       </c>
-      <c r="E17" s="14" t="inlineStr">
+      <c r="E18" s="11" t="inlineStr">
         <is>
           <t>LITTERALIS</t>
         </is>
       </c>
-      <c r="F17" s="14" t="inlineStr">
+      <c r="F18" s="11" t="inlineStr">
         <is>
           <t>Vente additionnelle</t>
         </is>
       </c>
-      <c r="G17" s="14" t="inlineStr">
+      <c r="G18" s="11" t="inlineStr">
         <is>
           <t>Services</t>
         </is>
       </c>
-      <c r="H17" s="14" t="inlineStr">
+      <c r="H18" s="11" t="inlineStr">
         <is>
           <t>00180506</t>
         </is>
       </c>
-      <c r="I17" s="25" t="n">
+      <c r="I18" s="26" t="n">
         <v>3974</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="17" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="B18" s="17" t="n"/>
-      <c r="C18" s="17" t="n"/>
-      <c r="D18" s="17" t="n"/>
-      <c r="E18" s="17" t="n"/>
-      <c r="F18" s="17" t="n"/>
-      <c r="G18" s="17" t="n"/>
-      <c r="H18" s="17" t="inlineStr">
-        <is>
-          <t>13 commande(s)</t>
-        </is>
-      </c>
-      <c r="I18" s="24" t="n">
-        <v>42279</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="17" t="inlineStr">
         <is>
-          <t>dont Littéralis</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="B19" s="17" t="n"/>
@@ -10906,17 +10930,17 @@
       <c r="G19" s="17" t="n"/>
       <c r="H19" s="17" t="inlineStr">
         <is>
-          <t>6 commande(s)</t>
+          <t>14 commande(s)</t>
         </is>
       </c>
       <c r="I19" s="24" t="n">
-        <v>4429</v>
+        <v>42279</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="17" t="inlineStr">
         <is>
-          <t>dont GEODP</t>
+          <t>dont Littéralis</t>
         </is>
       </c>
       <c r="B20" s="17" t="n"/>
@@ -10931,6 +10955,27 @@
         </is>
       </c>
       <c r="I20" s="24" t="n">
+        <v>4429</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="17" t="inlineStr">
+        <is>
+          <t>dont GEODP</t>
+        </is>
+      </c>
+      <c r="B21" s="17" t="n"/>
+      <c r="C21" s="17" t="n"/>
+      <c r="D21" s="17" t="n"/>
+      <c r="E21" s="17" t="n"/>
+      <c r="F21" s="17" t="n"/>
+      <c r="G21" s="17" t="n"/>
+      <c r="H21" s="17" t="inlineStr">
+        <is>
+          <t>7 commande(s)</t>
+        </is>
+      </c>
+      <c r="I21" s="24" t="n">
         <v>37850</v>
       </c>
     </row>
